--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -13456,150 +13456,6 @@
           <val>
             <numRef>
               <f>'VHI_最近6周汇总'!$E$266:$J$266</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="1"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="1"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart266.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln w="20000">
-              <a:solidFill>
-                <a:srgbClr val="E00000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="E00000"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="E00000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <val>
-            <numRef>
-              <f>'VHI_最近6周汇总'!$E$267:$J$267</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="1"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="1"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart267.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln w="20000">
-              <a:solidFill>
-                <a:srgbClr val="E00000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="E00000"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="E00000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <val>
-            <numRef>
-              <f>'VHI_最近6周汇总'!$E$268:$J$268</f>
             </numRef>
           </val>
         </ser>
@@ -25228,50 +25084,6 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2880000" cy="720000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="266" name="Chart 266"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId266"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>267</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2880000" cy="720000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="267" name="Chart 267"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId267"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -25564,7 +25376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L268"/>
+  <dimension ref="A1:L266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -26907,22 +26719,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>60.77</v>
+        <v>60.69</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>60.81</v>
+        <v>60.74</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>60.7</v>
+        <v>60.67</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>59.85</v>
+        <v>59.76</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>58.38</v>
+        <v>58.33</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>56.54</v>
+        <v>56.52</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -29009,12 +28821,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -29022,23 +28834,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E75" s="3" t="n">
-        <v>40.11</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>41.14</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>41.01</v>
+      <c r="E75" s="4" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>33.88</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>39.16</v>
+        <v>34.17</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
@@ -29050,17 +28862,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -29068,23 +28880,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E76" s="4" t="n">
-        <v>28.99</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>29.94</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>30.48</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>33.88</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>34.17</v>
+      <c r="E76" s="3" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>64.20999999999999</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -29106,7 +28918,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>New South Wales</t>
+          <t>Queensland</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -29114,23 +28926,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E77" s="3" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>57.92</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>58.43</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>61.27</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>64.20999999999999</v>
+      <c r="E77" s="4" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="J77" s="4" t="n">
+        <v>38.23</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
@@ -29152,7 +28964,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Queensland</t>
+          <t>South Australia</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -29160,23 +28972,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E78" s="4" t="n">
-        <v>36.02</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>37.07</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>37.22</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>37.18</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>37.68</v>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>38.23</v>
+      <c r="E78" s="3" t="n">
+        <v>64.47</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>66.97</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>70.08</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>72.01000000000001</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>75.51000000000001</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -29198,7 +29010,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>South Australia</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -29207,22 +29019,22 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>64.47</v>
+        <v>56.69</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>66.97</v>
+        <v>58.74</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>68.68000000000001</v>
+        <v>60.09</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>70.08</v>
+        <v>61.26</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>72.01000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>75.51000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -29244,7 +29056,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Western Australia</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -29253,22 +29065,22 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>56.69</v>
+        <v>60.19</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>58.74</v>
+        <v>59.39</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>60.09</v>
+        <v>58.97</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>61.26</v>
+        <v>59.28</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>63.1</v>
+        <v>60.63</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>62.73</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -29280,17 +29092,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Western Australia</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -29298,23 +29110,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E81" s="3" t="n">
-        <v>60.19</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>59.39</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>58.97</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>59.28</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>62.73</v>
+      <c r="E81" s="4" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>36.03</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -29336,7 +29148,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -29344,23 +29156,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n">
-        <v>30.01</v>
-      </c>
-      <c r="F82" s="4" t="n">
-        <v>30.49</v>
-      </c>
-      <c r="G82" s="4" t="n">
-        <v>32.15</v>
-      </c>
-      <c r="H82" s="4" t="n">
-        <v>34.23</v>
-      </c>
-      <c r="I82" s="4" t="n">
-        <v>35.91</v>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>36.03</v>
+      <c r="E82" s="3" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>46.43</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -29382,7 +29194,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -29391,22 +29203,22 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>59.99</v>
+        <v>53.19</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>57.64</v>
+        <v>52.21</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>54.77</v>
+        <v>49.8</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>51.53</v>
+        <v>46.2</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>48.65</v>
+        <v>45.36</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>46.43</v>
+        <v>45.84</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -29428,7 +29240,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -29436,23 +29248,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E84" s="3" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>52.21</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>49.8</v>
+      <c r="E84" s="4" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>39.94</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>46.2</v>
+        <v>41.28</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>45.36</v>
+        <v>41.7</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>45.84</v>
+        <v>40.48</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -29474,7 +29286,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -29482,23 +29294,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E85" s="4" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="F85" s="4" t="n">
-        <v>38.21</v>
-      </c>
-      <c r="G85" s="4" t="n">
-        <v>39.94</v>
+      <c r="E85" s="3" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>56.51</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>41.28</v>
+        <v>54.87</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>41.7</v>
+        <v>53.22</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>40.48</v>
+        <v>50.79</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -29520,7 +29332,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -29529,22 +29341,22 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>56.72</v>
+        <v>47.82</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>56.93</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>56.51</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>54.87</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>53.22</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>50.79</v>
+        <v>42.88</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>32.12</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>30.61</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -29566,7 +29378,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -29574,23 +29386,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E87" s="3" t="n">
-        <v>47.82</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>42.88</v>
+      <c r="E87" s="4" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>34.67</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>38.69</v>
+        <v>35.69</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>34.83</v>
+        <v>37.43</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>32.12</v>
+        <v>38.76</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>30.61</v>
+        <v>37.76</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -29602,17 +29414,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -29620,23 +29432,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E88" s="4" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="F88" s="4" t="n">
-        <v>34.67</v>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v>35.69</v>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="I88" s="4" t="n">
-        <v>38.76</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>37.76</v>
+      <c r="E88" s="3" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>65.58</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -29658,7 +29470,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -29667,22 +29479,22 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>55.63</v>
+        <v>53.65</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>57.49</v>
+        <v>55.89</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>58.4</v>
+        <v>58.61</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>59.04</v>
+        <v>61.46</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>60.28</v>
+        <v>63.41</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>65.58</v>
+        <v>66.98</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -29704,7 +29516,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -29713,22 +29525,22 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>53.65</v>
+        <v>62.69</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>55.89</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>58.61</v>
+        <v>69.52</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>61.46</v>
+        <v>71.56</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>63.41</v>
+        <v>71.67</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>66.98</v>
+        <v>73.36</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -29740,41 +29552,41 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>棉花</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>62.69</v>
+        <v>60.35</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>66.34999999999999</v>
+        <v>60.09</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>69.52</v>
+        <v>58.97</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>71.56</v>
+        <v>57.9</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>71.67</v>
+        <v>56.87</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>73.36</v>
+        <v>57.39</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
@@ -29786,17 +29598,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>中央邦</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -29805,22 +29617,22 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>60.35</v>
+        <v>43.75</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>60.09</v>
+        <v>44.27</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>58.97</v>
+        <v>46.12</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>57.9</v>
+        <v>49.11</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>56.87</v>
+        <v>52.14</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>57.39</v>
+        <v>53.99</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -29842,7 +29654,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>中央邦</t>
+          <t>卡纳塔克邦</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -29851,22 +29663,22 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>43.75</v>
+        <v>48.79</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>44.27</v>
+        <v>48.28</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>46.12</v>
+        <v>47.79</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>49.11</v>
+        <v>47.55</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>52.14</v>
+        <v>47.71</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>53.99</v>
+        <v>48.03</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
@@ -29888,7 +29700,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>卡纳塔克邦</t>
+          <t>古吉拉特邦</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -29897,22 +29709,22 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>48.79</v>
+        <v>43.77</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>48.28</v>
+        <v>44.18</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>47.79</v>
+        <v>45.23</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>47.55</v>
+        <v>48.16</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>47.71</v>
+        <v>52.59</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>48.03</v>
+        <v>57.44</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -29934,7 +29746,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>古吉拉特邦</t>
+          <t>安得拉邦</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -29943,22 +29755,22 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>43.77</v>
+        <v>42.45</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>44.18</v>
+        <v>42.17</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>48.16</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>52.59</v>
+        <v>41.21</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>39.93</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>57.44</v>
+        <v>40.04</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
@@ -29980,7 +29792,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>安得拉邦</t>
+          <t>拉贾斯坦邦</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -29989,22 +29801,22 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>42.45</v>
+        <v>62.56</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>42.17</v>
+        <v>62.52</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>41.21</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>39.93</v>
+        <v>62.96</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>66.03</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>40.04</v>
+        <v>68.94</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -30026,7 +29838,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>拉贾斯坦邦</t>
+          <t>马哈拉施特拉邦</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -30035,22 +29847,22 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>62.56</v>
+        <v>44.92</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>62.52</v>
+        <v>45.9</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>62.96</v>
+        <v>47.5</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>49.19</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>66.03</v>
+        <v>51.28</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>68.94</v>
+        <v>53.82</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
@@ -30062,17 +29874,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>马哈拉施特拉邦</t>
+          <t>南马托格罗索州</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -30081,22 +29893,22 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>44.92</v>
+        <v>63.84</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>45.9</v>
+        <v>62.97</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>47.5</v>
+        <v>62.68</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>49.19</v>
+        <v>62.62</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>51.28</v>
+        <v>62.41</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>53.82</v>
+        <v>62.22</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -30118,7 +29930,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>南马托格罗索州</t>
+          <t>巴伊亚州</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -30127,22 +29939,22 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>63.84</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>62.97</v>
+        <v>40.64</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>39.99</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>62.68</v>
+        <v>40.25</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>62.62</v>
+        <v>41.67</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>62.41</v>
+        <v>43.68</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>62.22</v>
+        <v>47.84</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -30154,17 +29966,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>巴伊亚州</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -30173,22 +29985,22 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="F100" s="4" t="n">
-        <v>39.99</v>
+        <v>58.37</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>59.99</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>40.25</v>
+        <v>60.95</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>41.67</v>
+        <v>62.35</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>43.68</v>
+        <v>64.56</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>47.84</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -30210,7 +30022,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>New South Wales</t>
+          <t>Queensland</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -30218,23 +30030,23 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E101" s="3" t="n">
-        <v>58.37</v>
+      <c r="E101" s="4" t="n">
+        <v>39.47</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>59.99</v>
+        <v>40.83</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>60.95</v>
+        <v>41.17</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>62.35</v>
+        <v>41.38</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>64.56</v>
+        <v>41.95</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>67.45999999999999</v>
+        <v>42.71</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -30246,17 +30058,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Queensland</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -30264,23 +30076,23 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E102" s="4" t="n">
-        <v>39.47</v>
+      <c r="E102" s="3" t="n">
+        <v>66.55</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>40.83</v>
+        <v>64.52</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>41.17</v>
+        <v>62.76</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>41.38</v>
+        <v>61.11</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>41.95</v>
+        <v>58.76</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>42.71</v>
+        <v>56.11</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -30302,7 +30114,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -30311,22 +30123,22 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>66.55</v>
+        <v>55.46</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>64.52</v>
+        <v>50</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>62.76</v>
+        <v>45.29</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>58.76</v>
-      </c>
-      <c r="J103" s="3" t="n">
-        <v>56.11</v>
+        <v>41.7</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="J103" s="4" t="n">
+        <v>38.4</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -30348,7 +30160,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -30357,22 +30169,22 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>55.46</v>
+        <v>56.27</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>50</v>
+        <v>56.25</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>45.29</v>
+        <v>57.75</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I104" s="4" t="n">
-        <v>39.09</v>
-      </c>
-      <c r="J104" s="4" t="n">
-        <v>38.4</v>
+        <v>60.38</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>62.5</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -30394,7 +30206,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -30403,22 +30215,22 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>56.27</v>
+        <v>56.92</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>56.25</v>
+        <v>52.76</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>57.75</v>
+        <v>49.11</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>60.38</v>
+        <v>46.42</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>61.41</v>
+        <v>44.1</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>62.5</v>
+        <v>42.22</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -30440,7 +30252,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -30449,22 +30261,22 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>56.92</v>
+        <v>64.55</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>52.76</v>
+        <v>61.59</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>49.11</v>
+        <v>58.93</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>46.42</v>
+        <v>55.61</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>44.1</v>
+        <v>52.09</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>42.22</v>
+        <v>49.94</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -30486,7 +30298,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -30495,22 +30307,22 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>64.55</v>
+        <v>53.98</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>61.59</v>
+        <v>55.08</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>58.93</v>
+        <v>55.04</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>55.61</v>
+        <v>54.56</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>52.09</v>
+        <v>52.52</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>49.94</v>
+        <v>51.59</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -30532,7 +30344,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -30541,22 +30353,22 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>53.98</v>
+        <v>68.3</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>55.08</v>
+        <v>64.02</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>55.04</v>
+        <v>59.71</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>54.56</v>
+        <v>55.93</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>52.52</v>
+        <v>51.95</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>51.59</v>
+        <v>48.73</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -30578,7 +30390,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -30586,23 +30398,23 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E109" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>64.02</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>59.71</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>51.95</v>
-      </c>
-      <c r="J109" s="3" t="n">
-        <v>48.73</v>
+      <c r="E109" s="4" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="J109" s="4" t="n">
+        <v>32.89</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -30614,41 +30426,41 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>东加里曼丹</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>棉花</t>
+          <t>棕榈油</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>37.48</v>
+        <v>37.98</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>35.43</v>
+        <v>36.42</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>34.41</v>
+        <v>35.12</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>33.5</v>
+        <v>34.05</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>33.03</v>
+        <v>33.37</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>32.89</v>
+        <v>32.96</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -30670,7 +30482,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>东加里曼丹</t>
+          <t>中加里曼丹</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -30679,22 +30491,22 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>37.98</v>
+        <v>32.76</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>36.42</v>
+        <v>32.64</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>35.12</v>
+        <v>32.31</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>34.05</v>
+        <v>31.49</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>33.37</v>
+        <v>31.85</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>32.96</v>
+        <v>32.42</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
@@ -30716,7 +30528,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>中加里曼丹</t>
+          <t>北苏门答腊</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -30724,23 +30536,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E112" s="4" t="n">
-        <v>32.76</v>
-      </c>
-      <c r="F112" s="4" t="n">
-        <v>32.64</v>
-      </c>
-      <c r="G112" s="4" t="n">
-        <v>32.31</v>
-      </c>
-      <c r="H112" s="4" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="I112" s="4" t="n">
-        <v>31.85</v>
-      </c>
-      <c r="J112" s="4" t="n">
-        <v>32.42</v>
+      <c r="E112" s="3" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>42.21</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -30762,7 +30574,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>北苏门答腊</t>
+          <t>南苏门答腊</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -30770,23 +30582,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E113" s="3" t="n">
-        <v>48.16</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>46.35</v>
-      </c>
-      <c r="G113" s="3" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="H113" s="3" t="n">
-        <v>43.31</v>
-      </c>
-      <c r="I113" s="3" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="J113" s="3" t="n">
-        <v>42.21</v>
+      <c r="E113" s="4" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="J113" s="4" t="n">
+        <v>36.27</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
@@ -30808,7 +30620,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>南苏门答腊</t>
+          <t>占碑</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -30817,22 +30629,22 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>33.4</v>
+        <v>32.64</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>33.76</v>
+        <v>32.36</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>34.19</v>
+        <v>32.29</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>34.72</v>
+        <v>31.94</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>35.55</v>
+        <v>31.91</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>36.27</v>
+        <v>33.78</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -30854,7 +30666,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>占碑</t>
+          <t>廖内</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -30862,23 +30674,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E115" s="4" t="n">
-        <v>32.64</v>
-      </c>
-      <c r="F115" s="4" t="n">
-        <v>32.36</v>
+      <c r="E115" s="3" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>41.5</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>32.29</v>
+        <v>39.44</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>31.94</v>
+        <v>36.63</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>31.91</v>
+        <v>34.76</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>33.78</v>
+        <v>34.83</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
@@ -30900,7 +30712,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>廖内</t>
+          <t>西加里曼丹</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -30908,23 +30720,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E116" s="3" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>41.5</v>
+      <c r="E116" s="4" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>27.57</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>39.44</v>
+        <v>27.39</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>36.63</v>
+        <v>27.49</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>34.76</v>
+        <v>28.25</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>34.83</v>
+        <v>28.33</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -30936,17 +30748,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>西加里曼丹</t>
+          <t>Johor</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -30955,22 +30767,22 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>29.24</v>
+        <v>39.3</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>27.57</v>
+        <v>38.54</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>27.39</v>
+        <v>37.22</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>27.49</v>
+        <v>35.96</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>28.25</v>
+        <v>35.66</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>28.33</v>
+        <v>35.53</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
@@ -30992,7 +30804,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Johor</t>
+          <t>Pahang</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -31000,23 +30812,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E118" s="4" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="F118" s="4" t="n">
-        <v>38.54</v>
-      </c>
-      <c r="G118" s="4" t="n">
-        <v>37.22</v>
+      <c r="E118" s="3" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>41.68</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>35.96</v>
+        <v>39.66</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>35.66</v>
+        <v>38.29</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>35.53</v>
+        <v>37.77</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -31038,7 +30850,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Pahang</t>
+          <t>Perak</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -31047,22 +30859,22 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>44.84</v>
+        <v>45.04</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>43.64</v>
+        <v>43.83</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>41.68</v>
-      </c>
-      <c r="H119" s="4" t="n">
-        <v>39.66</v>
-      </c>
-      <c r="I119" s="4" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="J119" s="4" t="n">
-        <v>37.77</v>
+        <v>42.56</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>41.75</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
@@ -31084,7 +30896,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Perak</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -31093,22 +30905,22 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>45.04</v>
+        <v>42.77</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>43.83</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>42.56</v>
-      </c>
-      <c r="H120" s="3" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="I120" s="3" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="J120" s="3" t="n">
-        <v>41.75</v>
+        <v>41.13</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>39.32</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="I120" s="4" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="J120" s="4" t="n">
+        <v>36.67</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -31130,7 +30942,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Sarawak</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -31138,23 +30950,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E121" s="3" t="n">
-        <v>42.77</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>41.13</v>
+      <c r="E121" s="4" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>34.71</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>39.32</v>
+        <v>32.8</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>37.98</v>
+        <v>31.59</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>36.87</v>
+        <v>30.9</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>36.67</v>
+        <v>30.16</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
@@ -31166,41 +30978,41 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Sarawak</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>棕榈油</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>37.05</v>
-      </c>
-      <c r="F122" s="4" t="n">
-        <v>34.71</v>
-      </c>
-      <c r="G122" s="4" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="H122" s="4" t="n">
-        <v>31.59</v>
-      </c>
-      <c r="I122" s="4" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="J122" s="4" t="n">
-        <v>30.16</v>
+          <t>玉米</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>49.71</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -31222,7 +31034,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -31231,22 +31043,22 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>47.43</v>
+        <v>70.48</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>48.21</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>48.64</v>
+        <v>71.25</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>48.79</v>
+        <v>70.77</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>49.36</v>
+        <v>69.31</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>49.71</v>
+        <v>67.23</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
@@ -31268,7 +31080,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -31277,22 +31089,22 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>70.48</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>70.81999999999999</v>
+        <v>65.03</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>71.25</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>70.77</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>69.31</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>67.23</v>
+        <v>64.86</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -31314,7 +31126,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -31323,22 +31135,22 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>47.71</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>65.03</v>
+        <v>48.23</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>65.98999999999999</v>
+        <v>48.1</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>48.08</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>65.73999999999999</v>
+        <v>48.21</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>64.86</v>
+        <v>47.63</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
@@ -31360,7 +31172,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -31369,22 +31181,22 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>47.71</v>
+        <v>59.73</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>48.23</v>
+        <v>57.71</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>48.1</v>
+        <v>55.14</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>48.08</v>
+        <v>52.43</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>48.21</v>
+        <v>51.02</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>47.63</v>
+        <v>51.1</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -31406,7 +31218,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -31414,23 +31226,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E127" s="3" t="n">
-        <v>59.73</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>55.14</v>
+      <c r="E127" s="6" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="G127" s="6" t="n">
+        <v>80.14</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>52.43</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>51.02</v>
+        <v>72.86</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>51.1</v>
+        <v>67.31</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
@@ -31452,7 +31264,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -31460,23 +31272,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E128" s="6" t="n">
-        <v>82.65000000000001</v>
-      </c>
-      <c r="F128" s="6" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="G128" s="6" t="n">
-        <v>80.14</v>
+      <c r="E128" s="3" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>53.2</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>77.23999999999999</v>
+        <v>52.28</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>72.86</v>
+        <v>51.42</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>67.31</v>
+        <v>51.56</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -31498,7 +31310,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -31507,22 +31319,22 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>54.12</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>54.04</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>53.2</v>
+        <v>70.98</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>52.28</v>
+        <v>66.58</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>51.42</v>
+        <v>61.14</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>51.56</v>
+        <v>57.71</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
@@ -31544,7 +31356,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -31553,22 +31365,22 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>75.65000000000001</v>
+        <v>62.47</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>73.70999999999999</v>
+        <v>62.26</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>70.98</v>
+        <v>61.83</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>66.58</v>
+        <v>61.1</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>61.14</v>
+        <v>59.45</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>57.71</v>
+        <v>58.96</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -31590,7 +31402,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -31599,22 +31411,22 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>62.47</v>
+        <v>62.4</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>62.26</v>
+        <v>61.9</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>61.83</v>
+        <v>61.39</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>61.1</v>
+        <v>60.53</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>59.45</v>
+        <v>59.08</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>58.96</v>
+        <v>58.6</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
@@ -31636,7 +31448,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -31645,22 +31457,22 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>62.4</v>
+        <v>71.87</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>61.9</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>61.39</v>
+        <v>73.86</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>60.53</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>59.08</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>58.6</v>
+        <v>68.94</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -31672,17 +31484,17 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>Cherkaska</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -31691,22 +31503,22 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>71.87</v>
+        <v>55.24</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>72.93000000000001</v>
+        <v>51.66</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>73.86</v>
+        <v>47.42</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>73.65000000000001</v>
+        <v>43.5</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>72.56999999999999</v>
-      </c>
-      <c r="J133" s="3" t="n">
-        <v>68.94</v>
+        <v>40.48</v>
+      </c>
+      <c r="J133" s="4" t="n">
+        <v>39.56</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
@@ -31728,7 +31540,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Cherkaska</t>
+          <t>Chernihivska</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -31737,22 +31549,22 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>55.24</v>
+        <v>65.64</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>51.66</v>
+        <v>62.65</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>47.42</v>
+        <v>57.06</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>43.5</v>
+        <v>50.63</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="J134" s="4" t="n">
-        <v>39.56</v>
+        <v>45.94</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>43.92</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -31774,7 +31586,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Chernihivska</t>
+          <t>Dnipropetrovska</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -31783,22 +31595,22 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>65.64</v>
+        <v>57.21</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>62.65</v>
+        <v>53.37</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>57.06</v>
+        <v>49.9</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>50.63</v>
+        <v>46.93</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>45.94</v>
+        <v>43.85</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>43.92</v>
+        <v>41.19</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
@@ -31820,7 +31632,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Dnipropetrovska</t>
+          <t>Donetsk</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -31829,22 +31641,22 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>57.21</v>
+        <v>48.18</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>53.37</v>
+        <v>45.08</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="H136" s="3" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="I136" s="3" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="J136" s="3" t="n">
-        <v>41.19</v>
+        <v>41.96</v>
+      </c>
+      <c r="H136" s="4" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="J136" s="4" t="n">
+        <v>36.11</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -31866,7 +31678,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Donetsk</t>
+          <t>Khersonska</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -31874,23 +31686,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E137" s="3" t="n">
-        <v>48.18</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="G137" s="3" t="n">
-        <v>41.96</v>
+      <c r="E137" s="4" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>23.03</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="I137" s="4" t="n">
-        <v>37.39</v>
-      </c>
-      <c r="J137" s="4" t="n">
-        <v>36.11</v>
+        <v>20.92</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>17.79</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
@@ -31912,7 +31724,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Khersonska</t>
+          <t>Khmelnitska</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -31920,23 +31732,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E138" s="4" t="n">
-        <v>27.67</v>
-      </c>
-      <c r="F138" s="4" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="G138" s="4" t="n">
-        <v>23.03</v>
-      </c>
-      <c r="H138" s="4" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>17.79</v>
+      <c r="E138" s="3" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>51.12</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -31958,7 +31770,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Khmelnitska</t>
+          <t>Kirovohradska</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -31967,22 +31779,22 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>59.25</v>
+        <v>52.49</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>59.32</v>
+        <v>49.28</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>58.6</v>
+        <v>47.07</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>56.39</v>
+        <v>45.23</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>53.32</v>
-      </c>
-      <c r="J139" s="3" t="n">
-        <v>51.12</v>
+        <v>42.56</v>
+      </c>
+      <c r="J139" s="4" t="n">
+        <v>39.28</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
@@ -32004,7 +31816,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Kirovohradska</t>
+          <t>Kyivska</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -32013,22 +31825,22 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>52.49</v>
+        <v>57</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>49.28</v>
+        <v>54.09</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>47.07</v>
+        <v>49.94</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>45.23</v>
+        <v>45.78</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>42.56</v>
-      </c>
-      <c r="J140" s="4" t="n">
-        <v>39.28</v>
+        <v>42.89</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>42.21</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -32050,7 +31862,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Kyivska</t>
+          <t>Mykolaivska</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -32058,23 +31870,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E141" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>54.09</v>
-      </c>
-      <c r="G141" s="3" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="H141" s="3" t="n">
-        <v>45.78</v>
-      </c>
-      <c r="I141" s="3" t="n">
-        <v>42.89</v>
-      </c>
-      <c r="J141" s="3" t="n">
-        <v>42.21</v>
+      <c r="E141" s="4" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="I141" s="4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="J141" s="4" t="n">
+        <v>26.94</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -32096,7 +31908,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Mykolaivska</t>
+          <t>Odeska</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -32104,23 +31916,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E142" s="4" t="n">
-        <v>36.82</v>
+      <c r="E142" s="3" t="n">
+        <v>41.49</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>34.22</v>
+        <v>37.84</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>32.17</v>
+        <v>34.86</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>30.57</v>
+        <v>32.53</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>28.8</v>
+        <v>30.34</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>26.94</v>
+        <v>29.37</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -32142,7 +31954,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Odeska</t>
+          <t>Poltava</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -32151,22 +31963,22 @@
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>41.49</v>
-      </c>
-      <c r="F143" s="4" t="n">
-        <v>37.84</v>
-      </c>
-      <c r="G143" s="4" t="n">
-        <v>34.86</v>
-      </c>
-      <c r="H143" s="4" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="I143" s="4" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="J143" s="4" t="n">
-        <v>29.37</v>
+        <v>66.58</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>45.77</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
@@ -32188,7 +32000,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Poltava</t>
+          <t>Sumy</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -32197,22 +32009,22 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>66.58</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>63.63</v>
+        <v>70.16</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>59.84</v>
+        <v>66.28</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>54.8</v>
+        <v>60.91</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>49.4</v>
+        <v>56.18</v>
       </c>
       <c r="J144" s="3" t="n">
-        <v>45.77</v>
+        <v>51.94</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -32234,7 +32046,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Sumy</t>
+          <t>Vinnitsa</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -32243,22 +32055,22 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>72.15000000000001</v>
+        <v>60.56</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>70.16</v>
+        <v>58.68</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>66.28</v>
+        <v>56.43</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>60.91</v>
+        <v>53.48</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>56.18</v>
+        <v>49.3</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>51.94</v>
+        <v>47.09</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
@@ -32280,7 +32092,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Vinnitsa</t>
+          <t>Zaporizka</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -32288,23 +32100,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E146" s="3" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>58.68</v>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>56.43</v>
-      </c>
-      <c r="H146" s="3" t="n">
-        <v>53.48</v>
-      </c>
-      <c r="I146" s="3" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="J146" s="3" t="n">
-        <v>47.09</v>
+      <c r="E146" s="4" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="H146" s="4" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="I146" s="4" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="J146" s="4" t="n">
+        <v>24.39</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -32326,7 +32138,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Zaporizka</t>
+          <t>Zhytomyrska</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -32334,23 +32146,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E147" s="4" t="n">
-        <v>34.59</v>
-      </c>
-      <c r="F147" s="4" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="G147" s="4" t="n">
-        <v>29.15</v>
-      </c>
-      <c r="H147" s="4" t="n">
-        <v>27.39</v>
-      </c>
-      <c r="I147" s="4" t="n">
-        <v>25.54</v>
-      </c>
-      <c r="J147" s="4" t="n">
-        <v>24.39</v>
+      <c r="E147" s="3" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>50.84</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
@@ -32362,17 +32174,17 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Zhytomyrska</t>
+          <t>南马托格罗索州</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -32381,22 +32193,22 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>60.42</v>
+        <v>64.11</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>60.52</v>
+        <v>63.52</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>59.34</v>
+        <v>63.58</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>56.47</v>
+        <v>63.5</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>52.68</v>
+        <v>63.24</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>50.84</v>
+        <v>63.08</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -32418,7 +32230,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>南马托格罗索州</t>
+          <t>圣保罗州</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -32427,22 +32239,22 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>64.11</v>
+        <v>71.03</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>63.52</v>
+        <v>72.64</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>63.58</v>
+        <v>74.27</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>63.5</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>63.24</v>
+        <v>75</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>63.08</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
@@ -32464,7 +32276,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>圣保罗州</t>
+          <t>巴拉那州</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -32473,22 +32285,22 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>71.03</v>
+        <v>63.58</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>72.64</v>
+        <v>65.25</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>74.27</v>
+        <v>66.14</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>74.79000000000001</v>
+        <v>66.14</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>75</v>
+        <v>65.37</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>63.98</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -32510,7 +32322,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>巴拉那州</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -32519,22 +32331,22 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>63.58</v>
+        <v>49.14</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>65.25</v>
+        <v>49.17</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>66.14</v>
+        <v>50.05</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>66.14</v>
+        <v>51.83</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>65.37</v>
+        <v>53.74</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>63.98</v>
+        <v>55.76</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
@@ -32556,7 +32368,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -32565,22 +32377,22 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>49.14</v>
+        <v>57.85</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>49.17</v>
+        <v>57.02</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>50.05</v>
+        <v>56.96</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>51.83</v>
+        <v>57</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>53.74</v>
+        <v>57.44</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>55.76</v>
+        <v>57.95</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -32602,7 +32414,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -32611,22 +32423,22 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>57.85</v>
+        <v>50.94</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>57.02</v>
+        <v>51.17</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>56.96</v>
+        <v>51.66</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>57</v>
+        <v>52.62</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>57.44</v>
+        <v>53.98</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>57.95</v>
+        <v>55.71</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
@@ -32638,17 +32450,17 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -32656,23 +32468,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E154" s="3" t="n">
-        <v>50.94</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>51.17</v>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>51.66</v>
-      </c>
-      <c r="H154" s="3" t="n">
-        <v>52.62</v>
-      </c>
-      <c r="I154" s="3" t="n">
-        <v>53.98</v>
-      </c>
-      <c r="J154" s="3" t="n">
-        <v>55.71</v>
+      <c r="E154" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="H154" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>28.89</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -32689,12 +32501,12 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -32702,23 +32514,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E155" s="4" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="F155" s="4" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="G155" s="4" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="H155" s="4" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="I155" s="4" t="n">
-        <v>29.33</v>
-      </c>
-      <c r="J155" s="4" t="n">
-        <v>28.89</v>
+      <c r="E155" s="3" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>40.76</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
@@ -32735,12 +32547,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -32748,23 +32560,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E156" s="3" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="G156" s="3" t="n">
-        <v>45.09</v>
-      </c>
-      <c r="H156" s="3" t="n">
-        <v>43.74</v>
-      </c>
-      <c r="I156" s="3" t="n">
-        <v>42.17</v>
-      </c>
-      <c r="J156" s="3" t="n">
-        <v>40.76</v>
+      <c r="E156" s="5" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="G156" s="4" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="H156" s="4" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <v>24.35</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -32781,12 +32593,12 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -32794,23 +32606,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E157" s="5" t="n">
-        <v>17.51</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>18.54</v>
+      <c r="E157" s="4" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>37.42</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="H157" s="4" t="n">
-        <v>22.42</v>
-      </c>
-      <c r="I157" s="4" t="n">
-        <v>24.62</v>
-      </c>
-      <c r="J157" s="4" t="n">
-        <v>24.35</v>
+        <v>38.54</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>41.15</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
@@ -32827,12 +32639,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -32841,22 +32653,22 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>36.84</v>
+        <v>21.76</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>37.42</v>
+        <v>21.01</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>38.54</v>
-      </c>
-      <c r="H158" s="3" t="n">
-        <v>40.01</v>
-      </c>
-      <c r="I158" s="3" t="n">
-        <v>41.05</v>
-      </c>
-      <c r="J158" s="3" t="n">
-        <v>41.15</v>
+        <v>20.31</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>20.06</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -32873,12 +32685,12 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -32887,22 +32699,22 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>21.76</v>
+        <v>36.76</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>21.01</v>
+        <v>36.47</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>20.31</v>
-      </c>
-      <c r="H159" s="5" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>19.61</v>
+        <v>36.24</v>
+      </c>
+      <c r="H159" s="4" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>35.77</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>20.06</v>
+        <v>35.84</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
@@ -32919,12 +32731,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -32932,23 +32744,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E160" s="4" t="n">
-        <v>36.76</v>
-      </c>
-      <c r="F160" s="4" t="n">
-        <v>36.47</v>
-      </c>
-      <c r="G160" s="4" t="n">
-        <v>36.24</v>
-      </c>
-      <c r="H160" s="4" t="n">
-        <v>36.03</v>
-      </c>
-      <c r="I160" s="4" t="n">
-        <v>35.77</v>
-      </c>
-      <c r="J160" s="4" t="n">
-        <v>35.84</v>
+      <c r="E160" s="3" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>52.26</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -32965,12 +32777,12 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -32979,22 +32791,22 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>53.45</v>
+        <v>44.52</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>53.47</v>
-      </c>
-      <c r="G161" s="3" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="H161" s="3" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="I161" s="3" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="J161" s="3" t="n">
-        <v>52.26</v>
+        <v>41.69</v>
+      </c>
+      <c r="G161" s="4" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="H161" s="4" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="I161" s="4" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="J161" s="4" t="n">
+        <v>35.41</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
@@ -33011,12 +32823,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -33024,23 +32836,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E162" s="3" t="n">
-        <v>44.52</v>
+      <c r="E162" s="4" t="n">
+        <v>39.81</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>41.69</v>
-      </c>
-      <c r="G162" s="4" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="H162" s="4" t="n">
-        <v>37.82</v>
-      </c>
-      <c r="I162" s="4" t="n">
-        <v>36.49</v>
+        <v>40.59</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>40.58</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>35.41</v>
+        <v>38.97</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -33052,17 +32864,17 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -33070,23 +32882,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E163" s="4" t="n">
-        <v>39.81</v>
+      <c r="E163" s="3" t="n">
+        <v>61.07</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>40.59</v>
+        <v>62.25</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>40.65</v>
+        <v>63.23</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>40.67</v>
+        <v>62.88</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>40.58</v>
-      </c>
-      <c r="J163" s="4" t="n">
-        <v>38.97</v>
+        <v>61.6</v>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>60.03</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
@@ -33108,7 +32920,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -33117,22 +32929,22 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>61.07</v>
+        <v>60.06</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>62.25</v>
+        <v>61.69</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>63.23</v>
+        <v>62.9</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>62.88</v>
+        <v>63.62</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>61.6</v>
+        <v>63.49</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>60.03</v>
+        <v>60.46</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -33154,7 +32966,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -33163,22 +32975,22 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>63.61</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="J165" s="3" t="n">
         <v>60.06</v>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>61.69</v>
-      </c>
-      <c r="G165" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="H165" s="3" t="n">
-        <v>63.62</v>
-      </c>
-      <c r="I165" s="3" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="J165" s="3" t="n">
-        <v>60.46</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
@@ -33200,7 +33012,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -33209,22 +33021,22 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>60.94</v>
+        <v>59.86</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>62.32</v>
+        <v>57.54</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>63.61</v>
+        <v>54.71</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>63.21</v>
+        <v>51.49</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>62.79</v>
+        <v>48.6</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>60.06</v>
+        <v>46.39</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -33246,7 +33058,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -33255,22 +33067,22 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>59.86</v>
+        <v>53.53</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>57.54</v>
+        <v>52.18</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>54.71</v>
+        <v>49.23</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>51.49</v>
+        <v>44.99</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>48.6</v>
+        <v>44.01</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>46.39</v>
+        <v>44.62</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
@@ -33292,7 +33104,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -33301,22 +33113,22 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>53.53</v>
+        <v>58.74</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>52.18</v>
+        <v>60.34</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>49.23</v>
+        <v>61.25</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>44.99</v>
+        <v>61.44</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>44.01</v>
+        <v>61.68</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>44.62</v>
+        <v>61.86</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -33338,7 +33150,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -33347,22 +33159,22 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>58.74</v>
+        <v>58.55</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>60.34</v>
+        <v>62.21</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>61.25</v>
+        <v>64.59</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>61.44</v>
+        <v>65.3</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>61.68</v>
+        <v>65.17</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>61.86</v>
+        <v>62.74</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
@@ -33384,7 +33196,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -33393,22 +33205,22 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>58.55</v>
+        <v>53.56</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>62.21</v>
+        <v>54.32</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>64.59</v>
+        <v>54.1</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>65.3</v>
+        <v>52.2</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>65.17</v>
+        <v>50.77</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>62.74</v>
+        <v>48.97</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -33430,7 +33242,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -33439,22 +33251,22 @@
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>53.56</v>
+        <v>42.43</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>54.32</v>
+        <v>42.39</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>54.1</v>
+        <v>42.47</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>52.2</v>
+        <v>42.64</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>50.77</v>
+        <v>42.8</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>48.97</v>
+        <v>43.32</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
@@ -33466,17 +33278,17 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -33485,22 +33297,22 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>42.43</v>
+        <v>55.64</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>42.39</v>
+        <v>57.48</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>42.47</v>
+        <v>58.32</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>42.64</v>
+        <v>58.94</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>42.8</v>
+        <v>60.18</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>43.32</v>
+        <v>65.53</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -33522,7 +33334,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -33531,22 +33343,22 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>55.64</v>
+        <v>53.62</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>57.48</v>
+        <v>55.89</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>58.32</v>
+        <v>58.63</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>58.94</v>
+        <v>61.53</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>60.18</v>
+        <v>63.49</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>65.53</v>
+        <v>67.09</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
@@ -33568,7 +33380,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -33577,22 +33389,22 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>53.62</v>
+        <v>62.64</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>55.89</v>
+        <v>66.3</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>58.63</v>
+        <v>69.47</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>61.53</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>63.49</v>
+        <v>71.61</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>67.09</v>
+        <v>73.3</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -33614,7 +33426,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Santiago del Estero</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -33623,22 +33435,22 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>62.64</v>
+        <v>68.14</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>66.3</v>
+        <v>71.95</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>69.47</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>71.51000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>71.61</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>73.3</v>
+        <v>77.8</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
@@ -33650,41 +33462,41 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>甘蔗</t>
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>68.14</v>
+        <v>46.47</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>71.95</v>
+        <v>47.45</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>75.65000000000001</v>
+        <v>47.83</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>77.36</v>
+        <v>47.99</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>76.73999999999999</v>
+        <v>48.78</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>77.8</v>
+        <v>49.34</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -33706,7 +33518,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -33715,22 +33527,22 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>46.47</v>
+        <v>58.03</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>47.45</v>
+        <v>60.5</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>47.83</v>
+        <v>61.23</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>47.99</v>
+        <v>60.82</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>48.78</v>
+        <v>60.1</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>49.34</v>
+        <v>59.54</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
@@ -33752,7 +33564,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -33761,22 +33573,22 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>58.03</v>
+        <v>56.96</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>60.5</v>
+        <v>58.85</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>61.23</v>
+        <v>61.06</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>60.82</v>
+        <v>62.02</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>60.1</v>
+        <v>61.45</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>59.54</v>
+        <v>60.72</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -33798,7 +33610,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -33810,19 +33622,19 @@
         <v>56.96</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>58.85</v>
+        <v>59.28</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>61.06</v>
+        <v>61.23</v>
       </c>
       <c r="H179" s="3" t="n">
         <v>62.02</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>61.45</v>
+        <v>61.23</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>60.72</v>
+        <v>59.12</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
@@ -33834,17 +33646,17 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北方邦</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -33853,22 +33665,22 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>56.96</v>
+        <v>52.73</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>59.28</v>
+        <v>55.24</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>61.23</v>
+        <v>57.93</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>62.02</v>
+        <v>60.65</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>61.23</v>
+        <v>63.48</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>59.12</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -33890,7 +33702,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>北方邦</t>
+          <t>卡纳塔克邦</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -33899,22 +33711,22 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>52.73</v>
+        <v>48.21</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>55.24</v>
+        <v>47.75</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>57.93</v>
+        <v>47.19</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>60.65</v>
+        <v>46.76</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>63.48</v>
+        <v>46.76</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>46.87</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
@@ -33936,7 +33748,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>卡纳塔克邦</t>
+          <t>古吉拉特邦</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -33945,22 +33757,22 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>48.21</v>
+        <v>40.64</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>47.75</v>
+        <v>41.01</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>47.19</v>
+        <v>41.44</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>46.76</v>
+        <v>44.05</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>46.76</v>
+        <v>48.6</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>46.87</v>
+        <v>53.13</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -33982,7 +33794,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>古吉拉特邦</t>
+          <t>安得拉邦</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -33991,22 +33803,22 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>40.64</v>
+        <v>41.96</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>41.01</v>
+        <v>41.67</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="H183" s="3" t="n">
-        <v>44.05</v>
-      </c>
-      <c r="I183" s="3" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="J183" s="3" t="n">
-        <v>53.13</v>
+        <v>40.72</v>
+      </c>
+      <c r="H183" s="4" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="I183" s="4" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="J183" s="4" t="n">
+        <v>39.73</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
@@ -34028,7 +33840,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>安得拉邦</t>
+          <t>泰米尔纳德邦</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -34037,22 +33849,22 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>41.96</v>
+        <v>44.58</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>41.67</v>
+        <v>42.25</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>40.72</v>
+        <v>40.09</v>
       </c>
       <c r="H184" s="4" t="n">
-        <v>39.63</v>
+        <v>38.3</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>39.67</v>
+        <v>36.83</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>39.73</v>
+        <v>35.75</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -34074,7 +33886,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>泰米尔纳德邦</t>
+          <t>马哈拉施特拉邦</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -34083,22 +33895,22 @@
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>44.58</v>
+        <v>45.36</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>42.25</v>
+        <v>46.31</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="H185" s="4" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I185" s="4" t="n">
-        <v>36.83</v>
-      </c>
-      <c r="J185" s="4" t="n">
-        <v>35.75</v>
+        <v>47.83</v>
+      </c>
+      <c r="H185" s="3" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>54.14</v>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
@@ -34110,17 +33922,17 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>马哈拉施特拉邦</t>
+          <t>南马托格罗索州</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -34129,22 +33941,22 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>45.36</v>
+        <v>66.87</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>46.31</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>47.83</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>49.48</v>
+        <v>66.88</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>51.5</v>
+        <v>66.38</v>
       </c>
       <c r="J186" s="3" t="n">
-        <v>54.14</v>
+        <v>65.77</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -34166,7 +33978,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>南马托格罗索州</t>
+          <t>圣保罗州</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -34175,22 +33987,22 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>66.87</v>
+        <v>71.08</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>66.76000000000001</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>67.04000000000001</v>
+        <v>74.34</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>66.88</v>
+        <v>74.88</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>66.38</v>
+        <v>75.08</v>
       </c>
       <c r="J187" s="3" t="n">
-        <v>65.77</v>
+        <v>72.13</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
@@ -34212,7 +34024,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>圣保罗州</t>
+          <t>巴拉那州</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -34221,22 +34033,22 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>71.08</v>
+        <v>62.72</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>72.68000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>74.34</v>
+        <v>65.09</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>74.88</v>
+        <v>65.28</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>75.08</v>
+        <v>64.83</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>72.13</v>
+        <v>63.76</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -34258,7 +34070,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>巴拉那州</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -34267,22 +34079,22 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>62.72</v>
+        <v>49.81</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>64.16</v>
+        <v>49.63</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>65.09</v>
+        <v>50.35</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>65.28</v>
+        <v>51.91</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>64.83</v>
+        <v>53.56</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>63.76</v>
+        <v>55.06</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
@@ -34304,7 +34116,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -34313,22 +34125,22 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>49.81</v>
+        <v>58.04</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>49.63</v>
+        <v>57.15</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>50.35</v>
+        <v>57.04</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>51.91</v>
+        <v>57.06</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>53.56</v>
+        <v>57.45</v>
       </c>
       <c r="J190" s="3" t="n">
-        <v>55.06</v>
+        <v>57.84</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -34350,7 +34162,7 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -34359,22 +34171,22 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>58.04</v>
+        <v>55.48</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>57.15</v>
+        <v>55.15</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>57.04</v>
+        <v>55.06</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>57.06</v>
+        <v>55.26</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>57.45</v>
+        <v>56.02</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>57.84</v>
+        <v>57.1</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
@@ -34386,41 +34198,41 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>甘蔗</t>
+          <t>菜籽</t>
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>55.48</v>
+        <v>47.66</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>55.15</v>
+        <v>48.49</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>55.06</v>
+        <v>49.01</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>55.26</v>
+        <v>49.23</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>56.02</v>
+        <v>49.83</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>57.1</v>
+        <v>50.2</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -34442,7 +34254,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -34451,22 +34263,22 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>47.66</v>
+        <v>47.72</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>48.49</v>
+        <v>48.24</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>49.01</v>
+        <v>48.15</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>49.23</v>
+        <v>48.16</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>49.83</v>
+        <v>48.32</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>50.2</v>
+        <v>47.72</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
@@ -34488,7 +34300,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -34497,22 +34309,22 @@
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>47.72</v>
+        <v>59.81</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>48.24</v>
+        <v>60.07</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>48.15</v>
+        <v>60.56</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>48.16</v>
+        <v>60.94</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>48.32</v>
+        <v>61.1</v>
       </c>
       <c r="J194" s="3" t="n">
-        <v>47.72</v>
+        <v>61.65</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -34534,7 +34346,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -34543,22 +34355,22 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>59.81</v>
+        <v>44.06</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>60.07</v>
+        <v>46.03</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>60.56</v>
+        <v>47.15</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>60.94</v>
+        <v>48.74</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>61.1</v>
+        <v>50.09</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>61.65</v>
+        <v>50.57</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
@@ -34580,7 +34392,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -34589,22 +34401,22 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>44.06</v>
+        <v>63.94</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>46.03</v>
+        <v>64.02</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>47.15</v>
+        <v>64.88</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>48.74</v>
+        <v>64.98</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>50.09</v>
+        <v>65.19</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>50.57</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -34626,7 +34438,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -34635,22 +34447,22 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>63.94</v>
+        <v>58.59</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>64.02</v>
+        <v>58.42</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>64.88</v>
+        <v>58.65</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>64.98</v>
+        <v>59.2</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>65.19</v>
+        <v>58.67</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>64.56999999999999</v>
+        <v>59.19</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
@@ -34672,7 +34484,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -34681,22 +34493,22 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>58.59</v>
+        <v>64.98</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>58.42</v>
+        <v>64.89</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>58.65</v>
+        <v>64.22</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>59.2</v>
+        <v>62.95</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>58.67</v>
+        <v>60.95</v>
       </c>
       <c r="J198" s="3" t="n">
-        <v>59.19</v>
+        <v>59.96</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -34718,7 +34530,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -34727,22 +34539,22 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>64.98</v>
+        <v>56.17</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>64.89</v>
+        <v>58.15</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>64.22</v>
+        <v>60</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>62.95</v>
+        <v>60.89</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>60.95</v>
+        <v>60.18</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>59.96</v>
+        <v>58.1</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
@@ -34764,7 +34576,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -34773,22 +34585,22 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>56.17</v>
+        <v>60.55</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>58.15</v>
+        <v>63.26</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>60</v>
+        <v>62.8</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>60.89</v>
+        <v>61.4</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>60.18</v>
+        <v>58.65</v>
       </c>
       <c r="J200" s="3" t="n">
-        <v>58.1</v>
+        <v>56.82</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -34800,17 +34612,17 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -34819,22 +34631,22 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>60.55</v>
+        <v>57.76</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>63.26</v>
+        <v>57.25</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>62.8</v>
+        <v>57.03</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>61.4</v>
+        <v>56.82</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>58.65</v>
+        <v>55.77</v>
       </c>
       <c r="J201" s="3" t="n">
-        <v>56.82</v>
+        <v>55.41</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
@@ -34856,7 +34668,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Alberta</t>
+          <t>Manitoba</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -34865,22 +34677,22 @@
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>57.76</v>
+        <v>57.64</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>57.25</v>
+        <v>60.29</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>57.03</v>
+        <v>60.98</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>56.82</v>
+        <v>58.92</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>55.77</v>
+        <v>55.38</v>
       </c>
       <c r="J202" s="3" t="n">
-        <v>55.41</v>
+        <v>53.26</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -34902,7 +34714,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>Saskatchewan</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -34911,22 +34723,22 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>57.64</v>
+        <v>65.8</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>60.29</v>
+        <v>65.3</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>60.98</v>
+        <v>63.5</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>58.92</v>
+        <v>60.47</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>55.38</v>
+        <v>56.64</v>
       </c>
       <c r="J203" s="3" t="n">
-        <v>53.26</v>
+        <v>54.85</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
@@ -34938,17 +34750,17 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Saskatchewan</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -34957,22 +34769,22 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>65.8</v>
+        <v>63.05</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>65.3</v>
+        <v>63.68</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>63.5</v>
+        <v>64.75</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>60.47</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>56.64</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="J204" s="3" t="n">
-        <v>54.85</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -34994,7 +34806,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -35003,22 +34815,22 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>63.05</v>
+        <v>44.71</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>63.68</v>
+        <v>45.79</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>64.75</v>
+        <v>48.32</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>65.84999999999999</v>
+        <v>51.15</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>68.54000000000001</v>
+        <v>53.43</v>
       </c>
       <c r="J205" s="3" t="n">
-        <v>72.93000000000001</v>
+        <v>54.92</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
@@ -35040,7 +34852,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -35049,22 +34861,22 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>44.71</v>
+        <v>58.62</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>45.79</v>
+        <v>58.49</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>48.32</v>
+        <v>58.78</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>51.15</v>
+        <v>59.96</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>53.43</v>
+        <v>62.39</v>
       </c>
       <c r="J206" s="3" t="n">
-        <v>54.92</v>
+        <v>66.28</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -35086,7 +34898,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -35095,22 +34907,22 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>58.62</v>
+        <v>52.32</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>58.49</v>
+        <v>55.05</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>58.78</v>
+        <v>58.13</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>59.96</v>
+        <v>61.15</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>62.39</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="J207" s="3" t="n">
-        <v>66.28</v>
+        <v>66.81</v>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
@@ -35132,7 +34944,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -35141,22 +34953,22 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>52.32</v>
+        <v>40.35</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>55.05</v>
+        <v>41.34</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>58.13</v>
+        <v>42.5</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>61.15</v>
+        <v>43.16</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>64.06999999999999</v>
+        <v>43.5</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>66.81</v>
+        <v>44.2</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -35168,17 +34980,17 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Czech</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -35186,23 +34998,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E209" s="3" t="n">
-        <v>40.35</v>
-      </c>
-      <c r="F209" s="3" t="n">
-        <v>41.34</v>
-      </c>
-      <c r="G209" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="H209" s="3" t="n">
-        <v>43.16</v>
-      </c>
-      <c r="I209" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="J209" s="3" t="n">
-        <v>44.2</v>
+      <c r="E209" s="4" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="F209" s="4" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="G209" s="4" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="H209" s="4" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="I209" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="J209" s="4" t="n">
+        <v>36.46</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
@@ -35219,12 +35031,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Czech</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -35232,23 +35044,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E210" s="4" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="F210" s="4" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="G210" s="4" t="n">
-        <v>35.43</v>
-      </c>
-      <c r="H210" s="4" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I210" s="4" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="J210" s="4" t="n">
-        <v>36.46</v>
+      <c r="E210" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>41.96</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -35265,12 +35077,12 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -35278,23 +35090,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E211" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="F211" s="3" t="n">
-        <v>41.26</v>
-      </c>
-      <c r="G211" s="3" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="H211" s="3" t="n">
-        <v>41.28</v>
-      </c>
-      <c r="I211" s="3" t="n">
-        <v>40.77</v>
-      </c>
-      <c r="J211" s="3" t="n">
-        <v>41.96</v>
+      <c r="E211" s="5" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="H211" s="4" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="I211" s="4" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="J211" s="4" t="n">
+        <v>24.39</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
@@ -35311,12 +35123,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -35324,23 +35136,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E212" s="5" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F212" s="5" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G212" s="5" t="n">
-        <v>19.78</v>
+      <c r="E212" s="4" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="F212" s="4" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="G212" s="4" t="n">
+        <v>37.76</v>
       </c>
       <c r="H212" s="4" t="n">
-        <v>22.18</v>
-      </c>
-      <c r="I212" s="4" t="n">
-        <v>24.56</v>
-      </c>
-      <c r="J212" s="4" t="n">
-        <v>24.39</v>
+        <v>39.55</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="J212" s="3" t="n">
+        <v>41.25</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -35357,12 +35169,12 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -35371,22 +35183,22 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>35.95</v>
+        <v>21.74</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>36.51</v>
+        <v>20.98</v>
       </c>
       <c r="G213" s="4" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="H213" s="4" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="I213" s="3" t="n">
-        <v>40.92</v>
-      </c>
-      <c r="J213" s="3" t="n">
-        <v>41.25</v>
+        <v>20.26</v>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="J213" s="5" t="n">
+        <v>19.99</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
@@ -35403,12 +35215,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -35416,23 +35228,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E214" s="4" t="n">
-        <v>21.74</v>
-      </c>
-      <c r="F214" s="4" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="G214" s="4" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="H214" s="5" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I214" s="5" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="J214" s="5" t="n">
-        <v>19.99</v>
+      <c r="E214" s="3" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H214" s="3" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="I214" s="3" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>49.78</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -35449,12 +35261,12 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -35463,22 +35275,22 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>56.78</v>
+        <v>53.79</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>56.64</v>
+        <v>53.77</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>56.6</v>
+        <v>54.28</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>56.15</v>
+        <v>54.22</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>52.85</v>
+        <v>52.98</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>49.78</v>
+        <v>52.14</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
@@ -35490,17 +35302,17 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -35509,22 +35321,22 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>53.79</v>
+        <v>57.98</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>53.77</v>
+        <v>59.01</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>54.28</v>
+        <v>59.56</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>54.22</v>
+        <v>60.59</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>52.98</v>
+        <v>62.48</v>
       </c>
       <c r="J216" s="3" t="n">
-        <v>52.14</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -35536,17 +35348,17 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>South Australia</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -35555,22 +35367,22 @@
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>45.71</v>
+        <v>64.86</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>43.02</v>
+        <v>67.39</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>40.85</v>
-      </c>
-      <c r="H217" s="4" t="n">
-        <v>39.26</v>
-      </c>
-      <c r="I217" s="4" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="J217" s="4" t="n">
-        <v>36.71</v>
+        <v>69.13</v>
+      </c>
+      <c r="H217" s="3" t="n">
+        <v>70.54000000000001</v>
+      </c>
+      <c r="I217" s="3" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="J217" s="3" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
@@ -35592,7 +35404,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>New South Wales</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -35601,22 +35413,22 @@
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>57.98</v>
+        <v>57.29</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>59.01</v>
+        <v>59.38</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>59.56</v>
+        <v>60.71</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>60.59</v>
+        <v>61.91</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>62.48</v>
+        <v>63.78</v>
       </c>
       <c r="J218" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -35638,7 +35450,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>South Australia</t>
+          <t>Western Australia</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -35647,22 +35459,22 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>64.86</v>
+        <v>60.29</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>67.39</v>
+        <v>59.48</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>69.13</v>
+        <v>59.06</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>70.54000000000001</v>
+        <v>59.37</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>72.45</v>
+        <v>60.72</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>62.82</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
@@ -35674,41 +35486,41 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Cherkaska</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>菜籽</t>
+          <t>葵籽</t>
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>57.29</v>
+        <v>55.24</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>59.38</v>
+        <v>51.66</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>60.71</v>
+        <v>47.42</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>61.91</v>
+        <v>43.5</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="J220" s="3" t="n">
-        <v>67.77</v>
+        <v>40.48</v>
+      </c>
+      <c r="J220" s="4" t="n">
+        <v>39.56</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -35720,41 +35532,41 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Western Australia</t>
+          <t>Chivnivska</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>菜籽</t>
+          <t>葵籽</t>
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>60.29</v>
+        <v>59.77</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>59.48</v>
+        <v>60.3</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>59.06</v>
+        <v>60</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>59.37</v>
+        <v>58.88</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>60.72</v>
+        <v>57.05</v>
       </c>
       <c r="J221" s="3" t="n">
-        <v>62.82</v>
+        <v>54.21</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
@@ -35776,7 +35588,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Cherkaska</t>
+          <t>Dnipropetrovska</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -35785,22 +35597,22 @@
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>55.24</v>
+        <v>57.21</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>51.66</v>
+        <v>53.37</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>47.42</v>
+        <v>49.9</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>43.5</v>
+        <v>46.93</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="J222" s="4" t="n">
-        <v>39.56</v>
+        <v>43.85</v>
+      </c>
+      <c r="J222" s="3" t="n">
+        <v>41.19</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -35822,7 +35634,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Chivnivska</t>
+          <t>Donetsk</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -35831,22 +35643,22 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>59.77</v>
+        <v>48.18</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>60.3</v>
+        <v>45.08</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H223" s="3" t="n">
-        <v>58.88</v>
-      </c>
-      <c r="I223" s="3" t="n">
-        <v>57.05</v>
-      </c>
-      <c r="J223" s="3" t="n">
-        <v>54.21</v>
+        <v>41.96</v>
+      </c>
+      <c r="H223" s="4" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="I223" s="4" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="J223" s="4" t="n">
+        <v>36.11</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
@@ -35868,7 +35680,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Dnipropetrovska</t>
+          <t>Kharkivska</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -35877,22 +35689,22 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>57.21</v>
+        <v>62.47</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>53.37</v>
+        <v>59.33</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>49.9</v>
+        <v>55.3</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>46.93</v>
+        <v>51.55</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>43.85</v>
+        <v>48.08</v>
       </c>
       <c r="J224" s="3" t="n">
-        <v>41.19</v>
+        <v>45.76</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -35914,7 +35726,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Donetsk</t>
+          <t>Khersonska</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -35922,23 +35734,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E225" s="3" t="n">
-        <v>48.18</v>
-      </c>
-      <c r="F225" s="3" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="G225" s="3" t="n">
-        <v>41.96</v>
+      <c r="E225" s="4" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F225" s="4" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="G225" s="4" t="n">
+        <v>23.03</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="I225" s="4" t="n">
-        <v>37.39</v>
-      </c>
-      <c r="J225" s="4" t="n">
-        <v>36.11</v>
+        <v>20.92</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="J225" s="5" t="n">
+        <v>17.79</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
@@ -35960,7 +35772,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Kharkivska</t>
+          <t>Kirovogradska</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -35969,22 +35781,22 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>62.47</v>
+        <v>52.49</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>59.33</v>
+        <v>49.28</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>55.3</v>
+        <v>47.07</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>51.55</v>
+        <v>45.23</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="J226" s="3" t="n">
-        <v>45.76</v>
+        <v>42.56</v>
+      </c>
+      <c r="J226" s="4" t="n">
+        <v>39.28</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -36006,7 +35818,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Khersonska</t>
+          <t>Kirovohradska</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -36014,23 +35826,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E227" s="4" t="n">
-        <v>27.67</v>
-      </c>
-      <c r="F227" s="4" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="G227" s="4" t="n">
-        <v>23.03</v>
-      </c>
-      <c r="H227" s="4" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="I227" s="5" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="J227" s="5" t="n">
-        <v>17.79</v>
+      <c r="E227" s="3" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="H227" s="3" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="I227" s="3" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="J227" s="4" t="n">
+        <v>39.28</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
@@ -36052,7 +35864,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Kirovogradska</t>
+          <t>Luhanska</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -36061,22 +35873,22 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>52.49</v>
+        <v>59.14</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>49.28</v>
+        <v>58.16</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>47.07</v>
+        <v>54.93</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>45.23</v>
+        <v>51.78</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>42.56</v>
-      </c>
-      <c r="J228" s="4" t="n">
-        <v>39.28</v>
+        <v>48.69</v>
+      </c>
+      <c r="J228" s="3" t="n">
+        <v>46.93</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -36098,7 +35910,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Kirovohradska</t>
+          <t>Odeska</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -36107,22 +35919,22 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="F229" s="3" t="n">
-        <v>49.28</v>
-      </c>
-      <c r="G229" s="3" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="H229" s="3" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I229" s="3" t="n">
-        <v>42.56</v>
+        <v>41.49</v>
+      </c>
+      <c r="F229" s="4" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="G229" s="4" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="H229" s="4" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="I229" s="4" t="n">
+        <v>30.34</v>
       </c>
       <c r="J229" s="4" t="n">
-        <v>39.28</v>
+        <v>29.37</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
@@ -36144,7 +35956,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Luhanska</t>
+          <t>Poltavska</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -36153,22 +35965,22 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>59.14</v>
+        <v>66.58</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>58.16</v>
+        <v>63.63</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>54.93</v>
+        <v>59.84</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>51.78</v>
+        <v>54.8</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>48.69</v>
+        <v>49.4</v>
       </c>
       <c r="J230" s="3" t="n">
-        <v>46.93</v>
+        <v>45.77</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -36190,7 +36002,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Odeska</t>
+          <t>Sumy</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -36199,22 +36011,22 @@
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>41.49</v>
-      </c>
-      <c r="F231" s="4" t="n">
-        <v>37.84</v>
-      </c>
-      <c r="G231" s="4" t="n">
-        <v>34.86</v>
-      </c>
-      <c r="H231" s="4" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="I231" s="4" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="J231" s="4" t="n">
-        <v>29.37</v>
+        <v>72.15000000000001</v>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="I231" s="3" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="J231" s="3" t="n">
+        <v>51.94</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
@@ -36236,7 +36048,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Poltavska</t>
+          <t>Vinnitsa</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -36245,22 +36057,22 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>66.58</v>
+        <v>60.56</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>63.63</v>
+        <v>58.68</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>59.84</v>
+        <v>56.43</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>54.8</v>
+        <v>53.48</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="J232" s="3" t="n">
-        <v>45.77</v>
+        <v>47.09</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -36282,7 +36094,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Sumy</t>
+          <t>Zaporizka</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -36290,23 +36102,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E233" s="3" t="n">
-        <v>72.15000000000001</v>
-      </c>
-      <c r="F233" s="3" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="G233" s="3" t="n">
-        <v>66.28</v>
-      </c>
-      <c r="H233" s="3" t="n">
-        <v>60.91</v>
-      </c>
-      <c r="I233" s="3" t="n">
-        <v>56.18</v>
-      </c>
-      <c r="J233" s="3" t="n">
-        <v>51.94</v>
+      <c r="E233" s="4" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="F233" s="4" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="G233" s="4" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="H233" s="4" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="I233" s="4" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="J233" s="4" t="n">
+        <v>24.39</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
@@ -36318,17 +36130,17 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>俄罗斯</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Vinnitsa</t>
+          <t>中央</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -36337,22 +36149,22 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>60.56</v>
+        <v>74.36</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>58.68</v>
+        <v>72.67</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>56.43</v>
+        <v>69.34</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>53.48</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>49.3</v>
+        <v>60.46</v>
       </c>
       <c r="J234" s="3" t="n">
-        <v>47.09</v>
+        <v>56.15</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -36364,17 +36176,17 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>俄罗斯</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Zaporizka</t>
+          <t>伏尔加</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -36382,23 +36194,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E235" s="4" t="n">
-        <v>34.59</v>
-      </c>
-      <c r="F235" s="4" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="G235" s="4" t="n">
-        <v>29.15</v>
-      </c>
-      <c r="H235" s="4" t="n">
-        <v>27.39</v>
-      </c>
-      <c r="I235" s="4" t="n">
-        <v>25.54</v>
-      </c>
-      <c r="J235" s="4" t="n">
-        <v>24.39</v>
+      <c r="E235" s="3" t="n">
+        <v>73.70999999999999</v>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="G235" s="3" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>63.27</v>
+      </c>
+      <c r="I235" s="3" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="J235" s="3" t="n">
+        <v>54.53</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
@@ -36420,7 +36232,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>中央</t>
+          <t>北高加索</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -36429,22 +36241,22 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>73.73999999999999</v>
+        <v>60.97</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>72.04000000000001</v>
+        <v>60.68</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>68.7</v>
+        <v>60.46</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>64.48999999999999</v>
+        <v>59.47</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>59.94</v>
+        <v>57.91</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>55.71</v>
+        <v>55.97</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -36466,7 +36278,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>伏尔加</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -36475,22 +36287,22 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>73.73</v>
+        <v>51.47</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>71.69</v>
+        <v>49.86</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>67.95999999999999</v>
+        <v>47.82</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>63.4</v>
+        <v>45.6</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>59.68</v>
+        <v>44.03</v>
       </c>
       <c r="J237" s="3" t="n">
-        <v>54.65</v>
+        <v>42.31</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
@@ -36502,17 +36314,17 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>北高加索</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -36521,22 +36333,22 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>60.4</v>
+        <v>50.2</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>60.42</v>
+        <v>47.37</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>60.3</v>
+        <v>45.03</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>59.42</v>
+        <v>43.7</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>57.94</v>
+        <v>42.14</v>
       </c>
       <c r="J238" s="3" t="n">
-        <v>56.07</v>
+        <v>40.77</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -36548,17 +36360,17 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>俄罗斯</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -36566,23 +36378,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E239" s="3" t="n">
-        <v>55.13</v>
-      </c>
-      <c r="F239" s="3" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="G239" s="3" t="n">
-        <v>52.12</v>
-      </c>
-      <c r="H239" s="3" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="I239" s="3" t="n">
-        <v>48.55</v>
-      </c>
-      <c r="J239" s="3" t="n">
-        <v>47.53</v>
+      <c r="E239" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F239" s="5" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="G239" s="5" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="H239" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I239" s="4" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="J239" s="4" t="n">
+        <v>24.02</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
@@ -36599,12 +36411,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -36612,23 +36424,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E240" s="3" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="F240" s="3" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="G240" s="3" t="n">
-        <v>45.03</v>
-      </c>
-      <c r="H240" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="I240" s="3" t="n">
-        <v>42.14</v>
-      </c>
-      <c r="J240" s="3" t="n">
-        <v>40.77</v>
+      <c r="E240" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F240" s="4" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="G240" s="4" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="H240" s="5" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="J240" s="5" t="n">
+        <v>19.82</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -36645,12 +36457,12 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -36658,23 +36470,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E241" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F241" s="5" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="G241" s="5" t="n">
-        <v>19.74</v>
+      <c r="E241" s="3" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="G241" s="3" t="n">
+        <v>40.05</v>
       </c>
       <c r="H241" s="4" t="n">
-        <v>22</v>
+        <v>38.45</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>24.25</v>
+        <v>37.07</v>
       </c>
       <c r="J241" s="4" t="n">
-        <v>24.02</v>
+        <v>35.97</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
@@ -36691,12 +36503,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -36705,22 +36517,22 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F242" s="4" t="n">
-        <v>20.73</v>
-      </c>
-      <c r="G242" s="4" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="H242" s="5" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="I242" s="5" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="J242" s="5" t="n">
-        <v>19.82</v>
+        <v>39.85</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="I242" s="3" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="J242" s="4" t="n">
+        <v>39.21</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -36732,17 +36544,17 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -36751,22 +36563,22 @@
         </is>
       </c>
       <c r="E243" s="3" t="n">
-        <v>45.05</v>
+        <v>55.63</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>42.29</v>
+        <v>57.47</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>40.05</v>
-      </c>
-      <c r="H243" s="4" t="n">
-        <v>38.45</v>
-      </c>
-      <c r="I243" s="4" t="n">
-        <v>37.07</v>
-      </c>
-      <c r="J243" s="4" t="n">
-        <v>35.97</v>
+        <v>58.33</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="I243" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="J243" s="3" t="n">
+        <v>65.56999999999999</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
@@ -36778,17 +36590,17 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>La Pampa</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -36796,23 +36608,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E244" s="4" t="n">
-        <v>39.85</v>
+      <c r="E244" s="3" t="n">
+        <v>55.42</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>40.89</v>
+        <v>57.63</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>41.15</v>
+        <v>58.85</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>41.31</v>
+        <v>58.79</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>41.21</v>
-      </c>
-      <c r="J244" s="4" t="n">
-        <v>39.21</v>
+        <v>59.27</v>
+      </c>
+      <c r="J244" s="3" t="n">
+        <v>63.36</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -36834,7 +36646,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -36843,22 +36655,22 @@
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>55.63</v>
+        <v>62.89</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>57.47</v>
+        <v>66.58</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>58.33</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>58.94</v>
+        <v>71.84</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>60.2</v>
+        <v>71.95</v>
       </c>
       <c r="J245" s="3" t="n">
-        <v>65.56999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
@@ -36870,41 +36682,41 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>葵籽</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="n">
-        <v>55.42</v>
-      </c>
-      <c r="F246" s="3" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="G246" s="3" t="n">
-        <v>58.85</v>
-      </c>
-      <c r="H246" s="3" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I246" s="3" t="n">
-        <v>59.27</v>
-      </c>
-      <c r="J246" s="3" t="n">
-        <v>63.36</v>
+          <t>高粱</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F246" s="4" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="G246" s="4" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="H246" s="4" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="I246" s="4" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="J246" s="4" t="n">
+        <v>24.75</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -36916,41 +36728,41 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Bauchi</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>葵籽</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="n">
-        <v>62.89</v>
-      </c>
-      <c r="F247" s="3" t="n">
-        <v>66.58</v>
-      </c>
-      <c r="G247" s="3" t="n">
-        <v>69.76000000000001</v>
-      </c>
-      <c r="H247" s="3" t="n">
-        <v>71.84</v>
-      </c>
-      <c r="I247" s="3" t="n">
-        <v>71.95</v>
-      </c>
-      <c r="J247" s="3" t="n">
-        <v>73.62</v>
+          <t>高粱</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="F247" s="4" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="G247" s="4" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="H247" s="4" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="I247" s="4" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="J247" s="4" t="n">
+        <v>39.44</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
@@ -36972,7 +36784,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -36980,23 +36792,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E248" s="4" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="F248" s="4" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="H248" s="4" t="n">
-        <v>24.84</v>
-      </c>
-      <c r="I248" s="4" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="J248" s="4" t="n">
-        <v>24.75</v>
+      <c r="E248" s="3" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I248" s="3" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="J248" s="3" t="n">
+        <v>57.58</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -37018,7 +36830,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Bauchi</t>
+          <t>Gombe</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -37027,22 +36839,22 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>32.74</v>
+        <v>27.88</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>32.68</v>
+        <v>27.56</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>33.7</v>
+        <v>27.77</v>
       </c>
       <c r="H249" s="4" t="n">
-        <v>35.12</v>
+        <v>27.53</v>
       </c>
       <c r="I249" s="4" t="n">
-        <v>37.83</v>
+        <v>28.49</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>39.44</v>
+        <v>28.26</v>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
@@ -37064,7 +36876,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Jigawa</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -37073,22 +36885,22 @@
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>54.84</v>
+        <v>50.76</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>52.99</v>
+        <v>51.76</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>52.12</v>
+        <v>54.52</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>52.8</v>
+        <v>57.43</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>55.72</v>
+        <v>60.52</v>
       </c>
       <c r="J250" s="3" t="n">
-        <v>57.58</v>
+        <v>63.55</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -37110,7 +36922,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Gombe</t>
+          <t>Kaduna</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -37119,22 +36931,22 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>27.88</v>
+        <v>33.65</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>27.56</v>
+        <v>35.36</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>27.77</v>
-      </c>
-      <c r="H251" s="4" t="n">
-        <v>27.53</v>
-      </c>
-      <c r="I251" s="4" t="n">
-        <v>28.49</v>
-      </c>
-      <c r="J251" s="4" t="n">
-        <v>28.26</v>
+        <v>37.83</v>
+      </c>
+      <c r="H251" s="3" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="I251" s="3" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="J251" s="3" t="n">
+        <v>44.43</v>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
@@ -37156,7 +36968,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Jigawa</t>
+          <t>Kano</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -37165,22 +36977,22 @@
         </is>
       </c>
       <c r="E252" s="3" t="n">
-        <v>50.76</v>
+        <v>46.69</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>51.76</v>
+        <v>48.28</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>54.52</v>
+        <v>50.48</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>57.43</v>
+        <v>52.21</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>60.52</v>
+        <v>54.61</v>
       </c>
       <c r="J252" s="3" t="n">
-        <v>63.55</v>
+        <v>58.71</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -37202,7 +37014,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Kaduna</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -37210,23 +37022,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E253" s="4" t="n">
-        <v>33.65</v>
-      </c>
-      <c r="F253" s="4" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="G253" s="4" t="n">
-        <v>37.83</v>
+      <c r="E253" s="3" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="G253" s="3" t="n">
+        <v>62.42</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>40.57</v>
+        <v>63.93</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>43.79</v>
+        <v>67.09</v>
       </c>
       <c r="J253" s="3" t="n">
-        <v>44.43</v>
+        <v>70.06</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
@@ -37248,7 +37060,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Kano</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -37256,23 +37068,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E254" s="3" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="F254" s="3" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="G254" s="3" t="n">
-        <v>50.48</v>
-      </c>
-      <c r="H254" s="3" t="n">
-        <v>52.21</v>
-      </c>
-      <c r="I254" s="3" t="n">
-        <v>54.61</v>
+      <c r="E254" s="4" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="F254" s="4" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="G254" s="4" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H254" s="4" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="I254" s="4" t="n">
+        <v>39.96</v>
       </c>
       <c r="J254" s="3" t="n">
-        <v>58.71</v>
+        <v>40.04</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -37294,7 +37106,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -37302,23 +37114,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E255" s="3" t="n">
-        <v>60.55</v>
-      </c>
-      <c r="F255" s="3" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="G255" s="3" t="n">
-        <v>62.42</v>
-      </c>
-      <c r="H255" s="3" t="n">
-        <v>63.93</v>
-      </c>
-      <c r="I255" s="3" t="n">
-        <v>67.09</v>
-      </c>
-      <c r="J255" s="3" t="n">
-        <v>70.06</v>
+      <c r="E255" s="4" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="F255" s="4" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G255" s="4" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="H255" s="4" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="I255" s="4" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="J255" s="4" t="n">
+        <v>32.51</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
@@ -37340,7 +37152,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Plateau</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -37349,22 +37161,22 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>35.15</v>
+        <v>37.1</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>36.65</v>
+        <v>37.43</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>38.33</v>
+        <v>38.4</v>
       </c>
       <c r="H256" s="4" t="n">
-        <v>38.99</v>
-      </c>
-      <c r="I256" s="4" t="n">
-        <v>39.96</v>
+        <v>39.82</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>41.16</v>
       </c>
       <c r="J256" s="3" t="n">
-        <v>40.04</v>
+        <v>41.42</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -37386,7 +37198,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -37394,23 +37206,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E257" s="4" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="F257" s="4" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G257" s="4" t="n">
-        <v>27.35</v>
-      </c>
-      <c r="H257" s="4" t="n">
-        <v>28.89</v>
-      </c>
-      <c r="I257" s="4" t="n">
-        <v>30.75</v>
-      </c>
-      <c r="J257" s="4" t="n">
-        <v>32.51</v>
+      <c r="E257" s="3" t="n">
+        <v>61.72</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="G257" s="3" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="H257" s="3" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="I257" s="3" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="J257" s="3" t="n">
+        <v>68.08</v>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
@@ -37432,7 +37244,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Plateau</t>
+          <t>Taraba</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -37441,22 +37253,22 @@
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>37.1</v>
+        <v>33.6</v>
       </c>
       <c r="F258" s="4" t="n">
-        <v>37.43</v>
+        <v>34.39</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>38.4</v>
+        <v>35.28</v>
       </c>
       <c r="H258" s="4" t="n">
-        <v>39.82</v>
-      </c>
-      <c r="I258" s="3" t="n">
-        <v>41.16</v>
-      </c>
-      <c r="J258" s="3" t="n">
-        <v>41.42</v>
+        <v>36.91</v>
+      </c>
+      <c r="I258" s="4" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="J258" s="4" t="n">
+        <v>39.41</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -37478,7 +37290,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Yobe</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -37487,22 +37299,22 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>61.72</v>
+        <v>46</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>61.97</v>
+        <v>44.87</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>62.11</v>
+        <v>45.24</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>62.7</v>
+        <v>46.87</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>50.48</v>
       </c>
       <c r="J259" s="3" t="n">
-        <v>68.08</v>
+        <v>52.92</v>
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
@@ -37524,7 +37336,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Taraba</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -37532,23 +37344,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E260" s="4" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="F260" s="4" t="n">
-        <v>34.39</v>
-      </c>
-      <c r="G260" s="4" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="H260" s="4" t="n">
-        <v>36.91</v>
-      </c>
-      <c r="I260" s="4" t="n">
-        <v>38.83</v>
-      </c>
-      <c r="J260" s="4" t="n">
-        <v>39.41</v>
+      <c r="E260" s="3" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="G260" s="3" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="H260" s="3" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="I260" s="3" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="J260" s="3" t="n">
+        <v>60.03</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -37560,17 +37372,17 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Yobe</t>
+          <t>圣保罗州</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -37579,22 +37391,22 @@
         </is>
       </c>
       <c r="E261" s="3" t="n">
-        <v>46</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F261" s="3" t="n">
-        <v>44.87</v>
+        <v>72.16</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>45.24</v>
+        <v>74.05</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>46.87</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>50.48</v>
+        <v>74.05</v>
       </c>
       <c r="J261" s="3" t="n">
-        <v>52.92</v>
+        <v>70.78</v>
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
@@ -37606,17 +37418,17 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -37625,22 +37437,22 @@
         </is>
       </c>
       <c r="E262" s="3" t="n">
-        <v>49.39</v>
+        <v>50.21</v>
       </c>
       <c r="F262" s="3" t="n">
-        <v>49.73</v>
+        <v>49.97</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>51.06</v>
+        <v>50.63</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>53.01</v>
+        <v>52.04</v>
       </c>
       <c r="I262" s="3" t="n">
-        <v>56.86</v>
+        <v>53.68</v>
       </c>
       <c r="J262" s="3" t="n">
-        <v>60.03</v>
+        <v>55.26</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -37662,7 +37474,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>圣保罗州</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -37671,22 +37483,22 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>57.36</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>72.16</v>
+        <v>56.48</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>74.05</v>
+        <v>56.5</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>74.23999999999999</v>
+        <v>56.85</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>74.05</v>
+        <v>57.56</v>
       </c>
       <c r="J263" s="3" t="n">
-        <v>70.78</v>
+        <v>58.25</v>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
@@ -37708,7 +37520,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -37717,22 +37529,22 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>50.21</v>
+        <v>50.68</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>49.97</v>
+        <v>50.78</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>50.63</v>
+        <v>51.16</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>52.04</v>
+        <v>52.01</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>53.68</v>
+        <v>53.32</v>
       </c>
       <c r="J264" s="3" t="n">
-        <v>55.26</v>
+        <v>55.03</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -37744,17 +37556,17 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -37763,22 +37575,22 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>57.36</v>
+        <v>59.93</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>56.48</v>
+        <v>57.7</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>56.5</v>
+        <v>54.92</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>56.85</v>
+        <v>51.81</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>57.56</v>
+        <v>49.05</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>58.25</v>
+        <v>46.91</v>
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
@@ -37790,17 +37602,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -37808,23 +37620,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E266" s="3" t="n">
-        <v>50.68</v>
-      </c>
-      <c r="F266" s="3" t="n">
-        <v>50.78</v>
-      </c>
-      <c r="G266" s="3" t="n">
-        <v>51.16</v>
-      </c>
-      <c r="H266" s="3" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="I266" s="3" t="n">
-        <v>53.32</v>
-      </c>
-      <c r="J266" s="3" t="n">
-        <v>55.03</v>
+      <c r="E266" s="4" t="n">
+        <v>37.96</v>
+      </c>
+      <c r="F266" s="4" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="G266" s="4" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="H266" s="4" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="I266" s="4" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="J266" s="4" t="n">
+        <v>35.07</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -37832,98 +37644,6 @@
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>美国</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="D267" s="3" t="inlineStr">
-        <is>
-          <t>高粱</t>
-        </is>
-      </c>
-      <c r="E267" s="3" t="n">
-        <v>59.93</v>
-      </c>
-      <c r="F267" s="3" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="G267" s="3" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="H267" s="3" t="n">
-        <v>51.81</v>
-      </c>
-      <c r="I267" s="3" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="J267" s="3" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="K267" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="L267" s="3" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>美国</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>高粱</t>
-        </is>
-      </c>
-      <c r="E268" s="4" t="n">
-        <v>37.96</v>
-      </c>
-      <c r="F268" s="4" t="n">
-        <v>36.27</v>
-      </c>
-      <c r="G268" s="4" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="H268" s="4" t="n">
-        <v>34.92</v>
-      </c>
-      <c r="I268" s="4" t="n">
-        <v>34.75</v>
-      </c>
-      <c r="J268" s="4" t="n">
-        <v>35.07</v>
-      </c>
-      <c r="K268" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="L268" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -27965,22 +27965,22 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>71.95999999999999</v>
+        <v>71.17</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>70.37</v>
+        <v>69.37</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>64.13</v>
+        <v>63.38</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>59.84</v>
+        <v>59.14</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>55.46</v>
+        <v>54.76</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -28057,22 +28057,22 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>73.41</v>
+        <v>74.34</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>71.25</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>67.5</v>
+        <v>69.05</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>62.73</v>
+        <v>64.38</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>59.12</v>
+        <v>60.75</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>54.32</v>
+        <v>55.87</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -28103,22 +28103,22 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>60.88</v>
+        <v>62.08</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>61.04</v>
+        <v>62.47</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>61.05</v>
+        <v>62.47</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>60.21</v>
+        <v>61.73</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>58.69</v>
+        <v>60.2</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>57.08</v>
+        <v>58.81</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -28195,22 +28195,22 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>55.09</v>
+        <v>54.83</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>54.59</v>
+        <v>54.41</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>53.88</v>
+        <v>53.6</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>53.62</v>
+        <v>53.31</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>53.23</v>
+        <v>52.99</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>51.34</v>
+        <v>50.93</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -27965,22 +27965,22 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>71.17</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>69.37</v>
+        <v>70.37</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>66.84</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>63.38</v>
+        <v>64.13</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>59.14</v>
+        <v>59.84</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>54.76</v>
+        <v>55.46</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -28057,22 +28057,22 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>74.34</v>
+        <v>73.41</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>72.48999999999999</v>
+        <v>71.25</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>69.05</v>
+        <v>67.5</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>64.38</v>
+        <v>62.73</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>60.75</v>
+        <v>59.12</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>55.87</v>
+        <v>54.32</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -28103,22 +28103,22 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>62.08</v>
+        <v>60.88</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>62.47</v>
+        <v>61.04</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>62.47</v>
+        <v>61.05</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>61.73</v>
+        <v>60.21</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>60.2</v>
+        <v>58.69</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>58.81</v>
+        <v>57.08</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -28195,22 +28195,22 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>54.83</v>
+        <v>55.09</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>54.41</v>
+        <v>54.59</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>53.6</v>
+        <v>53.88</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>53.31</v>
+        <v>53.62</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>52.99</v>
+        <v>53.23</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>50.93</v>
+        <v>51.34</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25604,32 +25604,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W32</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>W36</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -25665,26 +25665,26 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>65.64</v>
+        <v>66.97</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>66.55</v>
+        <v>66.87</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>66.42</v>
+        <v>66.5</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>66.03</v>
+        <v>66.06</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>63.94</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25711,26 +25711,26 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>47.55</v>
+        <v>49.55</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>48.26</v>
+        <v>50.24</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>48.24</v>
+        <v>51.66</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>48.25</v>
+        <v>53.68</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>48.41</v>
+        <v>54.49</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>47.82</v>
+        <v>56.02</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25757,26 +25757,26 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>59.71</v>
+        <v>61.08</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>60.44</v>
+        <v>61.81</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>60.97</v>
+        <v>62.51</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>61.23</v>
+        <v>63.35</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>61.27</v>
+        <v>64.48</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>61.75</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25803,26 +25803,26 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>62.15</v>
+        <v>62.76</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>61.97</v>
+        <v>62.93</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>61.67</v>
+        <v>63.07</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>61.05</v>
+        <v>62.51</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>59.53</v>
+        <v>62.19</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>59.11</v>
+        <v>63.49</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25849,26 +25849,26 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>72.51000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>73.51000000000001</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>74.3</v>
+        <v>72.59</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>72.88</v>
+        <v>67.52</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>69.01000000000001</v>
+        <v>63.53</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25895,26 +25895,26 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>62.72</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>69.58</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>68.45999999999999</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>70.62</v>
+        <v>72.98</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>70.5</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>73.06</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25941,26 +25941,26 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>64.14</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>63.84</v>
+        <v>66.34</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>63.92</v>
+        <v>67.69</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>63.98</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>63.8</v>
+        <v>70.69</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>63.59</v>
+        <v>71.3</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25986,27 +25986,27 @@
           <t>大豆</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>40.67</v>
+      <c r="E9" s="4" t="n">
+        <v>38.7</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>39.43</v>
+        <v>38.23</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>39.31</v>
+        <v>39</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>40.52</v>
+        <v>40.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>42.24</v>
+        <v>42.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>46.23</v>
+        <v>42.08</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26033,26 +26033,26 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>63.46</v>
+        <v>65.08</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>65.11</v>
+        <v>65.98</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>66.02</v>
+        <v>65.97</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>65.25</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>65.33</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>64.03</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26082,23 +26082,23 @@
         <v>49.5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>49.39</v>
+        <v>50.29</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>50.15</v>
+        <v>51.99</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>51.75</v>
+        <v>53.96</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>53.54</v>
+        <v>55.29</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>55.3</v>
+        <v>54.08</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26125,26 +26125,26 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>61.05</v>
+        <v>60.43</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>60.3</v>
+        <v>60.48</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>60.35</v>
+        <v>60.61</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>60.45</v>
+        <v>61.21</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>60.96</v>
+        <v>61.81</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26171,26 +26171,26 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>50.83</v>
+        <v>51.54</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>51.02</v>
+        <v>52.22</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>51.5</v>
+        <v>53.48</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>52.45</v>
+        <v>55.32</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>53.81</v>
+        <v>56.96</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>55.56</v>
+        <v>54.66</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26217,26 +26217,26 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>61.53</v>
+        <v>62.84</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>62.67</v>
+        <v>63.68</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>63.61</v>
+        <v>63.41</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>63.22</v>
+        <v>62.41</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>61.91</v>
+        <v>60.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>60.32</v>
+        <v>59.21</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26263,26 +26263,26 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>60.08</v>
+        <v>61.46</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>61.69</v>
+        <v>62.44</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>62.91</v>
+        <v>63.08</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>63.62</v>
+        <v>63.24</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>63.47</v>
+        <v>60.76</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>60.44</v>
+        <v>58.34</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26309,26 +26309,26 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>60.94</v>
+        <v>61.57</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>62.32</v>
+        <v>62.19</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>63.61</v>
+        <v>60.96</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>63.21</v>
+        <v>59.63</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>62.79</v>
+        <v>57.11</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>60.06</v>
+        <v>54.6</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26355,26 +26355,26 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>53.57</v>
+        <v>52.43</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>52.29</v>
+        <v>49.48</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>49.45</v>
+        <v>45.12</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>45.33</v>
+        <v>43.82</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>44.32</v>
+        <v>44.14</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>44.85</v>
+        <v>45.44</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26401,26 +26401,26 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>60.18</v>
+        <v>58.73</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>57.9</v>
+        <v>56.5</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>55.34</v>
+        <v>52.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>51.34</v>
+        <v>49.61</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>47.63</v>
+        <v>46.18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>45.24</v>
+        <v>44.92</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26447,26 +26447,26 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>62.11</v>
+        <v>63.88</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>63.82</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>65.14</v>
+        <v>65.95</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>65.67</v>
+        <v>66.8</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>66.23999999999999</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>66.55</v>
+        <v>65.77</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26493,26 +26493,26 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>61.25</v>
+        <v>61.97</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>61.86</v>
+        <v>61.72</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>61.49</v>
+        <v>60.22</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>59.75</v>
+        <v>58.5</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>57.64</v>
+        <v>56.35</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>54.94</v>
+        <v>54.91</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26539,26 +26539,26 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>57.69</v>
+        <v>59.28</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>58.81</v>
+        <v>59.51</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>58.73</v>
+        <v>57.95</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>56.72</v>
+        <v>57.11</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>55.27</v>
+        <v>55.7</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>53.47</v>
+        <v>54.43</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26585,26 +26585,26 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>55.66</v>
+        <v>58.54</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>57.48</v>
+        <v>59.89</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>58.3</v>
+        <v>61.37</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>58.91</v>
+        <v>63.92</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>60.15</v>
+        <v>67.78</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>69.56</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26631,26 +26631,26 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>53.7</v>
+        <v>56.97</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>55.96</v>
+        <v>60.11</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>58.69</v>
+        <v>63.57</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.56</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>63.49</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>67.05</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26677,26 +26677,26 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>62.58</v>
+        <v>66.86</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>66.2</v>
+        <v>70.12</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>69.31999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>71.36</v>
+        <v>72.97</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>71.47</v>
+        <v>73.58</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>73.17</v>
+        <v>73.36</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26723,26 +26723,26 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>67.62</v>
+        <v>72.47</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>71.47</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>75.29000000000001</v>
+        <v>78.73</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>77.20999999999999</v>
+        <v>78.81</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>76.73</v>
+        <v>78.45</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>77.87</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26769,26 +26769,26 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>71.95999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>70.37</v>
+        <v>66.92</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>62.89</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>64.13</v>
+        <v>58.11</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>59.84</v>
+        <v>53.37</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>55.46</v>
+        <v>49.38</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26815,26 +26815,26 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>57.06</v>
+        <v>55.16</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>56.23</v>
+        <v>53.52</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>54.67</v>
+        <v>50.82</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>51.97</v>
+        <v>49.45</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>50.36</v>
+        <v>48.28</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>49.02</v>
+        <v>47.98</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26861,26 +26861,26 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>73.69</v>
+        <v>71.16</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>71.48999999999999</v>
+        <v>67.39</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>67.7</v>
+        <v>62.68</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>62.88</v>
+        <v>59.09</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>59.21</v>
+        <v>54.96</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>54.4</v>
+        <v>51.41</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26907,26 +26907,26 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>60.77</v>
+        <v>59.65</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>60.81</v>
+        <v>58.93</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>60.7</v>
+        <v>57.22</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>59.85</v>
+        <v>54.52</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>58.38</v>
+        <v>51.77</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>56.54</v>
+        <v>47.68</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26953,26 +26953,26 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>50.06</v>
+        <v>47.96</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>48.54</v>
+        <v>45.88</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>46.72</v>
+        <v>43.42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>43.28</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>41.78</v>
+        <v>41.21</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>39.46</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>36.8</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -26999,26 +26999,26 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>55.59</v>
+        <v>52.57</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>55.06</v>
+        <v>50.71</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>54.31</v>
+        <v>49.09</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>53.99</v>
+        <v>47.41</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>53.49</v>
+        <v>46.75</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>51.46</v>
+        <v>46.92</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27045,26 +27045,26 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>56.33</v>
+        <v>53.83</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>53.96</v>
+        <v>53.32</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>53.47</v>
+        <v>52.29</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>52.39</v>
+        <v>50.56</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>50.64</v>
+        <v>48.26</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>48.92</v>
+        <v>45.94</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27091,26 +27091,26 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>40.43</v>
+        <v>42.6</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>41.28</v>
+        <v>43.31</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>41.34</v>
+        <v>44.27</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>41.28</v>
+        <v>45.33</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>40.76</v>
+        <v>47.69</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>41.95</v>
+        <v>47.37</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27137,26 +27137,26 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>17.19</v>
+        <v>18.03</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>19.88</v>
+        <v>19.28</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>20.96</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>22.27</v>
+        <v>22.39</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24.64</v>
+        <v>23.55</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>24.47</v>
+        <v>24.2</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27183,26 +27183,26 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>36.07</v>
+        <v>36.72</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>36.62</v>
+        <v>37.9</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>37.87</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>39.64</v>
+        <v>39.54</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>40.78</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>41</v>
+        <v>41.68</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>41.32</v>
+        <v>40.06</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27229,26 +27229,26 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>21.74</v>
+        <v>21.17</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>20.97</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>20.25</v>
+        <v>20.42</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>19.86</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>19.79</v>
+        <v>19.38</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>19.52</v>
+        <v>19.15</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>19.98</v>
+        <v>19.96</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27275,26 +27275,26 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>37.48</v>
+        <v>37.89</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>37.17</v>
+        <v>37.93</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>36.88</v>
+        <v>38.02</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>36.56</v>
+        <v>38.08</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>36.16</v>
+        <v>37.99</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>36.1</v>
+        <v>38.31</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27321,26 +27321,26 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>53.79</v>
+        <v>54.32</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>53.77</v>
+        <v>55</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>54.28</v>
+        <v>55.15</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>54.22</v>
+        <v>53.98</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>52.98</v>
+        <v>53.12</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>52.14</v>
+        <v>50.77</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27367,26 +27367,26 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>45.73</v>
+        <v>43.14</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>40.91</v>
+        <v>40.95</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>39.29</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>39.32</v>
+        <v>37.7</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>37.91</v>
+        <v>36.41</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>36.82</v>
+        <v>35.8</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27412,27 +27412,27 @@
           <t>大麦</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n">
-        <v>39.8</v>
+      <c r="E40" s="3" t="n">
+        <v>40.46</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>40.77</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>40.95</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>41.02</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>40.86</v>
+        <v>40.36</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>37.74</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>38.93</v>
+        <v>36.13</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27459,26 +27459,26 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>57.54</v>
+        <v>58.23</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>58.52</v>
+        <v>58.67</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>59.06</v>
+        <v>59.49</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>60.07</v>
+        <v>61.07</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>61.93</v>
+        <v>63.36</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>64.88</v>
+        <v>67.22</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27505,26 +27505,26 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>66.87</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>67.22</v>
+        <v>68.33</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>68.95</v>
+        <v>69.36</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>70.33</v>
+        <v>70.78</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>72.23</v>
+        <v>73</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>75.69</v>
+        <v>74.98</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27551,26 +27551,26 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>57.06</v>
+        <v>58.75</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>59.13</v>
+        <v>59.85</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>60.44</v>
+        <v>60.71</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>61.62</v>
+        <v>62.08</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>63.47</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>67.43000000000001</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27597,26 +27597,26 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>60.29</v>
+        <v>58.42</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>59.48</v>
+        <v>57.46</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>59.06</v>
+        <v>57.07</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>59.38</v>
+        <v>57.45</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>60.72</v>
+        <v>58.64</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>62.82</v>
+        <v>60.17</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27643,26 +27643,26 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>55.07</v>
+        <v>57.95</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>56.92</v>
+        <v>59.47</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>57.92</v>
+        <v>61.04</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>58.64</v>
+        <v>63.62</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>59.93</v>
+        <v>67.47</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>65.23999999999999</v>
+        <v>69.27</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27689,26 +27689,26 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>59.05</v>
+        <v>60.42</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>59.86</v>
+        <v>61.2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>60.43</v>
+        <v>61.88</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>60.7</v>
+        <v>62.73</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>60.73</v>
+        <v>63.93</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>61.26</v>
+        <v>66</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27735,26 +27735,26 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>59.81</v>
+        <v>57.34</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>57.8</v>
+        <v>54.65</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>55.27</v>
+        <v>51.64</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>52.58</v>
+        <v>49.79</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>51.18</v>
+        <v>49.47</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>51.25</v>
+        <v>50.97</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27781,26 +27781,26 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>53.22</v>
+        <v>53.23</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>53.13</v>
+        <v>52.47</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>52.35</v>
+        <v>51.66</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>51.53</v>
+        <v>51.11</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>50.85</v>
+        <v>50.87</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>51.09</v>
+        <v>48.67</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27827,26 +27827,26 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>46.73</v>
+        <v>48.76</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>48.42</v>
+        <v>50.02</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>49.47</v>
+        <v>51.85</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>50.95</v>
+        <v>53.67</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>52.14</v>
+        <v>55.47</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>52.46</v>
+        <v>58.48</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27873,26 +27873,26 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>75.25</v>
+        <v>73.14</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>73.16</v>
+        <v>70.28</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>70.23</v>
+        <v>65.73</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>65.56999999999999</v>
+        <v>60.16</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>59.88</v>
+        <v>56.68</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>56.8</v>
+        <v>56.44</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27919,26 +27919,26 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>62.59</v>
+        <v>63.2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>62.39</v>
+        <v>63.28</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>62</v>
+        <v>63.3</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>61.28</v>
+        <v>62.62</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>59.64</v>
+        <v>62.19</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>59.14</v>
+        <v>63.46</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27965,26 +27965,26 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>71.95999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>70.37</v>
+        <v>66.91</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>62.88</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>64.13</v>
+        <v>58.11</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>59.84</v>
+        <v>53.38</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>55.46</v>
+        <v>49.39</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28011,26 +28011,26 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>56.79</v>
+        <v>54.93</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>56.02</v>
+        <v>53.33</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>54.49</v>
+        <v>50.65</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>51.83</v>
+        <v>49.32</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>50.26</v>
+        <v>48.19</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>48.95</v>
+        <v>47.94</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28057,26 +28057,26 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>73.41</v>
+        <v>70.91</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>71.25</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>67.5</v>
+        <v>62.51</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>62.73</v>
+        <v>58.98</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>59.12</v>
+        <v>54.88</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>54.32</v>
+        <v>51.36</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28103,26 +28103,26 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>60.88</v>
+        <v>60.13</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>61.04</v>
+        <v>59.66</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>61.05</v>
+        <v>58.22</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>60.21</v>
+        <v>55.89</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>58.69</v>
+        <v>53.4</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>57.08</v>
+        <v>49.72</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28149,26 +28149,26 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>50.75</v>
+        <v>48.66</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>49.22</v>
+        <v>46.55</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>47.37</v>
+        <v>44.04</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>42.13</v>
+        <v>41.74</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>37.14</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28195,26 +28195,26 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>55.09</v>
+        <v>52.1</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>54.59</v>
+        <v>50.3</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>53.88</v>
+        <v>48.76</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>53.62</v>
+        <v>47.21</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>53.23</v>
+        <v>46.68</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>51.34</v>
+        <v>46.92</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28241,26 +28241,26 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>57.43</v>
+        <v>58.24</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>56.96</v>
+        <v>58.61</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>56.81</v>
+        <v>59.33</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>56.64</v>
+        <v>59.62</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>55.62</v>
+        <v>59.38</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>55.27</v>
+        <v>57.19</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28287,26 +28287,26 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>58.03</v>
+        <v>62.23</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>60.66</v>
+        <v>63.53</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>61.29</v>
+        <v>62.58</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>59.25</v>
+        <v>60.39</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>55.67</v>
+        <v>58.28</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>53.48</v>
+        <v>56.95</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28333,26 +28333,26 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>52.57</v>
+        <v>53.61</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>53.64</v>
+        <v>53.83</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>54.04</v>
+        <v>53.6</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>53.97</v>
+        <v>52.85</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>53.45</v>
+        <v>52.33</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>52.38</v>
+        <v>52.98</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28379,26 +28379,26 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>65.70999999999999</v>
+        <v>66.91</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>65.2</v>
+        <v>65.94</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>63.39</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>60.38</v>
+        <v>62.42</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>56.57</v>
+        <v>60.41</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>54.79</v>
+        <v>57.66</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28425,26 +28425,26 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>44.55</v>
+        <v>44.76</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>45.43</v>
+        <v>46.85</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>47.82</v>
+        <v>49.51</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>50.73</v>
+        <v>52.23</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>53.11</v>
+        <v>55</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>54.57</v>
+        <v>58.95</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28471,26 +28471,26 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>52.96</v>
+        <v>54.93</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>55.48</v>
+        <v>57.73</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>58.28</v>
+        <v>60.78</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>61.09</v>
+        <v>64.61</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>63.91</v>
+        <v>68.55</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>66.56</v>
+        <v>73.91</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28517,26 +28517,26 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>62.88</v>
+        <v>63.67</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>63.44</v>
+        <v>64.56</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>64.37</v>
+        <v>65.61</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>65.41</v>
+        <v>68.33</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>68.06999999999999</v>
+        <v>72.69</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>72.44</v>
+        <v>78.41</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28563,26 +28563,26 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>59.01</v>
+        <v>58.79</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>58.93</v>
+        <v>59.1</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>59.39</v>
+        <v>60.12</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>60.69</v>
+        <v>62.16</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>63.12</v>
+        <v>65.64</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>67.03</v>
+        <v>71.66</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28609,26 +28609,26 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>62.89</v>
+        <v>63.48</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>62.52</v>
+        <v>63.59</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>62.12</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>62</v>
+        <v>66.88</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>63.09</v>
+        <v>71.31</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>67.98</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28655,26 +28655,26 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>50.29</v>
+        <v>47.74</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>47.5</v>
+        <v>45.54</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>45.18</v>
+        <v>44.39</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>43.87</v>
+        <v>43.05</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>42.32</v>
+        <v>41.82</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>41.01</v>
+        <v>41.27</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28701,26 +28701,26 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>34.91</v>
+        <v>35.23</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>34.9</v>
+        <v>35.97</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>35.46</v>
+        <v>37.13</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>36.33</v>
+        <v>37.41</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>36.51</v>
+        <v>37.31</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>36.47</v>
+        <v>37.44</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28747,26 +28747,26 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>17.64</v>
+        <v>18.51</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>18.66</v>
+        <v>19.77</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>20.34</v>
+        <v>21.44</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>22.67</v>
+        <v>22.86</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>24.99</v>
+        <v>24.04</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>24.87</v>
+        <v>24.77</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28793,26 +28793,26 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>36</v>
+        <v>36.64</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>36.54</v>
+        <v>37.83</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>39.57</v>
+        <v>39.47</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>40.72</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>40.95</v>
+        <v>41.63</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>41.27</v>
+        <v>40.01</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28839,26 +28839,26 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>21.75</v>
+        <v>21.18</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>20.27</v>
+        <v>20.43</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>19.88</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="J71" s="4" t="n">
-        <v>20</v>
+        <v>19.17</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>19.98</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28885,26 +28885,26 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>37.28</v>
+        <v>37.69</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>37</v>
+        <v>37.71</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>36.71</v>
+        <v>37.78</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>36.38</v>
+        <v>37.84</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>36.01</v>
+        <v>37.78</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>35.99</v>
+        <v>38.11</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28931,26 +28931,26 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>53.8</v>
+        <v>54.33</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>53.78</v>
+        <v>55.01</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>54.29</v>
+        <v>55.16</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>54.23</v>
+        <v>53.99</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>52.99</v>
+        <v>53.13</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>52.14</v>
+        <v>50.77</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28977,26 +28977,26 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>45.72</v>
+        <v>43.15</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>40.91</v>
+        <v>40.96</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>39.31</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>39.33</v>
+        <v>37.72</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>37.92</v>
+        <v>36.43</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>36.84</v>
+        <v>35.83</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29023,26 +29023,26 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>40.11</v>
+        <v>40.69</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>41</v>
+        <v>40.55</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>41.14</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>41.01</v>
+        <v>40.17</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>38.01</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>39.16</v>
+        <v>36.49</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29069,26 +29069,26 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>28.99</v>
+        <v>29.8</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>29.94</v>
+        <v>29.89</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>30.48</v>
+        <v>30.22</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>31.72</v>
+        <v>31.05</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>33.88</v>
+        <v>32.6</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>34.17</v>
+        <v>31.81</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29115,26 +29115,26 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>56.92</v>
+        <v>57.62</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>57.92</v>
+        <v>58.04</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>58.43</v>
+        <v>58.82</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>59.4</v>
+        <v>60.4</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>61.27</v>
+        <v>62.68</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>64.20999999999999</v>
+        <v>66.55</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29161,26 +29161,26 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>36.02</v>
+        <v>36.07</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>37.07</v>
+        <v>35.74</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>37.22</v>
+        <v>34.96</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>37.18</v>
+        <v>34.32</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>37.68</v>
+        <v>33.73</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>38.23</v>
+        <v>35.98</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29207,26 +29207,26 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>64.47</v>
+        <v>66.62</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>66.97</v>
+        <v>68.06</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>68.68000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>70.08</v>
+        <v>70.56</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>72.01000000000001</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>75.51000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29253,26 +29253,26 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>56.69</v>
+        <v>58.35</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>58.74</v>
+        <v>59.48</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>60.09</v>
+        <v>60.33</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>61.26</v>
+        <v>61.7</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>63.1</v>
+        <v>64.22</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29299,26 +29299,26 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>60.19</v>
+        <v>58.32</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>59.39</v>
+        <v>57.35</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>58.97</v>
+        <v>56.97</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>59.28</v>
+        <v>57.35</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>60.63</v>
+        <v>58.55</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>62.73</v>
+        <v>60.09</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29345,26 +29345,26 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>30.01</v>
+        <v>30.58</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>30.49</v>
+        <v>32.31</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>32.15</v>
+        <v>34.53</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>34.23</v>
+        <v>36.41</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>35.91</v>
+        <v>37.03</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>36.03</v>
+        <v>34.66</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29391,26 +29391,26 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>59.99</v>
+        <v>58.63</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>57.64</v>
+        <v>56.28</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>54.77</v>
+        <v>53.8</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>51.53</v>
+        <v>51.86</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>48.65</v>
+        <v>49.44</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>46.43</v>
+        <v>48.55</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29437,26 +29437,26 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>53.19</v>
+        <v>52.61</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>52.21</v>
+        <v>50.16</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>49.8</v>
+        <v>46.4</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>46.2</v>
+        <v>45.29</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>45.36</v>
+        <v>45.56</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>45.84</v>
+        <v>46.73</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29483,26 +29483,26 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="F85" s="4" t="n">
-        <v>38.21</v>
-      </c>
-      <c r="G85" s="4" t="n">
-        <v>39.94</v>
+        <v>39.59</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>44.52</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>41.28</v>
+        <v>46.65</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>41.7</v>
+        <v>47.09</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>40.48</v>
+        <v>45.8</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29529,26 +29529,26 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>56.72</v>
+        <v>57.27</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>56.93</v>
+        <v>57.1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>56.51</v>
+        <v>55.89</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>54.87</v>
+        <v>54.91</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>53.22</v>
+        <v>53.4</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>50.79</v>
+        <v>52.3</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29575,26 +29575,26 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>47.82</v>
+        <v>43.93</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>42.88</v>
+        <v>40.17</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>38.69</v>
+        <v>36.98</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>34.83</v>
+        <v>35.3</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>32.12</v>
+        <v>33.8</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>30.61</v>
+        <v>31.91</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29621,26 +29621,26 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>35.33</v>
+        <v>35.03</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>34.67</v>
+        <v>36.38</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>35.69</v>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="I88" s="4" t="n">
-        <v>38.76</v>
+        <v>38.65</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>40.96</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>37.76</v>
+        <v>38.47</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29667,26 +29667,26 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>55.63</v>
+        <v>58.54</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>57.49</v>
+        <v>59.96</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>58.4</v>
+        <v>61.47</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>59.04</v>
+        <v>64</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>60.28</v>
+        <v>67.83</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>65.58</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29713,26 +29713,26 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>53.65</v>
+        <v>56.89</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>55.89</v>
+        <v>60.02</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>58.61</v>
+        <v>63.45</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>61.46</v>
+        <v>66.17</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>63.41</v>
+        <v>68.61</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>66.98</v>
+        <v>69.42</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29759,26 +29759,26 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>62.69</v>
+        <v>67.02</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>66.34999999999999</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>69.52</v>
+        <v>72.61</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>71.56</v>
+        <v>73.19</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>71.67</v>
+        <v>73.8</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>73.36</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29805,26 +29805,26 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>60.35</v>
+        <v>60.7</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>60.09</v>
+        <v>59.89</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>58.97</v>
+        <v>59.29</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>57.9</v>
+        <v>59.09</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>56.87</v>
+        <v>59.17</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>57.39</v>
+        <v>56.47</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29851,26 +29851,26 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>43.75</v>
+        <v>44.3</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>44.27</v>
+        <v>46.14</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>46.12</v>
+        <v>49.11</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>49.11</v>
+        <v>52.47</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>52.14</v>
+        <v>55.61</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>53.99</v>
+        <v>59.84</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29897,26 +29897,26 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>48.79</v>
+        <v>47.73</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>48.28</v>
+        <v>46.82</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>47.79</v>
+        <v>45.95</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>47.55</v>
+        <v>45.09</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>47.71</v>
+        <v>44.83</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>48.03</v>
+        <v>44.45</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29943,26 +29943,26 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>43.77</v>
+        <v>44.13</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>44.18</v>
+        <v>44.97</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>45.23</v>
+        <v>47.56</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>48.16</v>
+        <v>51.64</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>52.59</v>
+        <v>56.94</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>57.44</v>
+        <v>62.89</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -29989,26 +29989,26 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>42.45</v>
+        <v>42.27</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>42.17</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>41.21</v>
+        <v>41.25</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>39.94</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>39.93</v>
+        <v>39.9</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>40.11</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>40.04</v>
+        <v>40.41</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30035,26 +30035,26 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>62.56</v>
+        <v>62.34</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>62.52</v>
+        <v>62.61</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>62.96</v>
+        <v>63.44</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.88</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>66.03</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>68.94</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30081,26 +30081,26 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>44.92</v>
+        <v>45.99</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>45.9</v>
+        <v>47.53</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>47.5</v>
+        <v>49.08</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>49.19</v>
+        <v>51</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>51.28</v>
+        <v>53.52</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>53.82</v>
+        <v>57.32</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30127,26 +30127,26 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>63.84</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>62.97</v>
+        <v>64.87</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>62.68</v>
+        <v>65.97</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>62.62</v>
+        <v>67.44</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>62.41</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>62.22</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30172,27 +30172,27 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E100" s="3" t="n">
-        <v>40.64</v>
+      <c r="E100" s="4" t="n">
+        <v>39.36</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>39.99</v>
+        <v>39.35</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>40.25</v>
+        <v>40.45</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>41.67</v>
+        <v>41.96</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>43.68</v>
+        <v>44.51</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>47.84</v>
+        <v>45.06</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30219,26 +30219,26 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>58.37</v>
+        <v>59.67</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>59.99</v>
+        <v>60.49</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>60.95</v>
+        <v>61.65</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>62.35</v>
+        <v>63.49</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>64.56</v>
+        <v>65.66</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>67.45999999999999</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30265,26 +30265,26 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>39.47</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>40.83</v>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="H102" s="3" t="n">
-        <v>41.38</v>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>41.95</v>
+        <v>39.91</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>38.33</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>42.71</v>
+        <v>40.76</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30311,26 +30311,26 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>66.55</v>
+        <v>63.14</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>64.52</v>
+        <v>60.69</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>62.76</v>
+        <v>58.08</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>61.11</v>
+        <v>54.52</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>58.76</v>
+        <v>51.18</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>56.11</v>
+        <v>48.64</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30357,26 +30357,26 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>55.46</v>
+        <v>49.99</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>50</v>
+        <v>45.04</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>45.29</v>
-      </c>
-      <c r="H104" s="3" t="n">
-        <v>41.7</v>
+        <v>41.13</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>38.06</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>39.09</v>
+        <v>36.59</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>38.4</v>
+        <v>37.36</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30403,26 +30403,26 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>56.27</v>
+        <v>55.42</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>56.25</v>
+        <v>56.4</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>57.75</v>
+        <v>58.37</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>60.38</v>
+        <v>58.62</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>61.41</v>
+        <v>59.26</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>62.5</v>
+        <v>58.84</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30449,26 +30449,26 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>56.92</v>
+        <v>51.99</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>52.76</v>
+        <v>47.91</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>49.11</v>
+        <v>44.61</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>46.42</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="J106" s="3" t="n">
-        <v>42.22</v>
+        <v>41.35</v>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="J106" s="4" t="n">
+        <v>38</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30495,26 +30495,26 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>64.55</v>
+        <v>61.54</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>61.59</v>
+        <v>58.59</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>58.93</v>
+        <v>54.9</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>55.61</v>
+        <v>50.56</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>52.09</v>
+        <v>46.82</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>49.94</v>
+        <v>45.7</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30541,26 +30541,26 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>53.98</v>
+        <v>55.15</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>55.08</v>
+        <v>55.22</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>55.04</v>
+        <v>54.87</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>54.56</v>
+        <v>52.96</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>52.52</v>
+        <v>51.47</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>51.59</v>
+        <v>50.15</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30587,26 +30587,26 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>68.3</v>
+        <v>63.48</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>64.02</v>
+        <v>58.91</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>59.71</v>
+        <v>54.73</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>55.93</v>
+        <v>50.1</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>51.95</v>
+        <v>46.19</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>48.73</v>
+        <v>43.98</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30633,26 +30633,26 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>37.48</v>
+        <v>35.84</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>35.43</v>
+        <v>34.93</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>34.41</v>
+        <v>34.24</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>33.5</v>
+        <v>34.17</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>33.03</v>
+        <v>34.31</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>32.89</v>
+        <v>33.55</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30679,26 +30679,26 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>37.98</v>
+        <v>36.74</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>36.42</v>
+        <v>35.63</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>35.12</v>
+        <v>34.78</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>34.05</v>
+        <v>34.46</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>33.37</v>
+        <v>33.86</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>32.96</v>
+        <v>34.07</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30725,26 +30725,26 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>32.76</v>
+        <v>31.7</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>32.64</v>
+        <v>31</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>32.31</v>
+        <v>29.79</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>31.49</v>
+        <v>30.15</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>31.85</v>
+        <v>30.7</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>32.42</v>
+        <v>30.34</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30771,26 +30771,26 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>48.16</v>
+        <v>45.83</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>46.35</v>
+        <v>43.79</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>44.6</v>
+        <v>41.95</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>43.31</v>
+        <v>40.49</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>42.52</v>
+        <v>40.21</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>42.21</v>
+        <v>40.41</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30817,26 +30817,26 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>33.4</v>
+        <v>33.02</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>33.76</v>
+        <v>33.18</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>34.19</v>
+        <v>33.33</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>34.72</v>
+        <v>33.71</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>35.55</v>
+        <v>34.15</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>36.27</v>
+        <v>34.71</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30863,26 +30863,26 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>32.64</v>
+        <v>32</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>32.36</v>
+        <v>31.93</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>32.29</v>
+        <v>31.71</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>31.94</v>
+        <v>32.28</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>31.91</v>
+        <v>34.23</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>33.78</v>
+        <v>36.04</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30909,26 +30909,26 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>41.5</v>
+        <v>41.14</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>38.88</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>39.44</v>
+        <v>35.83</v>
       </c>
       <c r="H116" s="4" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="I116" s="4" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="J116" s="4" t="n">
         <v>36.63</v>
       </c>
-      <c r="I116" s="4" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="J116" s="4" t="n">
-        <v>34.83</v>
-      </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30955,26 +30955,26 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>29.24</v>
+        <v>26.46</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>27.57</v>
+        <v>25.83</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>27.39</v>
+        <v>25.51</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>27.49</v>
+        <v>26.08</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>28.25</v>
+        <v>26.4</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>28.33</v>
+        <v>26.89</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31001,26 +31001,26 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>39.3</v>
+        <v>38.07</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>38.54</v>
+        <v>36.48</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>37.22</v>
+        <v>34.81</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>35.96</v>
+        <v>33.86</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>35.66</v>
+        <v>33.97</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>35.53</v>
+        <v>34.89</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31047,26 +31047,26 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>44.84</v>
+        <v>43.65</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>41.68</v>
+        <v>41.6</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>39.38</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>39.66</v>
+        <v>37.71</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>38.29</v>
+        <v>37</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>37.77</v>
+        <v>36.78</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31093,26 +31093,26 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>45.04</v>
+        <v>43.51</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>43.83</v>
+        <v>41.97</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>42.56</v>
-      </c>
-      <c r="H120" s="3" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="I120" s="3" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="J120" s="3" t="n">
-        <v>41.75</v>
+        <v>40.54</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="I120" s="4" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="J120" s="4" t="n">
+        <v>37.6</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31139,26 +31139,26 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>42.77</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>41.13</v>
+        <v>41.25</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>39.84</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>39.32</v>
+        <v>39.04</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>37.98</v>
+        <v>38.66</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>36.87</v>
+        <v>38.85</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>36.67</v>
+        <v>39.42</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31185,26 +31185,26 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>37.05</v>
+        <v>35.3</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>34.71</v>
+        <v>33.73</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>32.8</v>
+        <v>33.12</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>31.59</v>
+        <v>33.17</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>30.9</v>
+        <v>33.26</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>30.16</v>
+        <v>34.35</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31231,26 +31231,26 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>47.43</v>
+        <v>48.36</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>48.21</v>
+        <v>48.77</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>48.64</v>
+        <v>48.87</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>48.79</v>
+        <v>49.42</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>49.36</v>
+        <v>49.86</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>49.71</v>
+        <v>51.01</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31277,26 +31277,26 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>70.48</v>
+        <v>70.97</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>70.81999999999999</v>
+        <v>71.42</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>71.25</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>70.77</v>
+        <v>69.81</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>69.31</v>
+        <v>67.83</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>67.23</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31323,26 +31323,26 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>65.52</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>65.03</v>
+        <v>66.37</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>65.98999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>66.14</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>65.73999999999999</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>64.86</v>
+        <v>63.63</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31369,26 +31369,26 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>47.71</v>
+        <v>49.41</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>48.23</v>
+        <v>49.9</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>48.1</v>
+        <v>51.1</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>48.08</v>
+        <v>52.86</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>48.21</v>
+        <v>53.56</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>47.63</v>
+        <v>55.03</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31415,26 +31415,26 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>59.73</v>
+        <v>57.27</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>57.71</v>
+        <v>54.54</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>55.14</v>
+        <v>51.51</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>52.43</v>
+        <v>49.67</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>51.02</v>
+        <v>49.36</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31461,26 +31461,26 @@
         </is>
       </c>
       <c r="E128" s="6" t="n">
-        <v>82.65000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="G128" s="6" t="n">
-        <v>80.14</v>
+        <v>81.13</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>78.78</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>77.23999999999999</v>
+        <v>75.33</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>72.86</v>
+        <v>70.48</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>67.31</v>
+        <v>67.36</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31507,26 +31507,26 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>54.12</v>
+        <v>54.15</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>54.04</v>
+        <v>53.33</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>53.2</v>
+        <v>52.43</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>52.28</v>
+        <v>51.72</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>51.42</v>
+        <v>51.39</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>51.56</v>
+        <v>48.99</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31553,26 +31553,26 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>75.65000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>73.70999999999999</v>
+        <v>70.84</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>70.98</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>66.58</v>
+        <v>60.98</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>61.14</v>
+        <v>57.29</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>57.71</v>
+        <v>56.62</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31599,26 +31599,26 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>62.47</v>
+        <v>63.06</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>62.26</v>
+        <v>63.11</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>61.83</v>
+        <v>63.11</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>61.1</v>
+        <v>62.41</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>59.45</v>
+        <v>61.95</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>58.96</v>
+        <v>63.19</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31645,26 +31645,26 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>62.4</v>
+        <v>62.53</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>61.9</v>
+        <v>62.22</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>61.39</v>
+        <v>61.77</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>60.53</v>
+        <v>60.96</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>59.08</v>
+        <v>59.96</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>58.6</v>
+        <v>58.47</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31691,26 +31691,26 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>71.87</v>
+        <v>72.17</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>72.93000000000001</v>
+        <v>72.62</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>73.86</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>73.65000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>72.56999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>68.94</v>
+        <v>63.06</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31737,26 +31737,26 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>55.24</v>
+        <v>51.21</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>51.66</v>
+        <v>46.72</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="H134" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="I134" s="3" t="n">
-        <v>40.48</v>
+        <v>42.39</v>
+      </c>
+      <c r="H134" s="4" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="I134" s="4" t="n">
+        <v>37.28</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>39.56</v>
+        <v>37.69</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31783,26 +31783,26 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>65.64</v>
+        <v>62.5</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>62.65</v>
+        <v>56.84</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>57.06</v>
+        <v>50.27</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>50.63</v>
+        <v>45.4</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>45.94</v>
+        <v>42.95</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>43.92</v>
+        <v>42.98</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31829,26 +31829,26 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>57.21</v>
+        <v>53.12</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>53.37</v>
+        <v>49.53</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>49.9</v>
+        <v>46.3</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="I136" s="3" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="J136" s="3" t="n">
-        <v>41.19</v>
+        <v>42.74</v>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="J136" s="4" t="n">
+        <v>36.09</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31875,26 +31875,26 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>48.18</v>
+        <v>44.48</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="G137" s="3" t="n">
-        <v>41.96</v>
+        <v>41.11</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>38.42</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>39.73</v>
+        <v>35.35</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>37.39</v>
+        <v>33.02</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>36.11</v>
+        <v>31.53</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31921,26 +31921,26 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>27.67</v>
+        <v>25.45</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>25.27</v>
+        <v>23.37</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>23.03</v>
-      </c>
-      <c r="H138" s="4" t="n">
-        <v>20.92</v>
+        <v>21.41</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>19.47</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>18.92</v>
+        <v>17.82</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>17.79</v>
+        <v>16.49</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31967,26 +31967,26 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>59.32</v>
+        <v>59.17</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>58.6</v>
+        <v>57.27</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>56.39</v>
+        <v>54.36</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>53.32</v>
+        <v>51.48</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>51.12</v>
+        <v>49.68</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32013,26 +32013,26 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>52.49</v>
+        <v>48.84</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>49.28</v>
+        <v>46.46</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>47.07</v>
+        <v>44.32</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I140" s="3" t="n">
-        <v>42.56</v>
+        <v>41.12</v>
+      </c>
+      <c r="I140" s="4" t="n">
+        <v>37.48</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>39.28</v>
+        <v>36.08</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32059,26 +32059,26 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>57</v>
+        <v>54.12</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>54.09</v>
+        <v>49.94</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>49.94</v>
+        <v>45.65</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>45.78</v>
+        <v>42.34</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>42.89</v>
+        <v>40.87</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>42.21</v>
+        <v>41.02</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32105,26 +32105,26 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>36.82</v>
+        <v>34.22</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>34.22</v>
+        <v>32.25</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>32.17</v>
+        <v>30.66</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>30.57</v>
+        <v>28.82</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>28.8</v>
+        <v>26.54</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>26.94</v>
+        <v>24.88</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32150,27 +32150,27 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E143" s="3" t="n">
-        <v>41.49</v>
+      <c r="E143" s="4" t="n">
+        <v>38.29</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>37.84</v>
+        <v>35.64</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>34.86</v>
+        <v>33.77</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>32.53</v>
+        <v>32.14</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>30.34</v>
+        <v>31.14</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>29.37</v>
+        <v>30.43</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32197,26 +32197,26 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>66.58</v>
+        <v>62.99</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>63.63</v>
+        <v>58.8</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>59.84</v>
+        <v>53.23</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>54.8</v>
+        <v>47.1</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>49.4</v>
+        <v>42.68</v>
       </c>
       <c r="J144" s="3" t="n">
-        <v>45.77</v>
+        <v>40.54</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32243,26 +32243,26 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>72.15000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>70.16</v>
+        <v>65.16</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>66.28</v>
+        <v>58.98</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>60.91</v>
+        <v>53.24</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>56.18</v>
+        <v>48.95</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>51.94</v>
+        <v>46.63</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32289,26 +32289,26 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>60.56</v>
+        <v>58.37</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>58.68</v>
+        <v>55.97</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>56.43</v>
+        <v>52.72</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>53.48</v>
+        <v>48.08</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>49.3</v>
+        <v>45.21</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>47.09</v>
+        <v>44.12</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32335,26 +32335,26 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>34.59</v>
+        <v>31.54</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>31.72</v>
+        <v>28.87</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>29.15</v>
+        <v>26.94</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>27.39</v>
+        <v>24.7</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>25.54</v>
+        <v>22.78</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>24.39</v>
+        <v>21.07</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32381,26 +32381,26 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>60.42</v>
+        <v>60.97</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>60.52</v>
+        <v>60.06</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>59.34</v>
+        <v>57.5</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>56.47</v>
+        <v>53.98</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>52.68</v>
+        <v>51.33</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>50.84</v>
+        <v>49.46</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32427,26 +32427,26 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>64.11</v>
+        <v>65.25</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>63.52</v>
+        <v>66.09</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>63.58</v>
+        <v>67.36</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>63.5</v>
+        <v>69.11</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>63.24</v>
+        <v>70.42</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>63.08</v>
+        <v>71.12</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32473,26 +32473,26 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>71.03</v>
+        <v>72.44</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>72.64</v>
+        <v>73.95</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>74.27</v>
+        <v>74.28</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>74.79000000000001</v>
+        <v>74.17</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>75</v>
+        <v>72.94</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>73.59</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32519,26 +32519,26 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>63.58</v>
+        <v>65.22</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>65.25</v>
+        <v>66.12</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>66.14</v>
+        <v>66.12</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>66.14</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>65.37</v>
+        <v>64.39</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>63.98</v>
+        <v>65.55</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32565,26 +32565,26 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>49.14</v>
+        <v>49.27</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>49.17</v>
+        <v>50.19</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>50.05</v>
+        <v>52.06</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>51.83</v>
+        <v>54.16</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>53.74</v>
+        <v>55.66</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>55.76</v>
+        <v>54.34</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32611,26 +32611,26 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>57.85</v>
+        <v>57.15</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>57.02</v>
+        <v>57.11</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>56.96</v>
+        <v>57.19</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>57</v>
+        <v>57.72</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>57.44</v>
+        <v>58.49</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>57.95</v>
+        <v>59.36</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32657,26 +32657,26 @@
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>50.94</v>
+        <v>51.73</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>51.17</v>
+        <v>52.44</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>51.66</v>
+        <v>53.74</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>52.62</v>
+        <v>55.61</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>53.98</v>
+        <v>57.28</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>55.71</v>
+        <v>55.03</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32703,26 +32703,26 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>29.7</v>
+        <v>30.8</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>30.44</v>
+        <v>31.67</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>31.17</v>
+        <v>31.09</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>30.5</v>
+        <v>29.75</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>29.33</v>
+        <v>28.96</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>28.89</v>
+        <v>29.17</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32749,26 +32749,26 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>50.29</v>
+        <v>47.65</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>47.46</v>
+        <v>45.38</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>45.09</v>
+        <v>44.16</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>43.74</v>
+        <v>42.76</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>42.17</v>
+        <v>41.41</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>40.76</v>
+        <v>40.72</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32795,26 +32795,26 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>17.51</v>
+        <v>18.32</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>18.54</v>
+        <v>19.5</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>20.19</v>
+        <v>20.99</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>22.42</v>
+        <v>22.21</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>24.62</v>
+        <v>23.28</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>24.35</v>
+        <v>24.08</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32841,26 +32841,26 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>36.84</v>
+        <v>37.57</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>37.42</v>
+        <v>38.6</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>38.54</v>
+        <v>39.87</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>40.01</v>
+        <v>40.72</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>41.05</v>
-      </c>
-      <c r="J158" s="3" t="n">
-        <v>41.15</v>
+        <v>41.38</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>39.71</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32887,26 +32887,26 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>21.76</v>
+        <v>21.21</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="G159" s="4" t="n">
-        <v>20.31</v>
+        <v>20.48</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>19.94</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>19.86</v>
+        <v>19.47</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>19.61</v>
+        <v>19.23</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>20.06</v>
+        <v>20.04</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32933,26 +32933,26 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>36.76</v>
+        <v>37.15</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>36.47</v>
+        <v>37.23</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>36.24</v>
+        <v>37.42</v>
       </c>
       <c r="H160" s="4" t="n">
-        <v>36.03</v>
+        <v>37.62</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>35.77</v>
+        <v>37.67</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>35.84</v>
+        <v>38.08</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32979,26 +32979,26 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>53.45</v>
+        <v>54.02</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>53.47</v>
+        <v>54.76</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>54.05</v>
+        <v>54.94</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>54.05</v>
+        <v>53.91</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>52.98</v>
+        <v>53.2</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>52.26</v>
+        <v>50.81</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33025,26 +33025,26 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>41.69</v>
+        <v>41.76</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>39.45</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>39.42</v>
+        <v>37.79</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>37.82</v>
+        <v>36.26</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>36.49</v>
+        <v>35</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>35.41</v>
+        <v>34.45</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33070,27 +33070,27 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E163" s="4" t="n">
-        <v>39.81</v>
+      <c r="E163" s="3" t="n">
+        <v>40.31</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>40.59</v>
-      </c>
-      <c r="G163" s="3" t="n">
-        <v>40.65</v>
-      </c>
-      <c r="H163" s="3" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="I163" s="3" t="n">
-        <v>40.58</v>
+        <v>40.11</v>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="H163" s="4" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="I163" s="4" t="n">
+        <v>37.82</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>38.97</v>
+        <v>36.33</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33117,26 +33117,26 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>61.07</v>
+        <v>62.41</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>62.25</v>
+        <v>63.28</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>63.23</v>
+        <v>63.03</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>62.88</v>
+        <v>62.06</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>61.6</v>
+        <v>59.99</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>60.03</v>
+        <v>58.91</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33163,26 +33163,26 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>60.06</v>
+        <v>61.45</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>61.69</v>
+        <v>62.42</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>62.9</v>
+        <v>63.07</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>63.62</v>
+        <v>63.24</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>63.49</v>
+        <v>60.76</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>60.46</v>
+        <v>58.3</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33209,26 +33209,26 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>60.94</v>
+        <v>61.57</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>62.32</v>
+        <v>62.19</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>63.61</v>
+        <v>60.96</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>63.21</v>
+        <v>59.63</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>62.79</v>
+        <v>57.11</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>60.06</v>
+        <v>54.6</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33255,26 +33255,26 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>59.86</v>
+        <v>58.51</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>57.54</v>
+        <v>56.2</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>51.49</v>
+        <v>51.74</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>46.39</v>
+        <v>48.41</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33301,26 +33301,26 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>53.53</v>
+        <v>52.32</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>52.18</v>
+        <v>49.24</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>49.23</v>
+        <v>44.76</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>44.99</v>
+        <v>43.48</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>44.01</v>
+        <v>43.85</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>44.62</v>
+        <v>45.21</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33347,26 +33347,26 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>58.74</v>
+        <v>60.56</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>60.34</v>
+        <v>61.63</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>61.25</v>
+        <v>62.08</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>61.44</v>
+        <v>62.75</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>61.68</v>
+        <v>62.84</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>61.86</v>
+        <v>61.7</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33393,26 +33393,26 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>58.55</v>
+        <v>62.58</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>62.21</v>
+        <v>65.16</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>64.59</v>
+        <v>66.34</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>65.3</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>65.17</v>
+        <v>65.39</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>62.74</v>
+        <v>62.79</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33439,26 +33439,26 @@
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>53.56</v>
+        <v>54.82</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>54.32</v>
+        <v>54.93</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>54.1</v>
+        <v>53.49</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>52.2</v>
+        <v>52.71</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>50.77</v>
+        <v>51.31</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>48.97</v>
+        <v>50.06</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33485,26 +33485,26 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>42.43</v>
+        <v>43.18</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>42.39</v>
+        <v>43.29</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>42.47</v>
+        <v>43.44</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>42.64</v>
+        <v>43.48</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>42.8</v>
+        <v>43.67</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>43.32</v>
+        <v>43.86</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33531,26 +33531,26 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>55.64</v>
+        <v>58.54</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>57.48</v>
+        <v>59.9</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>58.32</v>
+        <v>61.4</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>58.94</v>
+        <v>63.95</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>60.18</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>65.53</v>
+        <v>69.58</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33577,26 +33577,26 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>53.62</v>
+        <v>56.89</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>55.89</v>
+        <v>60.06</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>58.63</v>
+        <v>63.55</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>61.53</v>
+        <v>66.31</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>63.49</v>
+        <v>68.75</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>67.09</v>
+        <v>69.55</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33623,26 +33623,26 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>62.64</v>
+        <v>66.97</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>66.3</v>
+        <v>70.28</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>69.47</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>71.51000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>71.61</v>
+        <v>73.77</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>73.3</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33669,26 +33669,26 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>68.14</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>71.95</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>75.65000000000001</v>
+        <v>78.88</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>77.36</v>
+        <v>78.8</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>76.73999999999999</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>77.8</v>
+        <v>76.98</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33715,26 +33715,26 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>46.47</v>
+        <v>47.62</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>47.45</v>
+        <v>47.99</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>47.83</v>
+        <v>48.13</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>47.99</v>
+        <v>48.89</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>48.78</v>
+        <v>49.4</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>49.34</v>
+        <v>50.48</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33761,26 +33761,26 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>58.03</v>
+        <v>60.23</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>60.5</v>
+        <v>61.23</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>61.23</v>
+        <v>61.19</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>60.82</v>
+        <v>61.35</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>60.1</v>
+        <v>60.65</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>59.54</v>
+        <v>62.44</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33807,26 +33807,26 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>56.96</v>
+        <v>59.03</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>58.85</v>
+        <v>61.51</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>61.06</v>
+        <v>62.9</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>62.02</v>
+        <v>62.93</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>61.45</v>
+        <v>62.15</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>60.72</v>
+        <v>62.91</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33853,26 +33853,26 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>56.96</v>
+        <v>59.22</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>59.28</v>
+        <v>61.21</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>61.23</v>
+        <v>62.08</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>62.02</v>
+        <v>61.39</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>61.23</v>
+        <v>59.06</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>59.12</v>
+        <v>57.77</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33899,26 +33899,26 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>52.73</v>
+        <v>54.7</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>55.24</v>
+        <v>57.4</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>57.93</v>
+        <v>60.36</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>60.65</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>63.48</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33945,26 +33945,26 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>48.21</v>
+        <v>47.35</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>47.75</v>
+        <v>46.45</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>47.19</v>
+        <v>45.5</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>46.76</v>
+        <v>44.67</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>46.76</v>
+        <v>44.37</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>46.87</v>
+        <v>43.89</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -33991,26 +33991,26 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>40.64</v>
+        <v>41</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>41.01</v>
+        <v>41.28</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>41.44</v>
+        <v>43.66</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>44.05</v>
+        <v>47.98</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>48.6</v>
+        <v>52.74</v>
       </c>
       <c r="J183" s="3" t="n">
-        <v>53.13</v>
+        <v>58.3</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34037,26 +34037,26 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>41.96</v>
+        <v>41.84</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="G184" s="3" t="n">
-        <v>40.72</v>
+        <v>40.86</v>
+      </c>
+      <c r="G184" s="4" t="n">
+        <v>39.79</v>
       </c>
       <c r="H184" s="4" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="I184" s="4" t="n">
-        <v>39.67</v>
-      </c>
-      <c r="J184" s="4" t="n">
-        <v>39.73</v>
+        <v>39.9</v>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>40.43</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34083,26 +34083,26 @@
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>44.58</v>
+        <v>42.82</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="G185" s="3" t="n">
-        <v>40.09</v>
+        <v>40.91</v>
+      </c>
+      <c r="G185" s="4" t="n">
+        <v>39.52</v>
       </c>
       <c r="H185" s="4" t="n">
-        <v>38.3</v>
+        <v>38.68</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>36.83</v>
+        <v>37.91</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>35.75</v>
+        <v>38.38</v>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34129,26 +34129,26 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>45.36</v>
+        <v>46.39</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>46.31</v>
+        <v>47.86</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>47.83</v>
+        <v>49.39</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>49.48</v>
+        <v>51.23</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>51.5</v>
+        <v>53.74</v>
       </c>
       <c r="J186" s="3" t="n">
-        <v>54.14</v>
+        <v>57.54</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34175,26 +34175,26 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>66.87</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>66.76000000000001</v>
+        <v>69.48</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>67.04000000000001</v>
+        <v>70.63</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>66.88</v>
+        <v>72.08</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>66.38</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="J187" s="3" t="n">
-        <v>65.77</v>
+        <v>73.59</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34221,26 +34221,26 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>71.08</v>
+        <v>72.44</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>72.68000000000001</v>
+        <v>73.97</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>74.34</v>
+        <v>74.31</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>74.88</v>
+        <v>74.17</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>75.08</v>
+        <v>72.95</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>72.13</v>
+        <v>73.62</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34267,26 +34267,26 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>62.72</v>
+        <v>64.22</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>64.16</v>
+        <v>65.19</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>65.09</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>65.28</v>
+        <v>65.22</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>64.83</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>63.76</v>
+        <v>66.05</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34313,26 +34313,26 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>49.81</v>
+        <v>49.69</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>49.63</v>
+        <v>50.43</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>50.35</v>
+        <v>52.07</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>51.91</v>
+        <v>53.85</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>53.56</v>
+        <v>54.97</v>
       </c>
       <c r="J190" s="3" t="n">
-        <v>55.06</v>
+        <v>53.73</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34359,26 +34359,26 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>58.04</v>
+        <v>57.27</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>57.15</v>
+        <v>57.17</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>57.04</v>
+        <v>57.23</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>57.06</v>
+        <v>57.69</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>57.45</v>
+        <v>58.35</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>57.84</v>
+        <v>59.22</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34405,26 +34405,26 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>55.48</v>
+        <v>56.01</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>55.15</v>
+        <v>56.28</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>55.06</v>
+        <v>57.04</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>55.26</v>
+        <v>58.62</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>56.02</v>
+        <v>59.92</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>57.1</v>
+        <v>58.12</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34451,26 +34451,26 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>47.66</v>
+        <v>48.63</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>48.49</v>
+        <v>49.12</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>49.01</v>
+        <v>49.29</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>49.23</v>
+        <v>49.86</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>49.83</v>
+        <v>50.26</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>50.2</v>
+        <v>51.31</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34497,26 +34497,26 @@
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>47.72</v>
+        <v>49.38</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>48.24</v>
+        <v>49.89</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>48.15</v>
+        <v>51.12</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>48.16</v>
+        <v>52.87</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>48.32</v>
+        <v>53.63</v>
       </c>
       <c r="J194" s="3" t="n">
-        <v>47.72</v>
+        <v>55.24</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34543,26 +34543,26 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>59.81</v>
+        <v>61.01</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>60.07</v>
+        <v>61.8</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>60.56</v>
+        <v>62.77</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>60.94</v>
+        <v>63.93</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>61.1</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>61.65</v>
+        <v>67.3</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34589,26 +34589,26 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>44.06</v>
+        <v>46.66</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>46.03</v>
+        <v>48.02</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>47.15</v>
+        <v>50.06</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>48.74</v>
+        <v>52.23</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>50.09</v>
+        <v>54.04</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>50.57</v>
+        <v>56.97</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34635,26 +34635,26 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>63.94</v>
+        <v>63.55</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>64.02</v>
+        <v>64.27</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>64.88</v>
+        <v>64.17</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>64.98</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>65.19</v>
+        <v>63.86</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>64.56999999999999</v>
+        <v>65.42</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34681,26 +34681,26 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>58.59</v>
+        <v>59.41</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>58.42</v>
+        <v>60.17</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>58.65</v>
+        <v>61.46</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>59.2</v>
+        <v>61.88</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>58.67</v>
+        <v>63.14</v>
       </c>
       <c r="J198" s="3" t="n">
-        <v>59.19</v>
+        <v>65.78</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34727,26 +34727,26 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>64.98</v>
+        <v>65.09</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>64.89</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>64.22</v>
+        <v>63.85</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>62.95</v>
+        <v>62.29</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>60.95</v>
+        <v>60.99</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>59.96</v>
+        <v>62.34</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34773,26 +34773,26 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>56.17</v>
+        <v>58.12</v>
       </c>
       <c r="F200" s="3" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="I200" s="3" t="n">
         <v>58.15</v>
       </c>
-      <c r="G200" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H200" s="3" t="n">
-        <v>60.89</v>
-      </c>
-      <c r="I200" s="3" t="n">
-        <v>60.18</v>
-      </c>
       <c r="J200" s="3" t="n">
-        <v>58.1</v>
+        <v>57.14</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34819,26 +34819,26 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>60.55</v>
+        <v>65.58</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>63.26</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>62.8</v>
+        <v>67.52</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>61.4</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>58.65</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="J201" s="3" t="n">
-        <v>56.82</v>
+        <v>62.59</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34865,26 +34865,26 @@
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>57.76</v>
+        <v>58.53</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>57.25</v>
+        <v>58.84</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>57.03</v>
+        <v>59.53</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>56.82</v>
+        <v>59.78</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>55.77</v>
+        <v>59.53</v>
       </c>
       <c r="J202" s="3" t="n">
-        <v>55.41</v>
+        <v>57.3</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34911,26 +34911,26 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>57.64</v>
+        <v>61.85</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>60.29</v>
+        <v>63.19</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>60.98</v>
+        <v>62.21</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>58.92</v>
+        <v>60</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>55.38</v>
+        <v>57.92</v>
       </c>
       <c r="J203" s="3" t="n">
-        <v>53.26</v>
+        <v>56.68</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34957,26 +34957,26 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>65.8</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>65.3</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>63.5</v>
+        <v>64.37</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>60.47</v>
+        <v>62.47</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>56.64</v>
+        <v>60.45</v>
       </c>
       <c r="J204" s="3" t="n">
-        <v>54.85</v>
+        <v>57.71</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35003,26 +35003,26 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>63.05</v>
+        <v>63.86</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>63.68</v>
+        <v>64.86</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>64.75</v>
+        <v>65.92</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>65.84999999999999</v>
+        <v>68.59</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>68.54000000000001</v>
+        <v>72.91</v>
       </c>
       <c r="J205" s="3" t="n">
-        <v>72.93000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35049,26 +35049,26 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>44.71</v>
+        <v>45.03</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>45.79</v>
+        <v>47.23</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>48.32</v>
+        <v>49.84</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>51.15</v>
+        <v>52.49</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>53.43</v>
+        <v>55.31</v>
       </c>
       <c r="J206" s="3" t="n">
-        <v>54.92</v>
+        <v>59.26</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35095,26 +35095,26 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>58.62</v>
+        <v>58.34</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>58.49</v>
+        <v>58.47</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>58.78</v>
+        <v>59.36</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>59.96</v>
+        <v>61.39</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>62.39</v>
+        <v>64.91</v>
       </c>
       <c r="J207" s="3" t="n">
-        <v>66.28</v>
+        <v>71</v>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35141,26 +35141,26 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>52.32</v>
+        <v>54.49</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>55.05</v>
+        <v>57.57</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>58.13</v>
+        <v>60.85</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>61.15</v>
+        <v>64.77</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>64.06999999999999</v>
+        <v>68.81</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>66.81</v>
+        <v>74.13</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35187,26 +35187,26 @@
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>40.35</v>
+        <v>41.84</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>41.34</v>
+        <v>43.13</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>42.5</v>
+        <v>44.03</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>43.16</v>
+        <v>44.82</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>43.5</v>
+        <v>46.29</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>44.2</v>
+        <v>48.61</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35233,26 +35233,26 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>34.88</v>
+        <v>35.21</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>34.88</v>
+        <v>35.95</v>
       </c>
       <c r="G210" s="4" t="n">
-        <v>35.43</v>
+        <v>37.1</v>
       </c>
       <c r="H210" s="4" t="n">
-        <v>36.3</v>
+        <v>37.39</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>36.5</v>
+        <v>37.3</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>36.46</v>
+        <v>37.44</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35279,26 +35279,26 @@
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>40.4</v>
+        <v>42.57</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>41.26</v>
+        <v>43.29</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>41.33</v>
+        <v>44.25</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>41.28</v>
+        <v>45.32</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>40.77</v>
+        <v>47.68</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>41.96</v>
+        <v>47.36</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35325,26 +35325,26 @@
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>17.1</v>
+        <v>17.93</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G212" s="5" t="n">
-        <v>19.78</v>
+        <v>19.17</v>
+      </c>
+      <c r="G212" s="4" t="n">
+        <v>20.86</v>
       </c>
       <c r="H212" s="4" t="n">
-        <v>22.18</v>
+        <v>22.3</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>24.56</v>
+        <v>23.46</v>
       </c>
       <c r="J212" s="4" t="n">
-        <v>24.39</v>
+        <v>24.11</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35371,26 +35371,26 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>35.95</v>
+        <v>36.6</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>36.51</v>
+        <v>37.79</v>
       </c>
       <c r="G213" s="4" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="H213" s="4" t="n">
-        <v>39.55</v>
+        <v>39.45</v>
+      </c>
+      <c r="H213" s="3" t="n">
+        <v>40.69</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>40.92</v>
-      </c>
-      <c r="J213" s="3" t="n">
-        <v>41.25</v>
+        <v>41.6</v>
+      </c>
+      <c r="J213" s="4" t="n">
+        <v>39.97</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35417,26 +35417,26 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>21.74</v>
+        <v>21.17</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="G214" s="4" t="n">
-        <v>20.26</v>
+        <v>20.43</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>19.87</v>
       </c>
       <c r="H214" s="5" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>19.53</v>
+        <v>19.16</v>
       </c>
       <c r="J214" s="5" t="n">
-        <v>19.99</v>
+        <v>19.97</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35463,26 +35463,26 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>56.78</v>
+        <v>57.46</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>56.64</v>
+        <v>57.78</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>56.6</v>
+        <v>58.02</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>56.15</v>
+        <v>55.65</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>52.85</v>
+        <v>52.48</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>49.78</v>
+        <v>48.56</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35509,26 +35509,26 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>53.79</v>
+        <v>54.32</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>53.77</v>
+        <v>54.99</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>54.28</v>
+        <v>55.14</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>54.22</v>
+        <v>53.98</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>52.98</v>
+        <v>53.12</v>
       </c>
       <c r="J216" s="3" t="n">
-        <v>52.14</v>
+        <v>50.77</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35555,26 +35555,26 @@
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>45.71</v>
+        <v>43.1</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>43.02</v>
-      </c>
-      <c r="G217" s="3" t="n">
-        <v>40.85</v>
+        <v>40.9</v>
+      </c>
+      <c r="G217" s="4" t="n">
+        <v>39.23</v>
       </c>
       <c r="H217" s="4" t="n">
-        <v>39.26</v>
+        <v>37.62</v>
       </c>
       <c r="I217" s="4" t="n">
-        <v>37.83</v>
+        <v>36.3</v>
       </c>
       <c r="J217" s="4" t="n">
-        <v>36.71</v>
+        <v>35.69</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35601,26 +35601,26 @@
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>57.98</v>
+        <v>58.71</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>59.01</v>
+        <v>59.17</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>59.56</v>
+        <v>60.02</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>60.59</v>
+        <v>61.62</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>62.48</v>
+        <v>63.95</v>
       </c>
       <c r="J218" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35647,26 +35647,26 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>64.86</v>
+        <v>67.03</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>67.39</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>69.13</v>
+        <v>69.56</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>70.54000000000001</v>
+        <v>71</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>72.45</v>
+        <v>73.23</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35693,26 +35693,26 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>57.29</v>
+        <v>59</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>59.38</v>
+        <v>60.11</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>60.71</v>
+        <v>60.99</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>61.91</v>
+        <v>62.38</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>63.78</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>67.77</v>
+        <v>67.09</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35739,26 +35739,26 @@
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>60.29</v>
+        <v>58.41</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>59.48</v>
+        <v>57.45</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>59.06</v>
+        <v>57.07</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>59.37</v>
+        <v>57.45</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>60.72</v>
+        <v>58.64</v>
       </c>
       <c r="J221" s="3" t="n">
-        <v>62.82</v>
+        <v>60.17</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35785,26 +35785,26 @@
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>55.24</v>
+        <v>51.21</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>51.66</v>
+        <v>46.72</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="H222" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="I222" s="3" t="n">
-        <v>40.48</v>
+        <v>42.39</v>
+      </c>
+      <c r="H222" s="4" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="I222" s="4" t="n">
+        <v>37.28</v>
       </c>
       <c r="J222" s="4" t="n">
-        <v>39.56</v>
+        <v>37.69</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35831,26 +35831,26 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>59.77</v>
+        <v>60.23</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>60.3</v>
+        <v>59.79</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>60</v>
+        <v>58.59</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>58.88</v>
+        <v>56.52</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>57.05</v>
+        <v>54.09</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>54.21</v>
+        <v>51.15</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35877,26 +35877,26 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>57.21</v>
+        <v>53.12</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>53.37</v>
+        <v>49.53</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>49.9</v>
+        <v>46.3</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="I224" s="3" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="J224" s="3" t="n">
-        <v>41.19</v>
+        <v>42.74</v>
+      </c>
+      <c r="I224" s="4" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="J224" s="4" t="n">
+        <v>36.09</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35923,26 +35923,26 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>48.18</v>
+        <v>44.48</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="G225" s="3" t="n">
-        <v>41.96</v>
+        <v>41.11</v>
+      </c>
+      <c r="G225" s="4" t="n">
+        <v>38.42</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>39.73</v>
+        <v>35.35</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>37.39</v>
+        <v>33.02</v>
       </c>
       <c r="J225" s="4" t="n">
-        <v>36.11</v>
+        <v>31.53</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35969,26 +35969,26 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>62.47</v>
+        <v>58.59</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>59.33</v>
+        <v>54.13</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>55.3</v>
+        <v>49.74</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>51.55</v>
+        <v>45.43</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="J226" s="3" t="n">
-        <v>45.76</v>
+        <v>42.22</v>
+      </c>
+      <c r="J226" s="4" t="n">
+        <v>39.94</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36015,26 +36015,26 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>27.67</v>
+        <v>25.45</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>25.27</v>
+        <v>23.37</v>
       </c>
       <c r="G227" s="4" t="n">
-        <v>23.03</v>
-      </c>
-      <c r="H227" s="4" t="n">
-        <v>20.92</v>
+        <v>21.41</v>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>19.47</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>18.92</v>
+        <v>17.82</v>
       </c>
       <c r="J227" s="5" t="n">
-        <v>17.79</v>
+        <v>16.49</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36061,26 +36061,26 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>52.49</v>
+        <v>48.84</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>49.28</v>
+        <v>46.46</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>47.07</v>
+        <v>44.32</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I228" s="3" t="n">
-        <v>42.56</v>
+        <v>41.12</v>
+      </c>
+      <c r="I228" s="4" t="n">
+        <v>37.48</v>
       </c>
       <c r="J228" s="4" t="n">
-        <v>39.28</v>
+        <v>36.08</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36107,26 +36107,26 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>52.49</v>
+        <v>48.84</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>49.28</v>
+        <v>46.46</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>47.07</v>
+        <v>44.32</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I229" s="3" t="n">
-        <v>42.56</v>
+        <v>41.12</v>
+      </c>
+      <c r="I229" s="4" t="n">
+        <v>37.48</v>
       </c>
       <c r="J229" s="4" t="n">
-        <v>39.28</v>
+        <v>36.08</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36153,26 +36153,26 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>59.14</v>
+        <v>57.71</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>58.16</v>
+        <v>54.34</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>54.93</v>
+        <v>50.83</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>51.78</v>
+        <v>47.16</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>48.69</v>
+        <v>43.79</v>
       </c>
       <c r="J230" s="3" t="n">
-        <v>46.93</v>
+        <v>40.32</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36198,27 +36198,27 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E231" s="3" t="n">
-        <v>41.49</v>
+      <c r="E231" s="4" t="n">
+        <v>38.29</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>37.84</v>
+        <v>35.64</v>
       </c>
       <c r="G231" s="4" t="n">
-        <v>34.86</v>
+        <v>33.77</v>
       </c>
       <c r="H231" s="4" t="n">
-        <v>32.53</v>
+        <v>32.14</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>30.34</v>
+        <v>31.14</v>
       </c>
       <c r="J231" s="4" t="n">
-        <v>29.37</v>
+        <v>30.43</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36245,26 +36245,26 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>66.58</v>
+        <v>62.99</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>63.63</v>
+        <v>58.8</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>59.84</v>
+        <v>53.23</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>54.8</v>
+        <v>47.1</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>49.4</v>
+        <v>42.68</v>
       </c>
       <c r="J232" s="3" t="n">
-        <v>45.77</v>
+        <v>40.54</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36291,26 +36291,26 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>72.15000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>70.16</v>
+        <v>65.16</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>66.28</v>
+        <v>58.98</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>60.91</v>
+        <v>53.24</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>56.18</v>
+        <v>48.95</v>
       </c>
       <c r="J233" s="3" t="n">
-        <v>51.94</v>
+        <v>46.63</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36337,26 +36337,26 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>60.56</v>
+        <v>58.37</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>58.68</v>
+        <v>55.97</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>56.43</v>
+        <v>52.72</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>53.48</v>
+        <v>48.08</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>49.3</v>
+        <v>45.21</v>
       </c>
       <c r="J234" s="3" t="n">
-        <v>47.09</v>
+        <v>44.12</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36383,26 +36383,26 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>34.59</v>
+        <v>31.54</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>31.72</v>
+        <v>28.87</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>29.15</v>
+        <v>26.94</v>
       </c>
       <c r="H235" s="4" t="n">
-        <v>27.39</v>
+        <v>24.7</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>25.54</v>
+        <v>22.78</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>24.39</v>
+        <v>21.07</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36429,26 +36429,26 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>73.73999999999999</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>72.04000000000001</v>
+        <v>68.05</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>68.7</v>
+        <v>63.55</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>64.48999999999999</v>
+        <v>58.52</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>59.94</v>
+        <v>53.86</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>55.71</v>
+        <v>49.7</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36475,26 +36475,26 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>73.73</v>
+        <v>71.44</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>71.69</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>67.95999999999999</v>
+        <v>63.23</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>63.4</v>
+        <v>59.55</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>59.68</v>
+        <v>55.3</v>
       </c>
       <c r="J237" s="3" t="n">
-        <v>54.65</v>
+        <v>51.46</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36521,26 +36521,26 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>60.4</v>
+        <v>59.22</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>60.42</v>
+        <v>58.47</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>60.3</v>
+        <v>56.69</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>59.42</v>
+        <v>53.9</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>57.94</v>
+        <v>51.17</v>
       </c>
       <c r="J238" s="3" t="n">
-        <v>56.07</v>
+        <v>47</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36567,26 +36567,26 @@
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>55.13</v>
+        <v>52.77</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>53.75</v>
+        <v>50.7</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>52.12</v>
+        <v>47.59</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>49.7</v>
+        <v>45.38</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>48.55</v>
+        <v>43.81</v>
       </c>
       <c r="J239" s="3" t="n">
-        <v>47.53</v>
+        <v>40.25</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36613,26 +36613,26 @@
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>50.2</v>
+        <v>47.57</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>47.37</v>
+        <v>45.32</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>45.03</v>
+        <v>44.13</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>43.7</v>
+        <v>42.74</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>42.14</v>
+        <v>41.43</v>
       </c>
       <c r="J240" s="3" t="n">
-        <v>40.77</v>
+        <v>40.79</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36659,26 +36659,26 @@
         </is>
       </c>
       <c r="E241" s="5" t="n">
-        <v>17</v>
+        <v>17.87</v>
       </c>
       <c r="F241" s="5" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="G241" s="5" t="n">
-        <v>19.74</v>
+        <v>19.09</v>
+      </c>
+      <c r="G241" s="4" t="n">
+        <v>20.64</v>
       </c>
       <c r="H241" s="4" t="n">
-        <v>22</v>
+        <v>21.93</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>24.25</v>
+        <v>23.09</v>
       </c>
       <c r="J241" s="4" t="n">
-        <v>24.02</v>
+        <v>23.94</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36705,26 +36705,26 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>21.5</v>
+        <v>20.93</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>20.73</v>
-      </c>
-      <c r="G242" s="4" t="n">
-        <v>20.02</v>
+        <v>20.19</v>
+      </c>
+      <c r="G242" s="5" t="n">
+        <v>19.65</v>
       </c>
       <c r="H242" s="5" t="n">
-        <v>19.57</v>
+        <v>19.2</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>19.34</v>
+        <v>18.99</v>
       </c>
       <c r="J242" s="5" t="n">
-        <v>19.82</v>
+        <v>19.8</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36751,26 +36751,26 @@
         </is>
       </c>
       <c r="E243" s="3" t="n">
-        <v>45.05</v>
+        <v>42.35</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>42.29</v>
-      </c>
-      <c r="G243" s="3" t="n">
-        <v>40.05</v>
+        <v>40.08</v>
+      </c>
+      <c r="G243" s="4" t="n">
+        <v>38.41</v>
       </c>
       <c r="H243" s="4" t="n">
-        <v>38.45</v>
+        <v>36.84</v>
       </c>
       <c r="I243" s="4" t="n">
-        <v>37.07</v>
+        <v>35.54</v>
       </c>
       <c r="J243" s="4" t="n">
-        <v>35.97</v>
+        <v>34.96</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36796,27 +36796,27 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E244" s="4" t="n">
-        <v>39.85</v>
+      <c r="E244" s="3" t="n">
+        <v>40.51</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>40.89</v>
+        <v>40.46</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>41.15</v>
-      </c>
-      <c r="H244" s="3" t="n">
-        <v>41.31</v>
-      </c>
-      <c r="I244" s="3" t="n">
-        <v>41.21</v>
+        <v>40.12</v>
+      </c>
+      <c r="H244" s="4" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="I244" s="4" t="n">
+        <v>37.73</v>
       </c>
       <c r="J244" s="4" t="n">
-        <v>39.21</v>
+        <v>35.87</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36843,26 +36843,26 @@
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>55.63</v>
+        <v>58.53</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>57.47</v>
+        <v>59.9</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>58.33</v>
+        <v>61.38</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>58.94</v>
+        <v>63.95</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>60.2</v>
+        <v>67.84</v>
       </c>
       <c r="J245" s="3" t="n">
-        <v>65.56999999999999</v>
+        <v>69.62</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36889,26 +36889,26 @@
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>55.42</v>
+        <v>58.64</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>57.63</v>
+        <v>60.3</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>58.85</v>
+        <v>60.91</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>58.79</v>
+        <v>62.49</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>59.27</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="J246" s="3" t="n">
-        <v>63.36</v>
+        <v>65.94</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36935,26 +36935,26 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>62.89</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>66.58</v>
+        <v>70.56</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>69.76000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>71.84</v>
+        <v>73.47</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>71.95</v>
+        <v>74.06</v>
       </c>
       <c r="J247" s="3" t="n">
-        <v>73.62</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36981,26 +36981,26 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>26.4</v>
+        <v>25.32</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>25.38</v>
+        <v>24.59</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>24.86</v>
+        <v>24.19</v>
       </c>
       <c r="H248" s="4" t="n">
-        <v>24.84</v>
+        <v>24.75</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>25.77</v>
+        <v>25.05</v>
       </c>
       <c r="J248" s="4" t="n">
-        <v>24.75</v>
+        <v>27.94</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37027,26 +37027,26 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>32.74</v>
+        <v>33.1</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>32.68</v>
+        <v>34.17</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>33.7</v>
+        <v>35.72</v>
       </c>
       <c r="H249" s="4" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="I249" s="4" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="J249" s="4" t="n">
-        <v>39.44</v>
+        <v>38.74</v>
+      </c>
+      <c r="I249" s="3" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="J249" s="3" t="n">
+        <v>49.33</v>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37073,26 +37073,26 @@
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>54.84</v>
+        <v>52.36</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>52.99</v>
+        <v>51.01</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>52.12</v>
+        <v>50.94</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>52.8</v>
+        <v>52.74</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>55.72</v>
+        <v>54.68</v>
       </c>
       <c r="J250" s="3" t="n">
-        <v>57.58</v>
+        <v>59.6</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37119,26 +37119,26 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>27.88</v>
+        <v>28.16</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>27.56</v>
+        <v>28.46</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>27.77</v>
+        <v>28.39</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>27.53</v>
+        <v>29.84</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>28.49</v>
+        <v>31.27</v>
       </c>
       <c r="J251" s="4" t="n">
-        <v>28.26</v>
+        <v>36.71</v>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37165,26 +37165,26 @@
         </is>
       </c>
       <c r="E252" s="3" t="n">
-        <v>50.76</v>
+        <v>52.32</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>51.76</v>
+        <v>55.28</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>54.52</v>
+        <v>58.55</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>57.43</v>
+        <v>62.45</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>60.52</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J252" s="3" t="n">
-        <v>63.55</v>
+        <v>74.95</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37211,26 +37211,26 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>33.65</v>
+        <v>35.19</v>
       </c>
       <c r="F253" s="4" t="n">
-        <v>35.36</v>
+        <v>37.34</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>37.83</v>
+        <v>39.56</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>40.57</v>
+        <v>42.06</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>43.79</v>
+        <v>44.12</v>
       </c>
       <c r="J253" s="3" t="n">
-        <v>44.43</v>
+        <v>49.51</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37257,26 +37257,26 @@
         </is>
       </c>
       <c r="E254" s="3" t="n">
-        <v>46.69</v>
+        <v>49.25</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>48.28</v>
+        <v>51.85</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>50.48</v>
+        <v>54.4</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>52.21</v>
+        <v>58.15</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>54.61</v>
+        <v>63.4</v>
       </c>
       <c r="J254" s="3" t="n">
-        <v>58.71</v>
+        <v>72.23</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37303,26 +37303,26 @@
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>60.55</v>
+        <v>60.8</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>60.84</v>
+        <v>62.23</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>62.42</v>
+        <v>63.62</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>63.93</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="I255" s="3" t="n">
-        <v>67.09</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="J255" s="3" t="n">
-        <v>70.06</v>
+        <v>77.58</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37349,26 +37349,26 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>35.15</v>
+        <v>37.65</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>36.65</v>
-      </c>
-      <c r="G256" s="4" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="H256" s="4" t="n">
-        <v>38.99</v>
-      </c>
-      <c r="I256" s="4" t="n">
-        <v>39.96</v>
+        <v>39.68</v>
+      </c>
+      <c r="G256" s="3" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="H256" s="3" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>44.64</v>
       </c>
       <c r="J256" s="3" t="n">
-        <v>40.04</v>
+        <v>49.22</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37395,26 +37395,26 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>25.32</v>
+        <v>27.02</v>
       </c>
       <c r="F257" s="4" t="n">
-        <v>26.1</v>
+        <v>28.49</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>27.35</v>
+        <v>30.57</v>
       </c>
       <c r="H257" s="4" t="n">
-        <v>28.89</v>
+        <v>33.56</v>
       </c>
       <c r="I257" s="4" t="n">
-        <v>30.75</v>
-      </c>
-      <c r="J257" s="4" t="n">
-        <v>32.51</v>
+        <v>37.02</v>
+      </c>
+      <c r="J257" s="3" t="n">
+        <v>41.74</v>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37441,26 +37441,26 @@
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>37.1</v>
+        <v>37.14</v>
       </c>
       <c r="F258" s="4" t="n">
-        <v>37.43</v>
+        <v>37.79</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>38.4</v>
+        <v>38.82</v>
       </c>
       <c r="H258" s="4" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="I258" s="4" t="n">
         <v>39.82</v>
       </c>
-      <c r="I258" s="3" t="n">
-        <v>41.16</v>
-      </c>
       <c r="J258" s="3" t="n">
-        <v>41.42</v>
+        <v>41.36</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37487,26 +37487,26 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>61.72</v>
+        <v>62.34</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>61.97</v>
+        <v>62.53</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>62.11</v>
+        <v>63.26</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>62.7</v>
+        <v>65.87</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>69.31</v>
       </c>
       <c r="J259" s="3" t="n">
-        <v>68.08</v>
+        <v>74.17</v>
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37533,26 +37533,26 @@
         </is>
       </c>
       <c r="E260" s="4" t="n">
-        <v>33.6</v>
+        <v>33.87</v>
       </c>
       <c r="F260" s="4" t="n">
-        <v>34.39</v>
+        <v>34.27</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>35.28</v>
+        <v>35.21</v>
       </c>
       <c r="H260" s="4" t="n">
-        <v>36.91</v>
+        <v>36.07</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>38.83</v>
+        <v>36.43</v>
       </c>
       <c r="J260" s="4" t="n">
-        <v>39.41</v>
+        <v>36.64</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37579,26 +37579,26 @@
         </is>
       </c>
       <c r="E261" s="3" t="n">
-        <v>46</v>
+        <v>44.64</v>
       </c>
       <c r="F261" s="3" t="n">
-        <v>44.87</v>
+        <v>44.74</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>45.24</v>
+        <v>45.99</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>46.87</v>
+        <v>49.15</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>50.48</v>
+        <v>52.77</v>
       </c>
       <c r="J261" s="3" t="n">
-        <v>52.92</v>
+        <v>60.71</v>
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37625,26 +37625,26 @@
         </is>
       </c>
       <c r="E262" s="3" t="n">
-        <v>49.39</v>
+        <v>49.45</v>
       </c>
       <c r="F262" s="3" t="n">
-        <v>49.73</v>
+        <v>50.43</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>51.06</v>
+        <v>51.91</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>53.01</v>
+        <v>55</v>
       </c>
       <c r="I262" s="3" t="n">
-        <v>56.86</v>
+        <v>58.97</v>
       </c>
       <c r="J262" s="3" t="n">
-        <v>60.03</v>
+        <v>64.44</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37671,26 +37671,26 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.83</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>72.16</v>
+        <v>73.52</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>74.05</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>74.23999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>74.05</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="J263" s="3" t="n">
-        <v>70.78</v>
+        <v>71.64</v>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37717,26 +37717,26 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>50.21</v>
+        <v>50.05</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>49.97</v>
+        <v>50.73</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>50.63</v>
+        <v>52.23</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>52.04</v>
+        <v>54.01</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>53.68</v>
+        <v>55.21</v>
       </c>
       <c r="J264" s="3" t="n">
-        <v>55.26</v>
+        <v>54.08</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37763,26 +37763,26 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>57.36</v>
+        <v>56.57</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>56.48</v>
+        <v>56.58</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>56.5</v>
+        <v>56.93</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>56.85</v>
+        <v>57.68</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>57.56</v>
+        <v>58.5</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>58.25</v>
+        <v>59.03</v>
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37809,26 +37809,26 @@
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>50.68</v>
+        <v>51.33</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>50.78</v>
+        <v>51.92</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>51.16</v>
+        <v>53.11</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>52.01</v>
+        <v>54.92</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>53.32</v>
+        <v>56.53</v>
       </c>
       <c r="J266" s="3" t="n">
-        <v>55.03</v>
+        <v>54.29</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37855,26 +37855,26 @@
         </is>
       </c>
       <c r="E267" s="3" t="n">
-        <v>59.93</v>
+        <v>58.7</v>
       </c>
       <c r="F267" s="3" t="n">
-        <v>57.7</v>
+        <v>56.46</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>54.92</v>
+        <v>54.13</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>51.81</v>
+        <v>52.34</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>49.05</v>
+        <v>50.06</v>
       </c>
       <c r="J267" s="3" t="n">
-        <v>46.91</v>
+        <v>49.21</v>
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37901,26 +37901,26 @@
         </is>
       </c>
       <c r="E268" s="4" t="n">
-        <v>37.96</v>
+        <v>36.63</v>
       </c>
       <c r="F268" s="4" t="n">
-        <v>36.27</v>
+        <v>35.94</v>
       </c>
       <c r="G268" s="4" t="n">
         <v>35.52</v>
       </c>
       <c r="H268" s="4" t="n">
-        <v>34.92</v>
+        <v>35.69</v>
       </c>
       <c r="I268" s="4" t="n">
-        <v>34.75</v>
+        <v>36.2</v>
       </c>
       <c r="J268" s="4" t="n">
-        <v>35.07</v>
+        <v>35.76</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25604,32 +25604,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>W36</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>W37</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -25665,22 +25665,22 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>65.06</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>66.97</v>
+        <v>64.06</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>66.87</v>
+        <v>62.8</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>66.5</v>
+        <v>61.73</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>66.06</v>
+        <v>60.5</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>63.94</v>
+        <v>58.02</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -25711,22 +25711,22 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>49.55</v>
+        <v>51.49</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>50.24</v>
+        <v>53.5</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>51.66</v>
+        <v>56</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>53.68</v>
+        <v>57.18</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>54.49</v>
+        <v>56.96</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>56.02</v>
+        <v>57.05</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -25757,22 +25757,22 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>61.08</v>
+        <v>65.22</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>61.81</v>
+        <v>66.67</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>62.51</v>
+        <v>68.95</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>63.35</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>64.48</v>
+        <v>74.47</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>66.29000000000001</v>
+        <v>73.22</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -25803,22 +25803,22 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>62.76</v>
+        <v>67.34</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>62.93</v>
+        <v>68.27</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>63.07</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>62.51</v>
+        <v>69.47</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>62.19</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>63.49</v>
+        <v>69.11</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -25849,22 +25849,22 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>72.88</v>
+        <v>73.89</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>73.29000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>72.59</v>
+        <v>72.98</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>70.8</v>
+        <v>71.16</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.52</v>
+        <v>68.05</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>63.53</v>
+        <v>63.83</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -25895,22 +25895,22 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>66.26000000000001</v>
+        <v>68.53</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>69.58</v>
+        <v>70.55</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>72.26000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>72.98</v>
+        <v>69.78</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>73.81999999999999</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -25941,22 +25941,22 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>67.33</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>66.34</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>67.69</v>
+        <v>71.75</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>69.45999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>70.69</v>
+        <v>74.25</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>71.3</v>
+        <v>72.3</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -25987,22 +25987,22 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>38.7</v>
+        <v>36.37</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>38.23</v>
+        <v>36.46</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>42.2</v>
+        <v>36.53</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>38.27</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>42.08</v>
+        <v>41.09</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -26033,22 +26033,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>65.08</v>
+        <v>67.09</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>65.98</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>65.97</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>65.25</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>64.34999999999999</v>
+        <v>67.56</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -26079,22 +26079,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>49.5</v>
+        <v>49.66</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>50.29</v>
+        <v>51.06</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>51.99</v>
+        <v>52.64</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>53.96</v>
+        <v>53.4</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>55.29</v>
+        <v>52.76</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>54.08</v>
+        <v>50.35</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -26125,22 +26125,22 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>60.43</v>
+        <v>61.11</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>60.48</v>
+        <v>61.56</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>60.61</v>
+        <v>62.67</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>61.21</v>
+        <v>63.98</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>61.81</v>
+        <v>64.83</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -26171,22 +26171,22 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>51.54</v>
+        <v>51.43</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>52.22</v>
+        <v>52.33</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>53.48</v>
+        <v>53.52</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>55.32</v>
+        <v>54.16</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>56.96</v>
+        <v>52.78</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>54.66</v>
+        <v>49.33</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -26217,22 +26217,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>62.84</v>
+        <v>63.75</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>63.68</v>
+        <v>63.44</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>63.41</v>
+        <v>62.71</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>62.41</v>
+        <v>61.17</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>60.3</v>
+        <v>59.17</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>59.21</v>
+        <v>58.21</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -26263,22 +26263,22 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>61.46</v>
+        <v>63.1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>62.44</v>
+        <v>63.94</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>63.08</v>
+        <v>64.66</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>63.24</v>
+        <v>63.22</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>60.76</v>
+        <v>59.99</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>58.34</v>
+        <v>57.77</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -26309,22 +26309,22 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>61.57</v>
+        <v>63.58</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>62.19</v>
+        <v>63.19</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>60.96</v>
+        <v>63.36</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>59.63</v>
+        <v>63.24</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>57.11</v>
+        <v>60.95</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>54.6</v>
+        <v>59.77</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -26355,22 +26355,22 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>52.43</v>
+        <v>51.36</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>49.48</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45.12</v>
+        <v>45.77</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>43.82</v>
+        <v>46.55</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>44.14</v>
+        <v>47.24</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>45.44</v>
+        <v>48.14</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -26401,22 +26401,22 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>58.73</v>
+        <v>57.3</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>56.5</v>
+        <v>53.79</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>52.9</v>
+        <v>50.83</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>49.61</v>
+        <v>48.17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>46.18</v>
+        <v>45.2</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>44.92</v>
+        <v>42.93</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -26447,22 +26447,22 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>63.88</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>65.26000000000001</v>
+        <v>67.66</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>65.95</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>66.8</v>
+        <v>70.58</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>65.77</v>
+        <v>68</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -26493,22 +26493,22 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>61.97</v>
+        <v>62.9</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>61.72</v>
+        <v>62.02</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>60.22</v>
+        <v>61.25</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>58.5</v>
+        <v>60.48</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>56.35</v>
+        <v>59.62</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>54.91</v>
+        <v>56.7</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -26539,22 +26539,22 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>59.28</v>
+        <v>62.19</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>59.51</v>
+        <v>62.01</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>57.95</v>
+        <v>63.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>57.11</v>
+        <v>64.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>55.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>54.43</v>
+        <v>62.98</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -26585,22 +26585,22 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>58.54</v>
+        <v>58.16</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>59.89</v>
+        <v>58.77</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>61.37</v>
+        <v>59.93</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>63.92</v>
+        <v>61.74</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>67.78</v>
+        <v>62.07</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>69.56</v>
+        <v>59.99</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -26631,22 +26631,22 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>56.97</v>
+        <v>58.85</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>60.11</v>
+        <v>61.87</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>63.57</v>
+        <v>63.95</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>66.29000000000001</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>68.70999999999999</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>69.51000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -26677,22 +26677,22 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>66.86</v>
+        <v>69.31</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>70.12</v>
+        <v>71.31</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>71.39</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>72.97</v>
+        <v>71.19</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>73.58</v>
+        <v>70.53</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>73.36</v>
+        <v>69.14</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -26723,22 +26723,22 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>72.47</v>
+        <v>75.38</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>76.48999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>78.73</v>
+        <v>76.48</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>78.81</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>78.45</v>
+        <v>73.09</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>77.06999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -26769,22 +26769,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>69.7</v>
+        <v>66.23</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>66.92</v>
+        <v>61.75</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>62.89</v>
+        <v>56.36</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>58.11</v>
+        <v>51.01</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>53.37</v>
+        <v>47.78</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>49.38</v>
+        <v>46.61</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -26815,22 +26815,22 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>55.16</v>
+        <v>54.62</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>53.52</v>
+        <v>52.11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>50.82</v>
+        <v>50.98</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>49.45</v>
+        <v>50.08</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>48.28</v>
+        <v>49.22</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>47.98</v>
+        <v>48.5</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -26861,22 +26861,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>71.16</v>
+        <v>67.52</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>67.39</v>
+        <v>62.74</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>62.68</v>
+        <v>59.04</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>59.09</v>
+        <v>54.76</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>54.96</v>
+        <v>50.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>51.41</v>
+        <v>47.38</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -26907,22 +26907,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>59.65</v>
+        <v>57.76</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>58.93</v>
+        <v>55.53</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>57.22</v>
+        <v>51.96</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>54.52</v>
+        <v>47.87</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>51.77</v>
+        <v>43.79</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>47.68</v>
+        <v>40.92</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -26953,22 +26953,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>47.96</v>
+        <v>45.62</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>45.88</v>
+        <v>43.01</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43.42</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>41.21</v>
+        <v>40.46</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>38.02</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>39.46</v>
+        <v>35.69</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>36.8</v>
+        <v>34.17</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -26999,22 +26999,22 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>52.57</v>
+        <v>51.27</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>50.71</v>
+        <v>49.5</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>49.09</v>
+        <v>47.31</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>47.41</v>
+        <v>45.6</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>46.75</v>
+        <v>44.81</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46.92</v>
+        <v>46.25</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -27045,22 +27045,22 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>53.83</v>
+        <v>52.49</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>53.32</v>
+        <v>51.29</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>52.29</v>
+        <v>49.36</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>50.56</v>
+        <v>46.93</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>48.26</v>
+        <v>45.77</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>45.94</v>
+        <v>45.54</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -27091,22 +27091,22 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>42.6</v>
+        <v>43.42</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>43.31</v>
+        <v>44.53</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>44.27</v>
+        <v>45.87</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>45.33</v>
+        <v>48.74</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>47.69</v>
+        <v>50.15</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>47.37</v>
+        <v>49.59</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -27137,22 +27137,22 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>18.03</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>19.28</v>
+        <v>19.23</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>20.99</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20.96</v>
+        <v>22.48</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>22.39</v>
+        <v>23.57</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23.55</v>
+        <v>24.28</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>24.2</v>
+        <v>24.98</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -27183,22 +27183,22 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>39.54</v>
+        <v>38.21</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>42.02</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>40.78</v>
+        <v>43.48</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>41.68</v>
+        <v>42.77</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>40.06</v>
+        <v>42.53</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -27229,22 +27229,22 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>21.17</v>
+        <v>20.52</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>20.42</v>
+        <v>20</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>19.86</v>
+        <v>19.52</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>19.38</v>
+        <v>19.1</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>19.96</v>
+        <v>19.64</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>20.95</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -27275,22 +27275,22 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>37.89</v>
+        <v>38.97</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>38.08</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>38.31</v>
+        <v>39.66</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>42.55</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -27321,22 +27321,22 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>54.32</v>
+        <v>55.86</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>55</v>
+        <v>56.47</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>55.15</v>
+        <v>55.75</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>53.98</v>
+        <v>55.45</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>53.12</v>
+        <v>53.68</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>50.77</v>
+        <v>52.05</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -27367,22 +27367,22 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>40.95</v>
+        <v>40.78</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>39.01</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>39.29</v>
+        <v>37.25</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>37.7</v>
+        <v>35.63</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>36.41</v>
+        <v>34.79</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>35.8</v>
+        <v>34.07</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -27413,22 +27413,22 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>40.46</v>
+        <v>41.08</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>40.36</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>40</v>
+        <v>41.14</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>40.76</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>39.16</v>
+        <v>39.58</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>37.74</v>
+        <v>37.97</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>36.13</v>
+        <v>36.59</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -27459,22 +27459,22 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>58.23</v>
+        <v>56.86</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>58.67</v>
+        <v>56.78</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>59.49</v>
+        <v>57.03</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>61.07</v>
+        <v>57.39</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>63.36</v>
+        <v>58.33</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>67.22</v>
+        <v>59.26</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -27505,22 +27505,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>66.87</v>
+        <v>66.19</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>68.33</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>69.36</v>
+        <v>66.14</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>70.78</v>
+        <v>66.62</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>73</v>
+        <v>66.64</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>74.98</v>
+        <v>67.55</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -27551,22 +27551,22 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>58.75</v>
+        <v>58.34</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>59.85</v>
+        <v>58.42</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>60.71</v>
+        <v>58.68</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>62.08</v>
+        <v>59.54</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>64.65000000000001</v>
+        <v>60.48</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>66.76000000000001</v>
+        <v>62.41</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -27597,22 +27597,22 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>58.42</v>
+        <v>55.64</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>57.46</v>
+        <v>54.32</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>57.07</v>
+        <v>53.25</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>57.45</v>
+        <v>52.45</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>58.64</v>
+        <v>52.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>60.17</v>
+        <v>55.32</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -27643,22 +27643,22 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>57.95</v>
+        <v>57.79</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>59.47</v>
+        <v>58.52</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>61.04</v>
+        <v>59.75</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>63.62</v>
+        <v>61.61</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>67.47</v>
+        <v>62</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>69.27</v>
+        <v>60.07</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -27689,22 +27689,22 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>60.42</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>61.2</v>
+        <v>66.22</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>61.88</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>62.73</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>63.93</v>
+        <v>74.56</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>66</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -27735,22 +27735,22 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>57.34</v>
+        <v>53.96</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>54.65</v>
+        <v>50.51</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>51.64</v>
+        <v>48.04</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>49.79</v>
+        <v>46.98</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>49.47</v>
+        <v>47.49</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>50.97</v>
+        <v>47.94</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -27781,22 +27781,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>53.23</v>
+        <v>52.2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>52.47</v>
+        <v>51.12</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>51.66</v>
+        <v>50.14</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>51.11</v>
+        <v>49.24</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>50.87</v>
+        <v>47.72</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>48.67</v>
+        <v>46.4</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -27827,22 +27827,22 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>48.76</v>
+        <v>52.93</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>50.02</v>
+        <v>55.29</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>51.85</v>
+        <v>58.3</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>53.67</v>
+        <v>62.09</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>55.47</v>
+        <v>65.27</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>58.48</v>
+        <v>65.73</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -27873,22 +27873,22 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>73.14</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>70.28</v>
+        <v>65.88</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>65.73</v>
+        <v>60.52</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>60.16</v>
+        <v>57.41</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>56.68</v>
+        <v>57.03</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>56.44</v>
+        <v>57.7</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -27919,22 +27919,22 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>63.2</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>63.28</v>
+        <v>68.52</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>63.3</v>
+        <v>68.8</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>62.62</v>
+        <v>69.52</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>62.19</v>
+        <v>69.45</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>63.46</v>
+        <v>69.22</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -27965,22 +27965,22 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>69.7</v>
+        <v>66.23</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>66.91</v>
+        <v>61.74</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>62.88</v>
+        <v>56.37</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>58.11</v>
+        <v>51.04</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>53.38</v>
+        <v>47.81</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>49.39</v>
+        <v>46.63</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -28011,22 +28011,22 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>54.93</v>
+        <v>54.43</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>53.33</v>
+        <v>51.94</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>50.65</v>
+        <v>50.85</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>49.32</v>
+        <v>49.99</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>48.19</v>
+        <v>49.18</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>47.94</v>
+        <v>48.5</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -28057,22 +28057,22 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>70.91</v>
+        <v>67.31</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>67.18000000000001</v>
+        <v>62.57</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>62.51</v>
+        <v>58.93</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>58.98</v>
+        <v>54.68</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>54.88</v>
+        <v>50.66</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>51.36</v>
+        <v>47.4</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -28103,22 +28103,22 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>60.13</v>
+        <v>58.58</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>59.66</v>
+        <v>56.66</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>58.22</v>
+        <v>53.58</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>55.89</v>
+        <v>49.87</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>53.4</v>
+        <v>46.18</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>49.72</v>
+        <v>43.55</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -28149,22 +28149,22 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>48.66</v>
+        <v>46.29</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>46.55</v>
+        <v>43.62</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>44.04</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>41.74</v>
+        <v>40.98</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>38.39</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>39.86</v>
+        <v>36.01</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>37.14</v>
+        <v>34.5</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -28195,22 +28195,22 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>52.1</v>
+        <v>50.82</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>50.3</v>
+        <v>49.12</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>48.76</v>
+        <v>47.02</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>47.21</v>
+        <v>45.45</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>46.68</v>
+        <v>44.77</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>46.92</v>
+        <v>46.29</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -28241,22 +28241,22 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>58.24</v>
+        <v>56.94</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>58.61</v>
+        <v>56.83</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>59.33</v>
+        <v>55.99</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>59.62</v>
+        <v>54.4</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>59.38</v>
+        <v>51.64</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>57.19</v>
+        <v>47.18</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -28287,22 +28287,22 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>62.23</v>
+        <v>64.47</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>63.53</v>
+        <v>63.89</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>62.58</v>
+        <v>62.36</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>60.39</v>
+        <v>61.09</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>58.28</v>
+        <v>59.57</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>56.95</v>
+        <v>54.41</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -28333,22 +28333,22 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>53.61</v>
+        <v>54.96</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>53.83</v>
+        <v>55.07</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>53.6</v>
+        <v>54.99</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>52.85</v>
+        <v>55.25</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>52.33</v>
+        <v>55.8</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>52.98</v>
+        <v>56.46</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -28379,22 +28379,22 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>66.91</v>
+        <v>65.39</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>65.94</v>
+        <v>63.4</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>64.29000000000001</v>
+        <v>60.97</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>62.42</v>
+        <v>58.2</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>60.41</v>
+        <v>55.26</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>57.66</v>
+        <v>50.1</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -28425,22 +28425,22 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>44.76</v>
+        <v>47.12</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>46.85</v>
+        <v>49.87</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>49.51</v>
+        <v>52.8</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>52.23</v>
+        <v>56.04</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>55</v>
+        <v>60.72</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>58.95</v>
+        <v>65</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -28471,22 +28471,22 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>54.93</v>
+        <v>57.66</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>57.73</v>
+        <v>60.66</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>60.78</v>
+        <v>64.47</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>64.61</v>
+        <v>68.5</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>68.55</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>73.91</v>
+        <v>78.22</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -28517,22 +28517,22 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>63.67</v>
+        <v>63.99</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>64.56</v>
+        <v>64.44</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>65.61</v>
+        <v>66.34</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>68.33</v>
+        <v>69.56</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>72.69</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>78.41</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -28563,22 +28563,22 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>58.79</v>
+        <v>58.81</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>59.1</v>
+        <v>59.53</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>60.12</v>
+        <v>61.11</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>62.16</v>
+        <v>63.88</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>65.64</v>
+        <v>68.89</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>71.66</v>
+        <v>73.31</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -28609,22 +28609,22 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>63.48</v>
+        <v>63.44</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>63.59</v>
+        <v>63.99</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>64.43000000000001</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>66.88</v>
+        <v>69.92</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>71.31</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>79.06999999999999</v>
+        <v>76.66</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>83.11</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -28655,22 +28655,22 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>47.74</v>
+        <v>45.35</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>45.54</v>
+        <v>44.13</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>44.39</v>
+        <v>42.65</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>43.05</v>
+        <v>41.18</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>41.82</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>41.27</v>
+        <v>40.49</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>39.49</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
@@ -28701,22 +28701,22 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>35.23</v>
+        <v>37.06</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>35.97</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>37.13</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>37.41</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>37.31</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>37.44</v>
+        <v>39.01</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>42.23</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -28747,22 +28747,22 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>18.51</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>19.77</v>
+        <v>19.74</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>21.49</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>21.44</v>
+        <v>22.99</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>22.86</v>
+        <v>24.11</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>24.04</v>
+        <v>24.87</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>24.77</v>
+        <v>25.58</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
@@ -28793,22 +28793,22 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>36.64</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>39.47</v>
+        <v>38.13</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>41.97</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>40.72</v>
+        <v>43.43</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>41.63</v>
+        <v>42.73</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>40.01</v>
+        <v>42.51</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -28839,22 +28839,22 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>21.18</v>
+        <v>20.54</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>20.43</v>
+        <v>20.01</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>19.88</v>
+        <v>19.54</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>19.4</v>
+        <v>19.12</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="J71" s="5" t="n">
-        <v>19.98</v>
+        <v>19.66</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>20.97</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
@@ -28885,22 +28885,22 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>37.69</v>
+        <v>38.74</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>37.84</v>
-      </c>
-      <c r="I72" s="4" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="J72" s="4" t="n">
-        <v>38.11</v>
+        <v>39.38</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>42.3</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -28931,22 +28931,22 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>54.33</v>
+        <v>55.87</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>55.01</v>
+        <v>56.47</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>55.16</v>
+        <v>55.75</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>53.99</v>
+        <v>55.45</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>53.13</v>
+        <v>53.68</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>50.77</v>
+        <v>52.06</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
@@ -28977,22 +28977,22 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>43.15</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>40.96</v>
+        <v>40.79</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>39.03</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>39.31</v>
+        <v>37.27</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>37.72</v>
+        <v>35.66</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>36.43</v>
+        <v>34.82</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>35.83</v>
+        <v>34.1</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -29023,22 +29023,22 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>40.69</v>
+        <v>41.25</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>40.55</v>
+        <v>41.26</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>40.17</v>
+        <v>40.89</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>39.35</v>
+        <v>39.79</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>38.01</v>
+        <v>38.28</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>36.49</v>
+        <v>37</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
@@ -29069,22 +29069,22 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>29.8</v>
+        <v>29.98</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>29.89</v>
+        <v>30.29</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>30.22</v>
+        <v>31.05</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>31.05</v>
+        <v>32.55</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>32.6</v>
+        <v>33.44</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>31.81</v>
+        <v>33.31</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -29115,22 +29115,22 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>57.62</v>
+        <v>56.21</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>58.04</v>
+        <v>56.08</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>58.82</v>
+        <v>56.32</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>60.4</v>
+        <v>56.65</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>62.68</v>
+        <v>57.53</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>66.55</v>
+        <v>58.36</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
@@ -29161,22 +29161,22 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>36.07</v>
+        <v>35.14</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>35.74</v>
+        <v>34.09</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>34.96</v>
+        <v>33.07</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>34.32</v>
+        <v>32.01</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>33.73</v>
+        <v>31.82</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>35.98</v>
+        <v>32.61</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -29207,22 +29207,22 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>66.62</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>68.06</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>65.86</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>70.56</v>
+        <v>66.33</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>72.79000000000001</v>
+        <v>66.33</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -29253,22 +29253,22 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>58.35</v>
+        <v>57.98</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>59.48</v>
+        <v>58.04</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>60.33</v>
+        <v>58.29</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>61.7</v>
+        <v>59.11</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>64.22</v>
+        <v>59.99</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>66.31999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -29299,22 +29299,22 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>58.32</v>
+        <v>55.54</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>57.35</v>
+        <v>54.22</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>56.97</v>
+        <v>53.16</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>57.35</v>
+        <v>52.36</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>58.55</v>
+        <v>52.53</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>60.09</v>
+        <v>55.25</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -29345,22 +29345,22 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>30.58</v>
+        <v>32.13</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>32.31</v>
+        <v>34.46</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>34.53</v>
+        <v>36.4</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>36.41</v>
+        <v>37.07</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>37.03</v>
+        <v>35.95</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>34.66</v>
+        <v>34.15</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -29391,22 +29391,22 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>58.63</v>
+        <v>57.72</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>56.28</v>
+        <v>55.91</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>53.8</v>
+        <v>55.07</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>51.86</v>
+        <v>54.13</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>49.44</v>
+        <v>52.36</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>48.55</v>
+        <v>50.05</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -29437,22 +29437,22 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>52.61</v>
+        <v>52.2</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>50.16</v>
+        <v>48.59</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>46.4</v>
+        <v>47.76</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>45.29</v>
+        <v>48.65</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>45.56</v>
+        <v>49.25</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>46.73</v>
+        <v>49.61</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -29482,23 +29482,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E85" s="4" t="n">
-        <v>39.59</v>
+      <c r="E85" s="3" t="n">
+        <v>42.08</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>42.07</v>
+        <v>44.59</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>44.52</v>
+        <v>46.78</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>46.65</v>
+        <v>47.25</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>47.09</v>
+        <v>46.21</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>45.8</v>
+        <v>40.68</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -29529,22 +29529,22 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>57.27</v>
+        <v>58.36</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>57.1</v>
+        <v>57.85</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>55.89</v>
+        <v>57.98</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>54.91</v>
+        <v>58.14</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>53.4</v>
+        <v>57.62</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>52.3</v>
+        <v>54.48</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -29575,22 +29575,22 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>43.93</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>40.17</v>
+        <v>40.61</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>37.53</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>36.98</v>
+        <v>36.12</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>35.3</v>
+        <v>35.04</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>33.8</v>
+        <v>33.27</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>31.91</v>
+        <v>30.65</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -29621,22 +29621,22 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>35.03</v>
+        <v>35.28</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>36.38</v>
+        <v>37.03</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>40.79</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>40.96</v>
+        <v>38.33</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>35.94</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>38.47</v>
+        <v>33.07</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -29667,22 +29667,22 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>58.54</v>
+        <v>58.26</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>59.96</v>
+        <v>58.9</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>61.47</v>
+        <v>60.08</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>64</v>
+        <v>61.9</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>67.83</v>
+        <v>62.24</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>60.26</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -29713,22 +29713,22 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>56.89</v>
+        <v>58.79</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>60.02</v>
+        <v>61.8</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>63.45</v>
+        <v>63.9</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>66.17</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>68.61</v>
+        <v>65.95</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>69.42</v>
+        <v>64.73</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -29759,22 +29759,22 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>67.02</v>
+        <v>69.5</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>70.31999999999999</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>72.61</v>
+        <v>71.61</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>73.19</v>
+        <v>71.39</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>73.8</v>
+        <v>70.72</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>73.56999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
@@ -29805,22 +29805,22 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>60.7</v>
+        <v>59.44</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>59.89</v>
+        <v>58.43</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>59.29</v>
+        <v>57.61</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>59.09</v>
+        <v>56.75</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>59.17</v>
+        <v>55.04</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>56.47</v>
+        <v>52.77</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -29851,22 +29851,22 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>44.3</v>
+        <v>46.59</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>46.14</v>
+        <v>49.7</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>49.11</v>
+        <v>53.41</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>52.47</v>
+        <v>57.39</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>55.61</v>
+        <v>62.74</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>59.84</v>
+        <v>67.33</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
@@ -29897,22 +29897,22 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>47.73</v>
+        <v>46.85</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>46.82</v>
+        <v>46.01</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>45.95</v>
+        <v>45.2</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>45.09</v>
+        <v>45.01</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>44.83</v>
+        <v>44.89</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>44.45</v>
+        <v>45.56</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -29943,22 +29943,22 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>44.13</v>
+        <v>45.38</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>44.97</v>
+        <v>48.02</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>47.56</v>
+        <v>52.27</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>51.64</v>
+        <v>57.95</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>56.94</v>
+        <v>64.61</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>62.89</v>
+        <v>70.98</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
@@ -29989,22 +29989,22 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>42.27</v>
+        <v>41.38</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>39.9</v>
+        <v>40.15</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>40.63</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>40.11</v>
+        <v>41.17</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>40.41</v>
+        <v>41.34</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -30035,22 +30035,22 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>62.34</v>
+        <v>62.3</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>62.61</v>
+        <v>62.8</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>63.44</v>
+        <v>63.77</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>64.88</v>
+        <v>65.7</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>70.39</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>73.51000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
@@ -30081,22 +30081,22 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>45.99</v>
+        <v>47.89</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>47.53</v>
+        <v>49.61</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>49.08</v>
+        <v>51.81</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>51</v>
+        <v>54.86</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>53.52</v>
+        <v>59.05</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>57.32</v>
+        <v>63.08</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -30127,22 +30127,22 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>64.48999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>64.87</v>
+        <v>66.94</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>65.97</v>
+        <v>69.08</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>67.44</v>
+        <v>71.11</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>68.54000000000001</v>
+        <v>70.98</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>68.84999999999999</v>
+        <v>68.63</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -30173,22 +30173,22 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>39.36</v>
+        <v>37.65</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>39.35</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="H100" s="3" t="n">
-        <v>41.96</v>
+        <v>38.08</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>39.77</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>44.51</v>
+        <v>41.01</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>45.06</v>
+        <v>42.87</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -30219,22 +30219,22 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>59.67</v>
+        <v>58.6</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>60.49</v>
+        <v>58.85</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>61.65</v>
+        <v>59.4</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>63.49</v>
+        <v>59.7</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>65.66</v>
+        <v>60.3</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>69.06999999999999</v>
+        <v>60.84</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -30265,22 +30265,22 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>39.91</v>
+        <v>39.49</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>39.8</v>
+        <v>38.85</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>39.28</v>
+        <v>38.16</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>38.76</v>
+        <v>37.55</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="J102" s="3" t="n">
-        <v>40.76</v>
+        <v>37.77</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>39.23</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -30311,22 +30311,22 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>63.14</v>
+        <v>60.86</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>60.69</v>
+        <v>58.06</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>58.08</v>
+        <v>54.25</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>54.52</v>
+        <v>50.46</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>51.18</v>
+        <v>47.46</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>48.64</v>
+        <v>46.71</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -30357,22 +30357,22 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>45.04</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>41.13</v>
+        <v>44.35</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>36.25</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>38.06</v>
+        <v>34.02</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>36.59</v>
+        <v>33.06</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>37.36</v>
+        <v>32.41</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -30403,22 +30403,22 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>55.42</v>
+        <v>55.23</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>56.4</v>
+        <v>56.41</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>58.37</v>
+        <v>55.74</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>58.62</v>
+        <v>55.23</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>59.26</v>
+        <v>55.12</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>58.84</v>
+        <v>55.55</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -30449,22 +30449,22 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>51.99</v>
+        <v>48.52</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>47.91</v>
+        <v>45.05</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>41.35</v>
+        <v>41.7</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>39.34</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>39.1</v>
+        <v>37.45</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>38</v>
+        <v>36.92</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -30495,22 +30495,22 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>61.54</v>
+        <v>58.01</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>58.59</v>
+        <v>53.85</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>54.9</v>
+        <v>48.95</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>50.56</v>
+        <v>44.59</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>46.82</v>
+        <v>41.95</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>45.7</v>
+        <v>41.04</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -30541,22 +30541,22 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>55.15</v>
+        <v>54.46</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>55.22</v>
+        <v>53.57</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>54.87</v>
+        <v>50.92</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>52.96</v>
+        <v>48.33</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>51.47</v>
+        <v>46.8</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>50.15</v>
+        <v>45.42</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -30587,22 +30587,22 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>63.48</v>
+        <v>58.85</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>58.91</v>
+        <v>54.46</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>54.73</v>
+        <v>49.54</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>50.1</v>
+        <v>45.29</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>46.19</v>
-      </c>
-      <c r="J109" s="3" t="n">
-        <v>43.98</v>
+        <v>41.52</v>
+      </c>
+      <c r="J109" s="4" t="n">
+        <v>39.3</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -30633,22 +30633,22 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>35.84</v>
+        <v>34.69</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>34.93</v>
+        <v>33.88</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>34.24</v>
+        <v>33.64</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>34.17</v>
+        <v>33.52</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>34.31</v>
+        <v>33.11</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>33.55</v>
+        <v>31.22</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -30679,22 +30679,22 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>36.74</v>
+        <v>35.06</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>35.63</v>
+        <v>33.9</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>34.78</v>
+        <v>33.15</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>34.46</v>
+        <v>31.9</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>33.86</v>
+        <v>30.79</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>34.07</v>
+        <v>29.4</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
@@ -30725,22 +30725,22 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>31.7</v>
+        <v>30.48</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>31</v>
+        <v>28.86</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>29.79</v>
+        <v>28.38</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>30.15</v>
+        <v>27.97</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>30.7</v>
+        <v>27.5</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>30.34</v>
+        <v>26.99</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -30771,22 +30771,22 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>45.83</v>
+        <v>44.76</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>43.79</v>
+        <v>43.14</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>41.95</v>
+        <v>42.05</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>40.49</v>
+        <v>42.3</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>40.21</v>
+        <v>42.7</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>40.41</v>
+        <v>43.8</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
@@ -30817,22 +30817,22 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>33.02</v>
+        <v>33.94</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>33.18</v>
+        <v>34.41</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>33.33</v>
+        <v>35.35</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>33.71</v>
+        <v>36.66</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>34.15</v>
-      </c>
-      <c r="J114" s="4" t="n">
-        <v>34.71</v>
+        <v>37.89</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>40.59</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -30863,22 +30863,22 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>32</v>
+        <v>33.43</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>31.93</v>
+        <v>33.31</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>31.71</v>
+        <v>33.76</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>32.28</v>
+        <v>36.24</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>34.23</v>
-      </c>
-      <c r="J115" s="4" t="n">
-        <v>36.04</v>
+        <v>38.32</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>40.62</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
@@ -30909,22 +30909,22 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>41.14</v>
+        <v>40.36</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>38.88</v>
+        <v>37.73</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>35.83</v>
+        <v>36.11</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>33.68</v>
+        <v>37.96</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>34.53</v>
-      </c>
-      <c r="J116" s="4" t="n">
-        <v>36.63</v>
+        <v>39.74</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>40.24</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -30955,22 +30955,22 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>26.46</v>
+        <v>26.35</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>25.83</v>
+        <v>26.2</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>25.51</v>
+        <v>26.89</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>26.08</v>
+        <v>27.5</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>26.4</v>
+        <v>28.04</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>26.89</v>
+        <v>28.66</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
@@ -31001,22 +31001,22 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>38.07</v>
+        <v>37.67</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>36.48</v>
+        <v>36.47</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>34.81</v>
+        <v>36.33</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>33.86</v>
+        <v>37.51</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>33.97</v>
-      </c>
-      <c r="J118" s="4" t="n">
-        <v>34.89</v>
+        <v>39.12</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>41</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -31047,22 +31047,22 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>43.65</v>
+        <v>42.64</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>41.6</v>
+        <v>40.83</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>39.38</v>
-      </c>
-      <c r="H119" s="4" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="I119" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="J119" s="4" t="n">
-        <v>36.78</v>
+        <v>39.94</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>41.95</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
@@ -31093,22 +31093,22 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>43.51</v>
+        <v>42.17</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>41.97</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>40.54</v>
+        <v>40.78</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>39.93</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>39.64</v>
+        <v>39.65</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="J120" s="4" t="n">
-        <v>37.6</v>
+        <v>39.12</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>40.55</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -31138,23 +31138,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E121" s="3" t="n">
-        <v>41.25</v>
+      <c r="E121" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>39.84</v>
+        <v>38.93</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>39.04</v>
+        <v>38.2</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>38.66</v>
+        <v>37.97</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>38.85</v>
+        <v>37.85</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>39.42</v>
+        <v>37.45</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
@@ -31185,22 +31185,22 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>35.3</v>
+        <v>34.02</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>33.73</v>
+        <v>33.41</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>33.12</v>
+        <v>33.66</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>33.17</v>
+        <v>34.32</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>33.26</v>
+        <v>35.35</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>34.35</v>
+        <v>34.96</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -31231,22 +31231,22 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>48.36</v>
+        <v>48.9</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>48.77</v>
+        <v>49.01</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>48.87</v>
+        <v>49.56</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>49.42</v>
+        <v>49.97</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>49.86</v>
+        <v>50.55</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>51.01</v>
+        <v>51.43</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
@@ -31277,22 +31277,22 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>70.97</v>
+        <v>70.83</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>71.42</v>
+        <v>70.09</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>71.04000000000001</v>
+        <v>68.39</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>69.81</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>67.83</v>
+        <v>62.76</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>59.18</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -31323,22 +31323,22 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>65.52</v>
+        <v>64.41</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>66.37</v>
+        <v>63.54</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>62.37</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>66.14</v>
+        <v>61.38</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>65.76000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>63.63</v>
+        <v>57.81</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
@@ -31369,22 +31369,22 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>49.41</v>
+        <v>51.02</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>49.9</v>
+        <v>52.76</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>51.1</v>
+        <v>54.97</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>52.86</v>
+        <v>56.04</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>53.56</v>
+        <v>55.99</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>55.03</v>
+        <v>56.22</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -31415,22 +31415,22 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>57.27</v>
+        <v>53.83</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>54.54</v>
+        <v>50.35</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>51.51</v>
+        <v>47.9</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>49.67</v>
+        <v>46.84</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>49.36</v>
+        <v>47.37</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>50.9</v>
+        <v>47.83</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
@@ -31461,22 +31461,22 @@
         </is>
       </c>
       <c r="E128" s="6" t="n">
-        <v>82.33</v>
+        <v>82.42</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>81.13</v>
+        <v>80.7</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>78.78</v>
+        <v>78.33</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>75.33</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>70.48</v>
+        <v>73.45</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>67.36</v>
+        <v>71.62</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -31507,22 +31507,22 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>54.15</v>
+        <v>53.04</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>53.33</v>
+        <v>51.87</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>52.43</v>
+        <v>50.72</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>51.72</v>
+        <v>49.68</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>51.39</v>
+        <v>48.03</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>48.99</v>
+        <v>46.54</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
@@ -31553,22 +31553,22 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>70.84</v>
+        <v>66.22</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>66.43000000000001</v>
+        <v>60.84</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>60.98</v>
+        <v>57.35</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>57.29</v>
+        <v>56.51</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>56.62</v>
+        <v>56.81</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -31599,22 +31599,22 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>63.06</v>
+        <v>67.53</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>63.11</v>
+        <v>68.31</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>63.11</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>62.41</v>
+        <v>69.19</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>61.95</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>63.19</v>
+        <v>69.06</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
@@ -31645,22 +31645,22 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>62.53</v>
+        <v>60.45</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>62.22</v>
+        <v>59.01</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>61.77</v>
+        <v>56.97</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>60.96</v>
+        <v>54.75</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>59.96</v>
+        <v>53.02</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>58.47</v>
+        <v>51.34</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -31691,22 +31691,22 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>72.17</v>
+        <v>73.13</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>72.62</v>
+        <v>72.83</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>71.76000000000001</v>
+        <v>71.94</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>69.98</v>
+        <v>70.22</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>63.06</v>
+        <v>63.17</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
@@ -31737,22 +31737,22 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>51.21</v>
+        <v>46.35</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>46.72</v>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>42.39</v>
+        <v>41.69</v>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>37.6</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>38.78</v>
+        <v>35.4</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>37.28</v>
+        <v>35.48</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>37.69</v>
+        <v>36.3</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -31783,22 +31783,22 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>62.5</v>
+        <v>56.63</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>56.84</v>
+        <v>49.9</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>50.27</v>
+        <v>44.61</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>45.4</v>
+        <v>41.47</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>42.95</v>
+        <v>40.96</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>42.98</v>
+        <v>41</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
@@ -31829,22 +31829,22 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>53.12</v>
+        <v>48.92</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>49.53</v>
+        <v>45.25</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="H136" s="3" t="n">
-        <v>42.74</v>
+        <v>41.05</v>
+      </c>
+      <c r="H136" s="4" t="n">
+        <v>36.19</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>38.83</v>
+        <v>33.33</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>36.09</v>
+        <v>32.73</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -31875,22 +31875,22 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>44.48</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>41.11</v>
+        <v>40.57</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>37.55</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>38.42</v>
+        <v>34.06</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>35.35</v>
+        <v>31.11</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>33.02</v>
+        <v>29.89</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>31.53</v>
+        <v>31.08</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
@@ -31921,22 +31921,22 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>25.45</v>
+        <v>22.45</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="G138" s="4" t="n">
-        <v>21.41</v>
+        <v>20.07</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>17.64</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>19.47</v>
+        <v>15.41</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>17.82</v>
+        <v>14.57</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>16.49</v>
+        <v>14.55</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -31967,22 +31967,22 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>59.68</v>
+        <v>59.27</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>59.17</v>
+        <v>57.36</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>57.27</v>
+        <v>54.39</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>54.36</v>
+        <v>51.29</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>51.48</v>
+        <v>48.68</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>49.68</v>
+        <v>45.44</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
@@ -32013,22 +32013,22 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>48.84</v>
+        <v>46.27</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>46.46</v>
+        <v>43.95</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>44.32</v>
-      </c>
-      <c r="H140" s="3" t="n">
-        <v>41.12</v>
+        <v>40.36</v>
+      </c>
+      <c r="H140" s="4" t="n">
+        <v>35.98</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>37.48</v>
+        <v>34.24</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>36.08</v>
+        <v>33.08</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -32059,22 +32059,22 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>54.12</v>
+        <v>49.72</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>49.94</v>
+        <v>45.18</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="H141" s="3" t="n">
-        <v>42.34</v>
-      </c>
-      <c r="I141" s="3" t="n">
-        <v>40.87</v>
-      </c>
-      <c r="J141" s="3" t="n">
-        <v>41.02</v>
+        <v>41.38</v>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="I141" s="4" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="J141" s="4" t="n">
+        <v>39.13</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -32105,22 +32105,22 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>34.22</v>
+        <v>31.94</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>32.25</v>
+        <v>30.2</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>30.66</v>
+        <v>28.01</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>28.82</v>
+        <v>25.25</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>26.54</v>
+        <v>23.58</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>24.88</v>
+        <v>22.38</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -32151,22 +32151,22 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>38.29</v>
+        <v>35.6</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>35.64</v>
+        <v>33.77</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>33.77</v>
+        <v>32.13</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>32.14</v>
+        <v>31.04</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>31.14</v>
+        <v>30.25</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>30.43</v>
+        <v>29.23</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
@@ -32197,22 +32197,22 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>62.99</v>
+        <v>58.57</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>58.8</v>
+        <v>52.76</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>53.23</v>
+        <v>46.3</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I144" s="3" t="n">
-        <v>42.68</v>
-      </c>
-      <c r="J144" s="3" t="n">
-        <v>40.54</v>
+        <v>41.24</v>
+      </c>
+      <c r="I144" s="4" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="J144" s="4" t="n">
+        <v>38.28</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -32243,22 +32243,22 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>69.45</v>
+        <v>64.97</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>65.16</v>
+        <v>58.63</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>58.98</v>
+        <v>52.54</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>53.24</v>
+        <v>47.8</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>48.95</v>
+        <v>45.15</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>46.63</v>
+        <v>43.98</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
@@ -32289,22 +32289,22 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>58.37</v>
+        <v>55.6</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>55.97</v>
+        <v>52.03</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>52.72</v>
+        <v>46.89</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>48.08</v>
+        <v>43.41</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>45.21</v>
+        <v>42.01</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>44.12</v>
+        <v>40.96</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -32335,22 +32335,22 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>31.54</v>
+        <v>28.32</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>28.87</v>
+        <v>26.09</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>26.94</v>
+        <v>23.43</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I147" s="4" t="n">
-        <v>22.78</v>
+        <v>20.96</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>19.72</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>21.07</v>
+        <v>20.42</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
@@ -32381,22 +32381,22 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>60.97</v>
+        <v>60.28</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>60.06</v>
+        <v>57.77</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>57.5</v>
+        <v>54.15</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>53.98</v>
+        <v>51.16</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>51.33</v>
+        <v>49.12</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>49.46</v>
+        <v>47.37</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -32427,22 +32427,22 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>65.25</v>
+        <v>66.97</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>66.09</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>67.36</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>69.11</v>
+        <v>73.67</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>70.42</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>71.12</v>
+        <v>71.58</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
@@ -32473,22 +32473,22 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>72.44</v>
+        <v>76.06</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>73.95</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>74.28</v>
+        <v>78.63</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>74.17</v>
+        <v>79.58</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>72.94</v>
+        <v>78.97</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>73.59</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -32519,22 +32519,22 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>65.22</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>66.12</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>66.12</v>
+        <v>67.95</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>65.34999999999999</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>64.39</v>
+        <v>67.69</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>65.55</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
@@ -32565,22 +32565,22 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>49.27</v>
+        <v>49.38</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>50.19</v>
+        <v>50.87</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>52.06</v>
+        <v>52.48</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>54.16</v>
+        <v>53.24</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>55.66</v>
+        <v>52.59</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>54.34</v>
+        <v>50.15</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -32611,22 +32611,22 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>57.15</v>
+        <v>57.56</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>57.11</v>
+        <v>57.87</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>57.19</v>
+        <v>58.77</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>57.72</v>
+        <v>60.04</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>58.49</v>
+        <v>61.12</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>59.36</v>
+        <v>61.69</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
@@ -32657,22 +32657,22 @@
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>51.73</v>
+        <v>51.68</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>52.44</v>
+        <v>52.62</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>53.74</v>
+        <v>53.86</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>55.61</v>
+        <v>54.56</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>57.28</v>
+        <v>53.22</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>55.03</v>
+        <v>49.74</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -32703,22 +32703,22 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>30.8</v>
+        <v>32.61</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>31.67</v>
+        <v>32.53</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>31.09</v>
+        <v>31.66</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>29.75</v>
+        <v>31.02</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>28.96</v>
+        <v>31.44</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>29.17</v>
+        <v>33.34</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
@@ -32749,22 +32749,22 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>47.65</v>
+        <v>45.19</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>45.38</v>
+        <v>43.9</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>44.16</v>
+        <v>42.36</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>42.76</v>
-      </c>
-      <c r="I156" s="3" t="n">
-        <v>41.41</v>
-      </c>
-      <c r="J156" s="3" t="n">
-        <v>40.72</v>
+        <v>40.79</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <v>38.9</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -32795,22 +32795,22 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>18.32</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>19.5</v>
+        <v>19.49</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>21.08</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>20.99</v>
+        <v>22.38</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>22.21</v>
+        <v>23.36</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>23.28</v>
+        <v>24.11</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>24.08</v>
+        <v>24.9</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
@@ -32841,22 +32841,22 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>37.57</v>
-      </c>
-      <c r="F158" s="4" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="G158" s="4" t="n">
-        <v>39.87</v>
+        <v>38.93</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>41.81</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>40.72</v>
+        <v>42.86</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>41.38</v>
-      </c>
-      <c r="J158" s="4" t="n">
-        <v>39.71</v>
+        <v>42.08</v>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>41.67</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -32887,22 +32887,22 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>21.21</v>
+        <v>20.59</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>20.48</v>
+        <v>20.07</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>19.94</v>
+        <v>19.61</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>19.47</v>
+        <v>19.19</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>19.23</v>
+        <v>19.73</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>20.04</v>
+        <v>21.04</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
@@ -32933,22 +32933,22 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>37.15</v>
+        <v>38.24</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>37.23</v>
-      </c>
-      <c r="G160" s="4" t="n">
-        <v>37.42</v>
-      </c>
-      <c r="H160" s="4" t="n">
-        <v>37.62</v>
-      </c>
-      <c r="I160" s="4" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="J160" s="4" t="n">
-        <v>38.08</v>
+        <v>39</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>42.31</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -32979,22 +32979,22 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>54.02</v>
+        <v>55.66</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>54.76</v>
+        <v>56.31</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>54.94</v>
+        <v>55.74</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>53.91</v>
+        <v>55.6</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>53.2</v>
+        <v>53.82</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>50.81</v>
+        <v>52.28</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
@@ -33024,23 +33024,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E162" s="3" t="n">
-        <v>41.76</v>
+      <c r="E162" s="4" t="n">
+        <v>39.26</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>39.45</v>
+        <v>37.49</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>37.79</v>
+        <v>35.78</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>36.26</v>
+        <v>34.18</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>35</v>
+        <v>33.36</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>34.45</v>
+        <v>32.66</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -33071,22 +33071,22 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>40.31</v>
+        <v>40.75</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>40.11</v>
-      </c>
-      <c r="G163" s="4" t="n">
-        <v>39.73</v>
+        <v>40.73</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>40.36</v>
       </c>
       <c r="H163" s="4" t="n">
-        <v>38.99</v>
+        <v>39.36</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>37.82</v>
+        <v>37.96</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>36.33</v>
+        <v>36.75</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
@@ -33117,22 +33117,22 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>62.41</v>
+        <v>63.38</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>63.28</v>
+        <v>63.1</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>63.03</v>
+        <v>62.4</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>62.06</v>
+        <v>60.94</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>59.99</v>
+        <v>59</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>58.91</v>
+        <v>58.1</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -33163,22 +33163,22 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>61.45</v>
+        <v>63.07</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>62.42</v>
+        <v>63.91</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>63.07</v>
+        <v>64.61</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>63.24</v>
+        <v>63.15</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>60.76</v>
+        <v>59.9</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>58.3</v>
+        <v>57.66</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
@@ -33209,22 +33209,22 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>61.57</v>
+        <v>63.58</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>62.19</v>
+        <v>63.19</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>60.96</v>
+        <v>63.36</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>59.63</v>
+        <v>63.24</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>57.11</v>
+        <v>60.95</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>54.6</v>
+        <v>59.77</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -33255,22 +33255,22 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>58.51</v>
+        <v>57.63</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>53.71</v>
+        <v>54.92</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>51.74</v>
+        <v>53.92</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>49.3</v>
+        <v>52.1</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>48.41</v>
+        <v>49.81</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
@@ -33301,22 +33301,22 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>52.32</v>
+        <v>51.12</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>49.24</v>
+        <v>46.62</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>44.76</v>
+        <v>45.41</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>43.48</v>
+        <v>46.24</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>43.85</v>
+        <v>46.97</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>45.21</v>
+        <v>48</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -33347,22 +33347,22 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>60.56</v>
+        <v>62.91</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>61.63</v>
+        <v>63.93</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>62.08</v>
+        <v>65.5</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>62.75</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>62.84</v>
+        <v>65.78</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>61.7</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
@@ -33393,22 +33393,22 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>62.58</v>
+        <v>65.64</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>65.16</v>
+        <v>67.11</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>66.34</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>67.18000000000001</v>
+        <v>67.56</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>65.39</v>
+        <v>64.97</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>62.79</v>
+        <v>61.97</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -33439,22 +33439,22 @@
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>54.82</v>
+        <v>57.48</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>54.93</v>
+        <v>57.43</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>53.49</v>
+        <v>58.75</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>52.71</v>
+        <v>60.11</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>51.31</v>
+        <v>60</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>50.06</v>
+        <v>58.93</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
@@ -33485,22 +33485,22 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>43.18</v>
+        <v>44.85</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>43.29</v>
+        <v>45.28</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>43.44</v>
+        <v>45.86</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>43.48</v>
+        <v>46.58</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>43.67</v>
+        <v>46.1</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>43.86</v>
+        <v>45.83</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -33531,22 +33531,22 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>58.54</v>
+        <v>58.18</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>59.9</v>
+        <v>58.79</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>61.4</v>
+        <v>59.96</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>63.95</v>
+        <v>61.78</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>67.81999999999999</v>
+        <v>62.09</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>69.58</v>
+        <v>60</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
@@ -33577,22 +33577,22 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>56.89</v>
+        <v>58.76</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>60.06</v>
+        <v>61.81</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>63.55</v>
+        <v>63.91</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>66.31</v>
+        <v>65.42</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>68.75</v>
+        <v>65.91</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>69.55</v>
+        <v>64.69</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -33623,22 +33623,22 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>66.97</v>
+        <v>69.47</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>70.28</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>72.56999999999999</v>
+        <v>71.58</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>73.15000000000001</v>
+        <v>71.38</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>73.77</v>
+        <v>70.73</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>73.56999999999999</v>
+        <v>69.31</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
@@ -33669,22 +33669,22 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>72.95999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>76.84999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>78.88</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>78.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>78.34999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>76.98</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -33715,22 +33715,22 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>47.62</v>
+        <v>48.07</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>47.99</v>
+        <v>48.16</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>48.13</v>
+        <v>48.85</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>48.89</v>
+        <v>49.21</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>49.4</v>
+        <v>49.58</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>50.48</v>
+        <v>50.24</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
@@ -33761,22 +33761,22 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>60.23</v>
+        <v>61.5</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>61.23</v>
+        <v>61.73</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>61.19</v>
+        <v>62.3</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>61.35</v>
+        <v>62.31</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>60.65</v>
+        <v>61.79</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>62.44</v>
+        <v>59.1</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -33807,22 +33807,22 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>59.03</v>
+        <v>61.75</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>61.51</v>
+        <v>63.1</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>62.9</v>
+        <v>63.13</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>62.93</v>
+        <v>62.53</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>62.15</v>
+        <v>61.81</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>62.91</v>
+        <v>61.4</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
@@ -33853,22 +33853,22 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>59.22</v>
+        <v>61.01</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>61.21</v>
+        <v>61.69</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>62.08</v>
+        <v>60.86</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>61.39</v>
+        <v>58.28</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>59.06</v>
+        <v>56.38</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>57.77</v>
+        <v>55.39</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -33899,22 +33899,22 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>54.7</v>
+        <v>57.33</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>57.4</v>
+        <v>60.24</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>60.36</v>
+        <v>64.08</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>64.20999999999999</v>
+        <v>68.19</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>68.20999999999999</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>73.70999999999999</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
@@ -33945,22 +33945,22 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>47.35</v>
+        <v>46.62</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>46.45</v>
+        <v>45.76</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>45.5</v>
+        <v>45.08</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>44.67</v>
+        <v>44.99</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>44.37</v>
+        <v>44.9</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>43.89</v>
+        <v>45.56</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -33991,22 +33991,22 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>41</v>
+        <v>41.67</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>41.28</v>
+        <v>44.05</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>43.66</v>
+        <v>48.52</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>47.98</v>
+        <v>53.62</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>52.74</v>
+        <v>59.99</v>
       </c>
       <c r="J183" s="3" t="n">
-        <v>58.3</v>
+        <v>65.88</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
@@ -34037,22 +34037,22 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>41.84</v>
-      </c>
-      <c r="F184" s="3" t="n">
-        <v>40.86</v>
-      </c>
-      <c r="G184" s="4" t="n">
-        <v>39.79</v>
-      </c>
-      <c r="H184" s="4" t="n">
-        <v>39.9</v>
+        <v>40.97</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>40.51</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>40.12</v>
+        <v>40.94</v>
       </c>
       <c r="J184" s="3" t="n">
-        <v>40.43</v>
+        <v>40.88</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -34083,22 +34083,22 @@
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>42.82</v>
+        <v>41.41</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>40.91</v>
+        <v>40.31</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>39.52</v>
-      </c>
-      <c r="H185" s="4" t="n">
-        <v>38.68</v>
-      </c>
-      <c r="I185" s="4" t="n">
-        <v>37.91</v>
-      </c>
-      <c r="J185" s="4" t="n">
-        <v>38.38</v>
+        <v>39.98</v>
+      </c>
+      <c r="H185" s="3" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>42.84</v>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
@@ -34129,22 +34129,22 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>46.39</v>
+        <v>48.19</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>47.86</v>
+        <v>49.87</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>49.39</v>
+        <v>51.96</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>51.23</v>
+        <v>54.93</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>53.74</v>
+        <v>59.16</v>
       </c>
       <c r="J186" s="3" t="n">
-        <v>57.54</v>
+        <v>63.27</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -34175,22 +34175,22 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>68.43000000000001</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>69.48</v>
+        <v>72.06</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>70.63</v>
+        <v>74.31</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>72.08</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>72.98999999999999</v>
+        <v>76.34</v>
       </c>
       <c r="J187" s="3" t="n">
-        <v>73.59</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
@@ -34221,22 +34221,22 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>72.44</v>
+        <v>76.17</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>73.97</v>
+        <v>77.48</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>74.31</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>74.17</v>
+        <v>79.86</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>72.95</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>73.62</v>
+        <v>78.08</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -34267,22 +34267,22 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>64.22</v>
+        <v>66.33</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>65.19</v>
+        <v>67.19</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>67.87</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>65.22</v>
+        <v>68.98</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>68.31</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>66.05</v>
+        <v>68.28</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
@@ -34313,22 +34313,22 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>49.69</v>
+        <v>49.86</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>50.43</v>
+        <v>51.23</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>52.07</v>
+        <v>52.7</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>53.85</v>
+        <v>53.32</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>54.97</v>
+        <v>52.61</v>
       </c>
       <c r="J190" s="3" t="n">
-        <v>53.73</v>
+        <v>50.29</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -34359,22 +34359,22 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>57.27</v>
+        <v>57.64</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>57.17</v>
+        <v>57.93</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>57.23</v>
+        <v>58.79</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>57.69</v>
+        <v>59.98</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>58.35</v>
+        <v>61.02</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>59.22</v>
+        <v>61.58</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
@@ -34405,22 +34405,22 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>56.01</v>
+        <v>56.21</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>56.28</v>
+        <v>56.93</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>57.04</v>
+        <v>58.45</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>58.62</v>
+        <v>59.58</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>59.92</v>
+        <v>58.51</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>58.12</v>
+        <v>55.15</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -34451,22 +34451,22 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>48.63</v>
+        <v>49.28</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>49.12</v>
+        <v>49.45</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>49.29</v>
+        <v>50.05</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>49.86</v>
+        <v>50.44</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>50.26</v>
+        <v>50.93</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>51.31</v>
+        <v>51.78</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
@@ -34497,22 +34497,22 @@
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>49.38</v>
+        <v>51.04</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>49.89</v>
+        <v>52.81</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>51.12</v>
+        <v>55.02</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>52.87</v>
+        <v>56.13</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>53.63</v>
+        <v>56.15</v>
       </c>
       <c r="J194" s="3" t="n">
-        <v>55.24</v>
+        <v>56.31</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -34543,22 +34543,22 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>61.01</v>
+        <v>64.94</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>61.8</v>
+        <v>66.67</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>62.77</v>
+        <v>69.13</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>63.93</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>65.20999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>67.3</v>
+        <v>72.53</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
@@ -34589,22 +34589,22 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>46.66</v>
+        <v>50.97</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>48.02</v>
+        <v>53.75</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>50.06</v>
+        <v>57.4</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>52.23</v>
+        <v>61.71</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>54.04</v>
+        <v>65.52</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>56.97</v>
+        <v>65.86</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -34635,22 +34635,22 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>63.55</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>64.27</v>
+        <v>65.52</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>64.17</v>
+        <v>66.22</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>64.23999999999999</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>63.86</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>65.42</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
@@ -34681,22 +34681,22 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>59.41</v>
+        <v>61.01</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>60.17</v>
+        <v>62.15</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>61.46</v>
+        <v>62.31</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>61.88</v>
+        <v>63.12</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>63.14</v>
+        <v>62.55</v>
       </c>
       <c r="J198" s="3" t="n">
-        <v>65.78</v>
+        <v>58.49</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -34727,22 +34727,22 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>65.09</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>63.96</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>63.85</v>
+        <v>62.2</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>62.29</v>
+        <v>60.97</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>60.99</v>
+        <v>59.94</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>62.34</v>
+        <v>57.19</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
@@ -34773,22 +34773,22 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>58.12</v>
+        <v>59.88</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>60.02</v>
+        <v>60.74</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>61</v>
+        <v>59.95</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>60.32</v>
+        <v>57.58</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>58.15</v>
+        <v>55.97</v>
       </c>
       <c r="J200" s="3" t="n">
-        <v>57.14</v>
+        <v>55</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -34819,22 +34819,22 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>65.58</v>
+        <v>67.37</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>66.81999999999999</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>67.52</v>
+        <v>65.98</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>66.43000000000001</v>
+        <v>62.72</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>64.56999999999999</v>
+        <v>58.08</v>
       </c>
       <c r="J201" s="3" t="n">
-        <v>62.59</v>
+        <v>54.72</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
@@ -34865,22 +34865,22 @@
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>58.53</v>
+        <v>57.18</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>58.84</v>
+        <v>57.03</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>59.53</v>
+        <v>56.14</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>59.78</v>
+        <v>54.53</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>59.53</v>
+        <v>51.72</v>
       </c>
       <c r="J202" s="3" t="n">
-        <v>57.3</v>
+        <v>47.21</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -34911,22 +34911,22 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>61.85</v>
+        <v>64.12</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>63.19</v>
+        <v>63.51</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>62.21</v>
+        <v>61.94</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>60</v>
+        <v>60.67</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>57.92</v>
+        <v>59.2</v>
       </c>
       <c r="J203" s="3" t="n">
-        <v>56.68</v>
+        <v>54.14</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
@@ -34957,22 +34957,22 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>67.01000000000001</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>66.04000000000001</v>
+        <v>63.47</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>64.37</v>
+        <v>61.02</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>62.47</v>
+        <v>58.24</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>60.45</v>
+        <v>55.31</v>
       </c>
       <c r="J204" s="3" t="n">
-        <v>57.71</v>
+        <v>50.15</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -35003,22 +35003,22 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>63.86</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>64.86</v>
+        <v>64.72</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>65.92</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>68.59</v>
+        <v>69.7</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>72.91</v>
+        <v>73.81</v>
       </c>
       <c r="J205" s="3" t="n">
-        <v>78.5</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
@@ -35049,22 +35049,22 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>45.03</v>
+        <v>47.47</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>47.23</v>
+        <v>50.19</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>49.84</v>
+        <v>53.03</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>52.49</v>
+        <v>56.29</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>55.31</v>
+        <v>60.83</v>
       </c>
       <c r="J206" s="3" t="n">
-        <v>59.26</v>
+        <v>65.03</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -35095,22 +35095,22 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>58.34</v>
+        <v>58.19</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>58.47</v>
+        <v>58.8</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>59.36</v>
+        <v>60.39</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>61.39</v>
+        <v>63.23</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>64.91</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="J207" s="3" t="n">
-        <v>71</v>
+        <v>72.72</v>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
@@ -35141,22 +35141,22 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>54.49</v>
+        <v>57.52</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>57.57</v>
+        <v>60.75</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>60.85</v>
+        <v>64.67</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>64.77</v>
+        <v>68.83</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>68.81</v>
+        <v>73.92</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>74.13</v>
+        <v>78.62</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -35187,22 +35187,22 @@
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>41.84</v>
+        <v>44.2</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>43.13</v>
+        <v>45.66</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>44.03</v>
+        <v>47.32</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>44.82</v>
+        <v>50.31</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>46.29</v>
+        <v>54.34</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>48.61</v>
+        <v>59.77</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
@@ -35233,22 +35233,22 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>35.21</v>
+        <v>37.03</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>35.95</v>
-      </c>
-      <c r="G210" s="4" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="H210" s="4" t="n">
-        <v>37.39</v>
-      </c>
-      <c r="I210" s="4" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="J210" s="4" t="n">
-        <v>37.44</v>
+        <v>38.98</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>42.22</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -35279,22 +35279,22 @@
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>42.57</v>
+        <v>43.39</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>43.29</v>
+        <v>44.52</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>44.25</v>
+        <v>45.86</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>45.32</v>
+        <v>48.73</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>47.68</v>
+        <v>50.14</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>47.36</v>
+        <v>49.58</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
@@ -35325,22 +35325,22 @@
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="F212" s="5" t="n">
-        <v>19.17</v>
+        <v>19.13</v>
+      </c>
+      <c r="F212" s="4" t="n">
+        <v>20.89</v>
       </c>
       <c r="G212" s="4" t="n">
-        <v>20.86</v>
+        <v>22.38</v>
       </c>
       <c r="H212" s="4" t="n">
-        <v>22.3</v>
+        <v>23.47</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>23.46</v>
+        <v>24.18</v>
       </c>
       <c r="J212" s="4" t="n">
-        <v>24.11</v>
+        <v>24.88</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -35371,22 +35371,22 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="F213" s="4" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="G213" s="4" t="n">
-        <v>39.45</v>
+        <v>38.1</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>41.94</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>40.69</v>
+        <v>43.4</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="J213" s="4" t="n">
-        <v>39.97</v>
+        <v>42.7</v>
+      </c>
+      <c r="J213" s="3" t="n">
+        <v>42.48</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
@@ -35417,22 +35417,22 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>21.17</v>
+        <v>20.53</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>20.43</v>
+        <v>20.01</v>
       </c>
       <c r="G214" s="5" t="n">
-        <v>19.87</v>
+        <v>19.53</v>
       </c>
       <c r="H214" s="5" t="n">
-        <v>19.4</v>
+        <v>19.12</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>19.16</v>
-      </c>
-      <c r="J214" s="5" t="n">
-        <v>19.97</v>
+        <v>19.65</v>
+      </c>
+      <c r="J214" s="4" t="n">
+        <v>20.96</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -35463,22 +35463,22 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>57.46</v>
+        <v>58.14</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>57.78</v>
+        <v>58.77</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>58.02</v>
+        <v>56.87</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>55.65</v>
+        <v>54.23</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>52.48</v>
+        <v>51.15</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>48.56</v>
+        <v>48.29</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
@@ -35509,22 +35509,22 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>54.32</v>
+        <v>55.85</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>54.99</v>
+        <v>56.46</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>55.14</v>
+        <v>55.74</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>53.98</v>
+        <v>55.45</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>53.12</v>
+        <v>53.67</v>
       </c>
       <c r="J216" s="3" t="n">
-        <v>50.77</v>
+        <v>52.05</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -35555,22 +35555,22 @@
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="F217" s="3" t="n">
-        <v>40.9</v>
+        <v>40.72</v>
+      </c>
+      <c r="F217" s="4" t="n">
+        <v>38.95</v>
       </c>
       <c r="G217" s="4" t="n">
-        <v>39.23</v>
+        <v>37.17</v>
       </c>
       <c r="H217" s="4" t="n">
-        <v>37.62</v>
+        <v>35.52</v>
       </c>
       <c r="I217" s="4" t="n">
-        <v>36.3</v>
+        <v>34.67</v>
       </c>
       <c r="J217" s="4" t="n">
-        <v>35.69</v>
+        <v>33.94</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
@@ -35601,22 +35601,22 @@
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>58.71</v>
+        <v>57.36</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>59.17</v>
+        <v>57.3</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>60.02</v>
+        <v>57.58</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>61.62</v>
+        <v>57.98</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>63.95</v>
+        <v>58.96</v>
       </c>
       <c r="J218" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>59.93</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -35647,22 +35647,22 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>67.03</v>
+        <v>66.37</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>68.51000000000001</v>
+        <v>66.36</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>69.56</v>
+        <v>66.38</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>71</v>
+        <v>66.87</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>73.23</v>
+        <v>66.89</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>75.20999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
@@ -35693,22 +35693,22 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>59</v>
+        <v>58.6</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>60.11</v>
+        <v>58.69</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>60.99</v>
+        <v>58.96</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>62.38</v>
+        <v>59.83</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>64.95999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>67.09</v>
+        <v>62.75</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -35739,22 +35739,22 @@
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>58.41</v>
+        <v>55.63</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>57.45</v>
+        <v>54.31</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>57.07</v>
+        <v>53.25</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>57.45</v>
+        <v>52.45</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>58.64</v>
+        <v>52.61</v>
       </c>
       <c r="J221" s="3" t="n">
-        <v>60.17</v>
+        <v>55.33</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
@@ -35785,22 +35785,22 @@
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>51.21</v>
+        <v>46.35</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>46.72</v>
-      </c>
-      <c r="G222" s="3" t="n">
-        <v>42.39</v>
+        <v>41.69</v>
+      </c>
+      <c r="G222" s="4" t="n">
+        <v>37.6</v>
       </c>
       <c r="H222" s="4" t="n">
-        <v>38.78</v>
+        <v>35.4</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>37.28</v>
+        <v>35.48</v>
       </c>
       <c r="J222" s="4" t="n">
-        <v>37.69</v>
+        <v>36.3</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -35831,22 +35831,22 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>60.23</v>
+        <v>59.27</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>59.79</v>
+        <v>57.74</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>58.59</v>
+        <v>55.19</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>56.52</v>
+        <v>52.01</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>54.09</v>
+        <v>48.41</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>51.15</v>
+        <v>44.99</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
@@ -35877,22 +35877,22 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>53.12</v>
+        <v>48.92</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>49.53</v>
+        <v>45.25</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="H224" s="3" t="n">
-        <v>42.74</v>
+        <v>41.05</v>
+      </c>
+      <c r="H224" s="4" t="n">
+        <v>36.19</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>38.83</v>
+        <v>33.33</v>
       </c>
       <c r="J224" s="4" t="n">
-        <v>36.09</v>
+        <v>32.73</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -35923,22 +35923,22 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>44.48</v>
-      </c>
-      <c r="F225" s="3" t="n">
-        <v>41.11</v>
+        <v>40.57</v>
+      </c>
+      <c r="F225" s="4" t="n">
+        <v>37.55</v>
       </c>
       <c r="G225" s="4" t="n">
-        <v>38.42</v>
+        <v>34.06</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>35.35</v>
+        <v>31.11</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>33.02</v>
+        <v>29.89</v>
       </c>
       <c r="J225" s="4" t="n">
-        <v>31.53</v>
+        <v>31.08</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
@@ -35969,22 +35969,22 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>58.59</v>
+        <v>53.72</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>54.13</v>
+        <v>49.06</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>49.74</v>
+        <v>44.43</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="I226" s="3" t="n">
-        <v>42.22</v>
+        <v>40.69</v>
+      </c>
+      <c r="I226" s="4" t="n">
+        <v>38.67</v>
       </c>
       <c r="J226" s="4" t="n">
-        <v>39.94</v>
+        <v>38.56</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -36015,22 +36015,22 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>25.45</v>
+        <v>22.45</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="G227" s="4" t="n">
-        <v>21.41</v>
+        <v>20.07</v>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>17.64</v>
       </c>
       <c r="H227" s="5" t="n">
-        <v>19.47</v>
+        <v>15.41</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>17.82</v>
+        <v>14.57</v>
       </c>
       <c r="J227" s="5" t="n">
-        <v>16.49</v>
+        <v>14.55</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
@@ -36061,22 +36061,22 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>48.84</v>
+        <v>46.27</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>46.46</v>
+        <v>43.95</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>44.32</v>
-      </c>
-      <c r="H228" s="3" t="n">
-        <v>41.12</v>
+        <v>40.36</v>
+      </c>
+      <c r="H228" s="4" t="n">
+        <v>35.98</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>37.48</v>
+        <v>34.24</v>
       </c>
       <c r="J228" s="4" t="n">
-        <v>36.08</v>
+        <v>33.08</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -36107,22 +36107,22 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>48.84</v>
+        <v>46.27</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>46.46</v>
+        <v>43.95</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>44.32</v>
-      </c>
-      <c r="H229" s="3" t="n">
-        <v>41.12</v>
+        <v>40.36</v>
+      </c>
+      <c r="H229" s="4" t="n">
+        <v>35.98</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>37.48</v>
+        <v>34.24</v>
       </c>
       <c r="J229" s="4" t="n">
-        <v>36.08</v>
+        <v>33.08</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
@@ -36153,22 +36153,22 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>57.71</v>
+        <v>53.31</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>54.34</v>
+        <v>49.22</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>50.83</v>
+        <v>44.8</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>47.16</v>
-      </c>
-      <c r="I230" s="3" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="J230" s="3" t="n">
-        <v>40.32</v>
+        <v>40.61</v>
+      </c>
+      <c r="I230" s="4" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="J230" s="4" t="n">
+        <v>37.94</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -36199,22 +36199,22 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>38.29</v>
+        <v>35.6</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>35.64</v>
+        <v>33.77</v>
       </c>
       <c r="G231" s="4" t="n">
-        <v>33.77</v>
+        <v>32.13</v>
       </c>
       <c r="H231" s="4" t="n">
-        <v>32.14</v>
+        <v>31.04</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>31.14</v>
+        <v>30.25</v>
       </c>
       <c r="J231" s="4" t="n">
-        <v>30.43</v>
+        <v>29.23</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
@@ -36245,22 +36245,22 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>62.99</v>
+        <v>58.57</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>58.8</v>
+        <v>52.76</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>53.23</v>
+        <v>46.3</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I232" s="3" t="n">
-        <v>42.68</v>
-      </c>
-      <c r="J232" s="3" t="n">
-        <v>40.54</v>
+        <v>41.24</v>
+      </c>
+      <c r="I232" s="4" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="J232" s="4" t="n">
+        <v>38.28</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -36291,22 +36291,22 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>69.45</v>
+        <v>64.97</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>65.16</v>
+        <v>58.63</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>58.98</v>
+        <v>52.54</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>53.24</v>
+        <v>47.8</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>48.95</v>
+        <v>45.15</v>
       </c>
       <c r="J233" s="3" t="n">
-        <v>46.63</v>
+        <v>43.98</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
@@ -36337,22 +36337,22 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>58.37</v>
+        <v>55.6</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>55.97</v>
+        <v>52.03</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>52.72</v>
+        <v>46.89</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>48.08</v>
+        <v>43.41</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>45.21</v>
+        <v>42.01</v>
       </c>
       <c r="J234" s="3" t="n">
-        <v>44.12</v>
+        <v>40.96</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -36383,22 +36383,22 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>31.54</v>
+        <v>28.32</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>28.87</v>
+        <v>26.09</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>26.94</v>
+        <v>23.43</v>
       </c>
       <c r="H235" s="4" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I235" s="4" t="n">
-        <v>22.78</v>
+        <v>20.96</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>19.72</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>21.07</v>
+        <v>20.42</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
@@ -36429,22 +36429,22 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>71.54000000000001</v>
+        <v>67.52</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>68.05</v>
+        <v>62.67</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>63.55</v>
+        <v>57.13</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>58.52</v>
+        <v>51.94</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>53.86</v>
+        <v>48.25</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>49.7</v>
+        <v>46.2</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -36475,22 +36475,22 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>71.44</v>
+        <v>67.81</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>67.70999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>63.23</v>
+        <v>59.48</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>59.55</v>
+        <v>54.98</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>55.3</v>
+        <v>50.74</v>
       </c>
       <c r="J237" s="3" t="n">
-        <v>51.46</v>
+        <v>47.09</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
@@ -36521,22 +36521,22 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>59.22</v>
+        <v>57.29</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>58.47</v>
+        <v>54.99</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>56.69</v>
+        <v>51.33</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>53.9</v>
+        <v>47.23</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>51.17</v>
+        <v>43.1</v>
       </c>
       <c r="J238" s="3" t="n">
-        <v>47</v>
+        <v>40.19</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -36567,22 +36567,22 @@
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>52.77</v>
+        <v>49.95</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>50.7</v>
+        <v>46.8</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>47.59</v>
+        <v>44.16</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>45.38</v>
-      </c>
-      <c r="I239" s="3" t="n">
-        <v>43.81</v>
-      </c>
-      <c r="J239" s="3" t="n">
-        <v>40.25</v>
+        <v>41.8</v>
+      </c>
+      <c r="I239" s="4" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="J239" s="4" t="n">
+        <v>37.97</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
@@ -36613,22 +36613,22 @@
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>47.57</v>
+        <v>45.13</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>45.32</v>
+        <v>43.87</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>44.13</v>
+        <v>42.34</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>42.74</v>
-      </c>
-      <c r="I240" s="3" t="n">
-        <v>41.43</v>
-      </c>
-      <c r="J240" s="3" t="n">
-        <v>40.79</v>
+        <v>40.8</v>
+      </c>
+      <c r="I240" s="4" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="J240" s="4" t="n">
+        <v>38.99</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -36659,22 +36659,22 @@
         </is>
       </c>
       <c r="E241" s="5" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="F241" s="5" t="n">
         <v>19.09</v>
       </c>
+      <c r="F241" s="4" t="n">
+        <v>20.74</v>
+      </c>
       <c r="G241" s="4" t="n">
-        <v>20.64</v>
+        <v>22.14</v>
       </c>
       <c r="H241" s="4" t="n">
-        <v>21.93</v>
+        <v>23.21</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>23.09</v>
+        <v>24.03</v>
       </c>
       <c r="J241" s="4" t="n">
-        <v>23.94</v>
+        <v>24.82</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
@@ -36705,22 +36705,22 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="F242" s="4" t="n">
-        <v>20.19</v>
+        <v>20.29</v>
+      </c>
+      <c r="F242" s="5" t="n">
+        <v>19.78</v>
       </c>
       <c r="G242" s="5" t="n">
-        <v>19.65</v>
+        <v>19.33</v>
       </c>
       <c r="H242" s="5" t="n">
-        <v>19.2</v>
+        <v>18.94</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="J242" s="5" t="n">
-        <v>19.8</v>
+        <v>19.49</v>
+      </c>
+      <c r="J242" s="4" t="n">
+        <v>20.8</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -36750,23 +36750,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E243" s="3" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="F243" s="3" t="n">
-        <v>40.08</v>
+      <c r="E243" s="4" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="F243" s="4" t="n">
+        <v>38.11</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>38.41</v>
+        <v>36.36</v>
       </c>
       <c r="H243" s="4" t="n">
-        <v>36.84</v>
+        <v>34.72</v>
       </c>
       <c r="I243" s="4" t="n">
-        <v>35.54</v>
+        <v>33.88</v>
       </c>
       <c r="J243" s="4" t="n">
-        <v>34.96</v>
+        <v>33.17</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
@@ -36797,22 +36797,22 @@
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>40.51</v>
+        <v>41.12</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>40.46</v>
+        <v>41.17</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>40.12</v>
+        <v>40.7</v>
       </c>
       <c r="H244" s="4" t="n">
-        <v>39.25</v>
+        <v>39.34</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>37.73</v>
+        <v>37.53</v>
       </c>
       <c r="J244" s="4" t="n">
-        <v>35.87</v>
+        <v>36.07</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -36843,22 +36843,22 @@
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>58.53</v>
+        <v>58.17</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>59.9</v>
+        <v>58.77</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>61.38</v>
+        <v>59.94</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>63.95</v>
+        <v>61.78</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>67.84</v>
+        <v>62.11</v>
       </c>
       <c r="J245" s="3" t="n">
-        <v>69.62</v>
+        <v>60.01</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
@@ -36892,19 +36892,19 @@
         <v>58.64</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>60.3</v>
+        <v>58.47</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>60.91</v>
+        <v>58.79</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>62.49</v>
+        <v>59.3</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>65.04000000000001</v>
+        <v>58.49</v>
       </c>
       <c r="J246" s="3" t="n">
-        <v>65.94</v>
+        <v>55.98</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -36935,22 +36935,22 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>67.23999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>70.56</v>
+        <v>71.81</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>72.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>73.47</v>
+        <v>71.67</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>74.06</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="J247" s="3" t="n">
-        <v>73.79000000000001</v>
+        <v>69.47</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
@@ -36981,22 +36981,22 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>25.32</v>
+        <v>25.55</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>24.59</v>
+        <v>25.73</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>24.19</v>
+        <v>27.43</v>
       </c>
       <c r="H248" s="4" t="n">
-        <v>24.75</v>
+        <v>29.46</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>25.05</v>
+        <v>32.78</v>
       </c>
       <c r="J248" s="4" t="n">
-        <v>27.94</v>
+        <v>38.77</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -37027,22 +37027,22 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>33.1</v>
+        <v>35.99</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>34.17</v>
-      </c>
-      <c r="G249" s="4" t="n">
-        <v>35.72</v>
-      </c>
-      <c r="H249" s="4" t="n">
-        <v>38.74</v>
+        <v>38.57</v>
+      </c>
+      <c r="G249" s="3" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>49.96</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>41.89</v>
+        <v>57.39</v>
       </c>
       <c r="J249" s="3" t="n">
-        <v>49.33</v>
+        <v>64.22</v>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
@@ -37073,22 +37073,22 @@
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>52.36</v>
+        <v>52.04</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>51.01</v>
+        <v>52.65</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>50.94</v>
+        <v>55.68</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>52.74</v>
+        <v>59.57</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>54.68</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="J250" s="3" t="n">
-        <v>59.6</v>
+        <v>73.23</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -37119,22 +37119,22 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>28.16</v>
+        <v>29.81</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>28.46</v>
+        <v>30.35</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>28.39</v>
+        <v>33.04</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>29.84</v>
-      </c>
-      <c r="I251" s="4" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="J251" s="4" t="n">
-        <v>36.71</v>
+        <v>36.78</v>
+      </c>
+      <c r="I251" s="3" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="J251" s="3" t="n">
+        <v>47.64</v>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
@@ -37165,22 +37165,22 @@
         </is>
       </c>
       <c r="E252" s="3" t="n">
-        <v>52.32</v>
+        <v>56.52</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>55.28</v>
+        <v>60.46</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>58.55</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>62.45</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>66.98999999999999</v>
-      </c>
-      <c r="J252" s="3" t="n">
-        <v>74.95</v>
+        <v>78.98</v>
+      </c>
+      <c r="J252" s="6" t="n">
+        <v>84.5</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -37211,22 +37211,22 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>35.19</v>
-      </c>
-      <c r="F253" s="4" t="n">
-        <v>37.34</v>
-      </c>
-      <c r="G253" s="4" t="n">
-        <v>39.56</v>
+        <v>37.97</v>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="G253" s="3" t="n">
+        <v>44.28</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>42.06</v>
+        <v>48.03</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>44.12</v>
+        <v>52.76</v>
       </c>
       <c r="J253" s="3" t="n">
-        <v>49.51</v>
+        <v>57.51</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
@@ -37257,22 +37257,22 @@
         </is>
       </c>
       <c r="E254" s="3" t="n">
-        <v>49.25</v>
+        <v>52.59</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>51.85</v>
+        <v>55.62</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>54.4</v>
+        <v>60.31</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>58.15</v>
+        <v>67.13</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="J254" s="3" t="n">
-        <v>72.23</v>
+        <v>75.81999999999999</v>
+      </c>
+      <c r="J254" s="6" t="n">
+        <v>84.03</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -37303,22 +37303,22 @@
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>60.8</v>
+        <v>63.12</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>62.23</v>
+        <v>65.05</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>63.62</v>
+        <v>68.94</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>66.56999999999999</v>
-      </c>
-      <c r="I255" s="3" t="n">
-        <v>70.65000000000001</v>
-      </c>
-      <c r="J255" s="3" t="n">
-        <v>77.58</v>
+        <v>74.45</v>
+      </c>
+      <c r="I255" s="6" t="n">
+        <v>80.84</v>
+      </c>
+      <c r="J255" s="6" t="n">
+        <v>86.83</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
@@ -37348,23 +37348,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E256" s="4" t="n">
-        <v>37.65</v>
-      </c>
-      <c r="F256" s="4" t="n">
-        <v>39.68</v>
+      <c r="E256" s="3" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>43.3</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>40.93</v>
+        <v>46.62</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>42.89</v>
+        <v>50.59</v>
       </c>
       <c r="I256" s="3" t="n">
-        <v>44.64</v>
+        <v>55.47</v>
       </c>
       <c r="J256" s="3" t="n">
-        <v>49.22</v>
+        <v>60.02</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -37395,22 +37395,22 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>27.02</v>
+        <v>28.53</v>
       </c>
       <c r="F257" s="4" t="n">
-        <v>28.49</v>
+        <v>30.64</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>30.57</v>
+        <v>33.8</v>
       </c>
       <c r="H257" s="4" t="n">
-        <v>33.56</v>
-      </c>
-      <c r="I257" s="4" t="n">
-        <v>37.02</v>
+        <v>37.79</v>
+      </c>
+      <c r="I257" s="3" t="n">
+        <v>42.69</v>
       </c>
       <c r="J257" s="3" t="n">
-        <v>41.74</v>
+        <v>46.14</v>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
@@ -37441,22 +37441,22 @@
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>37.14</v>
+        <v>38.25</v>
       </c>
       <c r="F258" s="4" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="G258" s="4" t="n">
-        <v>38.82</v>
-      </c>
-      <c r="H258" s="4" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="I258" s="4" t="n">
-        <v>39.82</v>
+        <v>39.46</v>
+      </c>
+      <c r="G258" s="3" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="H258" s="3" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="I258" s="3" t="n">
+        <v>43.16</v>
       </c>
       <c r="J258" s="3" t="n">
-        <v>41.36</v>
+        <v>47.13</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -37487,22 +37487,22 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>62.34</v>
+        <v>64.08</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>62.53</v>
+        <v>65.62</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>63.26</v>
+        <v>69.59</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>65.87</v>
-      </c>
-      <c r="I259" s="3" t="n">
-        <v>69.31</v>
-      </c>
-      <c r="J259" s="3" t="n">
-        <v>74.17</v>
+        <v>74.93000000000001</v>
+      </c>
+      <c r="I259" s="6" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="J259" s="6" t="n">
+        <v>85.54000000000001</v>
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
@@ -37533,22 +37533,22 @@
         </is>
       </c>
       <c r="E260" s="4" t="n">
-        <v>33.87</v>
+        <v>34.17</v>
       </c>
       <c r="F260" s="4" t="n">
-        <v>34.27</v>
+        <v>35.12</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>35.21</v>
+        <v>36.02</v>
       </c>
       <c r="H260" s="4" t="n">
-        <v>36.07</v>
+        <v>36.47</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>36.43</v>
-      </c>
-      <c r="J260" s="4" t="n">
-        <v>36.64</v>
+        <v>37.3</v>
+      </c>
+      <c r="J260" s="3" t="n">
+        <v>40.52</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -37579,22 +37579,22 @@
         </is>
       </c>
       <c r="E261" s="3" t="n">
-        <v>44.64</v>
+        <v>46.15</v>
       </c>
       <c r="F261" s="3" t="n">
-        <v>44.74</v>
+        <v>48.18</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>45.99</v>
+        <v>52.69</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>49.15</v>
+        <v>58.25</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>52.77</v>
+        <v>65.23</v>
       </c>
       <c r="J261" s="3" t="n">
-        <v>60.71</v>
+        <v>72.7</v>
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
@@ -37625,22 +37625,22 @@
         </is>
       </c>
       <c r="E262" s="3" t="n">
-        <v>49.45</v>
+        <v>51.44</v>
       </c>
       <c r="F262" s="3" t="n">
-        <v>50.43</v>
+        <v>53.55</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>51.91</v>
+        <v>57.75</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>55</v>
+        <v>63.58</v>
       </c>
       <c r="I262" s="3" t="n">
-        <v>58.97</v>
+        <v>70.05</v>
       </c>
       <c r="J262" s="3" t="n">
-        <v>64.44</v>
+        <v>77.64</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -37671,22 +37671,22 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>71.83</v>
+        <v>75.64</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>73.52</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>73.45999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>72.8</v>
+        <v>78.12</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>71.20999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="J263" s="3" t="n">
-        <v>71.64</v>
+        <v>76.09</v>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
@@ -37717,22 +37717,22 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>50.05</v>
+        <v>50.23</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>50.73</v>
+        <v>51.49</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>52.23</v>
+        <v>52.99</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>54.01</v>
+        <v>53.74</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>55.21</v>
+        <v>53.14</v>
       </c>
       <c r="J264" s="3" t="n">
-        <v>54.08</v>
+        <v>50.83</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -37763,22 +37763,22 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>56.57</v>
+        <v>56.84</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>56.58</v>
+        <v>57.35</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>56.93</v>
+        <v>58.34</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>57.68</v>
+        <v>59.57</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>58.5</v>
+        <v>60.48</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>59.03</v>
+        <v>60.74</v>
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
@@ -37809,22 +37809,22 @@
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>51.33</v>
+        <v>51.2</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>51.92</v>
+        <v>52.05</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>53.11</v>
+        <v>53.27</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>54.92</v>
+        <v>53.95</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>56.53</v>
+        <v>52.56</v>
       </c>
       <c r="J266" s="3" t="n">
-        <v>54.29</v>
+        <v>49.1</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -37855,22 +37855,22 @@
         </is>
       </c>
       <c r="E267" s="3" t="n">
-        <v>58.7</v>
+        <v>57.87</v>
       </c>
       <c r="F267" s="3" t="n">
-        <v>56.46</v>
+        <v>56.19</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>54.13</v>
+        <v>55.46</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>52.34</v>
+        <v>54.6</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>50.06</v>
+        <v>52.82</v>
       </c>
       <c r="J267" s="3" t="n">
-        <v>49.21</v>
+        <v>50.37</v>
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
@@ -37901,22 +37901,22 @@
         </is>
       </c>
       <c r="E268" s="4" t="n">
-        <v>36.63</v>
+        <v>35.55</v>
       </c>
       <c r="F268" s="4" t="n">
-        <v>35.94</v>
+        <v>34.91</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>35.52</v>
+        <v>34.75</v>
       </c>
       <c r="H268" s="4" t="n">
-        <v>35.69</v>
+        <v>34.82</v>
       </c>
       <c r="I268" s="4" t="n">
-        <v>36.2</v>
+        <v>34.56</v>
       </c>
       <c r="J268" s="4" t="n">
-        <v>35.76</v>
+        <v>33.02</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25604,32 +25604,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W36</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>W37</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>W38</t>
+          <t>W39</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -25665,22 +25665,22 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>65.06</v>
+        <v>64.34</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>64.06</v>
+        <v>63.24</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>62.8</v>
+        <v>62.41</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>61.73</v>
+        <v>61.79</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>60.5</v>
+        <v>59.84</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>58.02</v>
+        <v>57.94</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -25711,22 +25711,22 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>51.49</v>
+        <v>51.63</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>53.5</v>
+        <v>53.18</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>56</v>
+        <v>53.41</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>57.18</v>
+        <v>52.63</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>56.96</v>
+        <v>53.09</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>57.05</v>
+        <v>52.73</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -25757,22 +25757,22 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>65.22</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>66.67</v>
+        <v>70.44</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>68.95</v>
+        <v>73.22</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>72.51000000000001</v>
+        <v>72.09</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>74.47</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>73.22</v>
+        <v>66.58</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -25803,22 +25803,22 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>67.34</v>
+        <v>70.41</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>68.27</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>68.65000000000001</v>
+        <v>71.61</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>69.47</v>
+        <v>69.2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>69.43000000000001</v>
+        <v>64.12</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>69.11</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -25849,22 +25849,22 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>73.89</v>
+        <v>73.25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>73.8</v>
+        <v>72.22</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>72.98</v>
+        <v>70.2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>71.16</v>
+        <v>67</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>68.05</v>
+        <v>62.9</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>63.83</v>
+        <v>56.91</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -25895,22 +25895,22 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>68.53</v>
+        <v>68.88</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>70.55</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>70.3</v>
+        <v>66.11</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>69.78</v>
+        <v>63.36</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>68.81999999999999</v>
+        <v>61.98</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>68.93000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -25941,22 +25941,22 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>67.33</v>
+        <v>66.63</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>69.15000000000001</v>
+        <v>67.98</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>71.75</v>
+        <v>69.05</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>74.19</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>74.25</v>
+        <v>65.78</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>72.3</v>
+        <v>61.84</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -25987,22 +25987,22 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>36.37</v>
+        <v>35.87</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>36.46</v>
+        <v>35.72</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>36.53</v>
+        <v>36.01</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>37.13</v>
+        <v>36.63</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>38.27</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>41.09</v>
+        <v>37.88</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>36.23</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -26033,22 +26033,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>67.09</v>
+        <v>65.84</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>64.39</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>68.23999999999999</v>
+        <v>61.92</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>67.56</v>
+        <v>60.46</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>67.70999999999999</v>
+        <v>58.85</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -26079,22 +26079,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>49.66</v>
+        <v>50.92</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>51.06</v>
+        <v>52.46</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>52.64</v>
+        <v>53.17</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>53.4</v>
+        <v>52.45</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>52.76</v>
+        <v>50.11</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>50.35</v>
+        <v>46.54</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -26125,22 +26125,22 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>61.11</v>
+        <v>60.72</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>61.56</v>
+        <v>61.46</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>62.67</v>
+        <v>62.26</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>63.98</v>
+        <v>62.38</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>64.83</v>
+        <v>61.97</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>59.78</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -26171,22 +26171,22 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>51.43</v>
+        <v>51.9</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>52.33</v>
+        <v>52.95</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>53.52</v>
+        <v>53.37</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>54.16</v>
+        <v>51.61</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>52.78</v>
+        <v>48.2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>49.33</v>
+        <v>43.69</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -26217,22 +26217,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>63.75</v>
+        <v>61.91</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>63.44</v>
+        <v>60.48</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>62.71</v>
+        <v>58.08</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>61.17</v>
+        <v>54.95</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>59.17</v>
+        <v>52.61</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>58.21</v>
+        <v>50.89</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -26263,22 +26263,22 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>63.1</v>
+        <v>62.81</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>63.94</v>
+        <v>63.11</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>64.66</v>
+        <v>61.15</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>63.22</v>
+        <v>57.14</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>59.99</v>
+        <v>54.22</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>57.77</v>
+        <v>52.91</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -26309,22 +26309,22 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>63.58</v>
+        <v>63.31</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>63.19</v>
+        <v>63.92</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>63.36</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>63.24</v>
+        <v>63.06</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>60.95</v>
+        <v>59.84</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>59.77</v>
+        <v>58.29</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -26355,22 +26355,22 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>51.36</v>
+        <v>46.8</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>47</v>
+        <v>45.41</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45.77</v>
+        <v>46.22</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>46.55</v>
+        <v>46.79</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>47.24</v>
+        <v>47.06</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>48.14</v>
+        <v>46.56</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -26401,22 +26401,22 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>57.3</v>
+        <v>54.08</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>53.79</v>
+        <v>51.25</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>50.83</v>
+        <v>48.86</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>48.17</v>
+        <v>46.22</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>45.2</v>
+        <v>45.01</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>42.93</v>
+        <v>45.38</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -26447,22 +26447,22 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>66.45999999999999</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>67.66</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>69.31999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>70.58</v>
+        <v>69.33</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>69.41</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>68</v>
+        <v>62.56</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -26493,22 +26493,22 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>62.9</v>
+        <v>61.44</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>62.02</v>
+        <v>60.23</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>61.25</v>
+        <v>58.86</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>60.48</v>
+        <v>57.17</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>59.62</v>
+        <v>53.66</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>56.7</v>
+        <v>48.43</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -26539,22 +26539,22 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>62.19</v>
+        <v>62.41</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>62.01</v>
+        <v>63.81</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>63.3</v>
+        <v>65.25</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>64.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>62.38</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>62.98</v>
+        <v>58.66</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -26585,22 +26585,22 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>58.16</v>
+        <v>57.9</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>58.77</v>
+        <v>58.61</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>59.93</v>
+        <v>59.77</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>61.74</v>
+        <v>59.2</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>62.07</v>
+        <v>57.58</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>59.99</v>
+        <v>58.63</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -26631,22 +26631,22 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>58.85</v>
+        <v>61.15</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>61.87</v>
+        <v>62.97</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>63.95</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>65.95999999999999</v>
+        <v>62.66</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>64.73999999999999</v>
+        <v>62.99</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -26677,22 +26677,22 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>69.31</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>71.31</v>
+        <v>70.55</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>71.39</v>
+        <v>69.84</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>71.19</v>
+        <v>68.34</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>70.53</v>
+        <v>66.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>69.14</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -26723,22 +26723,22 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>75.38</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>77.14</v>
+        <v>74.67</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>76.48</v>
+        <v>72.36</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>74.98999999999999</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>73.09</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>70.7</v>
+        <v>62.35</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -26769,22 +26769,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>66.23</v>
+        <v>62.91</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>61.75</v>
+        <v>57.98</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>56.36</v>
+        <v>52.83</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>51.01</v>
+        <v>49.43</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>47.78</v>
+        <v>47.42</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>46.61</v>
+        <v>46.52</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -26815,22 +26815,22 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>54.62</v>
+        <v>52.09</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>52.11</v>
+        <v>50.67</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>50.98</v>
+        <v>49.62</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>50.08</v>
+        <v>48.46</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>49.22</v>
+        <v>47.72</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>48.5</v>
+        <v>47.69</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -26861,22 +26861,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>67.52</v>
+        <v>61.9</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>62.74</v>
+        <v>57.85</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>59.04</v>
+        <v>53.16</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>54.76</v>
+        <v>48.84</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>50.7</v>
+        <v>46.41</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>47.38</v>
+        <v>46.22</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -26907,22 +26907,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>57.76</v>
+        <v>57.62</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>55.53</v>
+        <v>55.29</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>51.96</v>
+        <v>52.77</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>47.87</v>
+        <v>50.97</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>43.79</v>
+        <v>48.92</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>40.92</v>
+        <v>48.73</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -26953,22 +26953,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>45.62</v>
+        <v>44.27</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>43.01</v>
+        <v>42.38</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>40.46</v>
+        <v>40.75</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>38.02</v>
+        <v>39.31</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>35.69</v>
+        <v>37.6</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>34.17</v>
+        <v>36.61</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -26999,22 +26999,22 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>51.27</v>
+        <v>52.19</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>49.5</v>
+        <v>50.85</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>47.31</v>
+        <v>49.92</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>45.6</v>
+        <v>49.41</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>44.81</v>
+        <v>49.3</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46.25</v>
+        <v>49.99</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -27045,22 +27045,22 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>52.49</v>
+        <v>51.38</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>51.29</v>
+        <v>49.52</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>49.36</v>
+        <v>47.24</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>46.93</v>
+        <v>46.35</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>45.77</v>
+        <v>45.96</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>45.54</v>
+        <v>46.19</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -27091,22 +27091,22 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>43.42</v>
+        <v>44.08</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>44.53</v>
+        <v>45.03</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45.87</v>
+        <v>47.32</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>48.74</v>
+        <v>48.28</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>50.15</v>
+        <v>48.29</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>49.59</v>
+        <v>45.7</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -27136,23 +27136,23 @@
           <t>大麦</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n">
-        <v>19.23</v>
+      <c r="E34" s="4" t="n">
+        <v>20.49</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>20.99</v>
+        <v>21.76</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>22.48</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>23.57</v>
+        <v>22.66</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24.28</v>
+        <v>23.26</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>24.98</v>
+        <v>24.12</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -27182,23 +27182,23 @@
           <t>大麦</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
-        <v>38.21</v>
+      <c r="E35" s="3" t="n">
+        <v>40.19</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>40.25</v>
+        <v>42.08</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>42.02</v>
+        <v>43.67</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>43.48</v>
+        <v>43.1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>42.77</v>
+        <v>42.74</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>42.53</v>
+        <v>41.8</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -27228,23 +27228,23 @@
           <t>大麦</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>20</v>
+      <c r="E36" s="5" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>19.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>19.52</v>
+        <v>18.86</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>19.64</v>
+        <v>19.37</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>20.73</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>20.95</v>
+        <v>22.54</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -27275,22 +27275,22 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>38.97</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>39.66</v>
+        <v>39.73</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>40.76</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>40.61</v>
+        <v>41.97</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>41.71</v>
+        <v>42.92</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>42.47</v>
+        <v>43.85</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>42.55</v>
+        <v>42.61</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -27321,22 +27321,22 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>55.86</v>
+        <v>56.08</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>56.47</v>
+        <v>55.54</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>55.75</v>
+        <v>55.4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>55.45</v>
+        <v>53.76</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>53.68</v>
+        <v>51.84</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>52.05</v>
+        <v>48.76</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -27366,23 +27366,23 @@
           <t>大麦</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>40.78</v>
+      <c r="E39" s="4" t="n">
+        <v>39.02</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>39.01</v>
+        <v>37.38</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>37.25</v>
+        <v>35.84</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>35.63</v>
+        <v>35.02</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>34.79</v>
+        <v>34.5</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>34.07</v>
+        <v>34.43</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -27413,22 +27413,22 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>41.08</v>
+        <v>40.87</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>41.14</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>40.76</v>
+        <v>40.38</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>38.98</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>39.58</v>
+        <v>37.02</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>37.97</v>
+        <v>35.47</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>36.59</v>
+        <v>34.01</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -27459,22 +27459,22 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>56.86</v>
+        <v>55.16</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>56.78</v>
+        <v>54.59</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>57.03</v>
+        <v>53.73</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>57.39</v>
+        <v>52.83</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>58.33</v>
+        <v>52.32</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>59.26</v>
+        <v>55.04</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -27505,22 +27505,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>66.19</v>
+        <v>65.09</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>64.56</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>66.14</v>
+        <v>64.31</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>66.62</v>
+        <v>63.27</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>66.64</v>
+        <v>62.66</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>67.55</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -27551,22 +27551,22 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>58.34</v>
+        <v>58.12</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>58.42</v>
+        <v>58.19</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>58.68</v>
+        <v>58.79</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>59.54</v>
+        <v>59.31</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>60.48</v>
+        <v>60.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>62.41</v>
+        <v>63.08</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -27597,22 +27597,22 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>55.64</v>
+        <v>53.67</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>54.32</v>
+        <v>52.15</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>53.25</v>
+        <v>50.66</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>52.45</v>
+        <v>49.76</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>52.6</v>
+        <v>50.7</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>55.32</v>
+        <v>55.16</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -27643,22 +27643,22 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>57.79</v>
+        <v>57.69</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>58.52</v>
+        <v>58.49</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>59.75</v>
+        <v>59.73</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>61.61</v>
+        <v>59.26</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>62</v>
+        <v>57.73</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>60.07</v>
+        <v>58.8</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -27689,22 +27689,22 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>64.76000000000001</v>
+        <v>67.66</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>66.22</v>
+        <v>70.38</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>68.56999999999999</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>74.56</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>73.48999999999999</v>
+        <v>66.16</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -27735,22 +27735,22 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>53.96</v>
+        <v>51.52</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>50.51</v>
+        <v>49.17</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>48.04</v>
+        <v>48.41</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46.98</v>
+        <v>49.57</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>47.49</v>
+        <v>50.8</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>47.94</v>
+        <v>54.26</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -27781,22 +27781,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>52.2</v>
+        <v>51.79</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>51.12</v>
+        <v>51.13</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>50.14</v>
+        <v>50.65</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>49.24</v>
+        <v>49.54</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>47.72</v>
+        <v>47.78</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>46.4</v>
+        <v>45.11</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -27827,22 +27827,22 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>52.93</v>
+        <v>57.1</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>55.29</v>
+        <v>60.53</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>58.3</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>62.09</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>65.27</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>65.73</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -27873,22 +27873,22 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>70.23999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>65.88</v>
+        <v>61.11</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>60.52</v>
+        <v>58.1</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>57.41</v>
+        <v>57.91</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>57.03</v>
+        <v>59.2</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>57.7</v>
+        <v>61.03</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -27919,22 +27919,22 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>67.70999999999999</v>
+        <v>70.64</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>68.52</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>68.8</v>
+        <v>71.56</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>69.52</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>69.45</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>69.22</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -27965,22 +27965,22 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>66.23</v>
+        <v>62.9</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>61.74</v>
+        <v>57.99</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>56.37</v>
+        <v>52.85</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>51.04</v>
+        <v>49.45</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>47.81</v>
+        <v>47.44</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>46.63</v>
+        <v>46.54</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -28011,22 +28011,22 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>54.43</v>
+        <v>51.93</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>51.94</v>
+        <v>50.54</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>50.85</v>
+        <v>49.55</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>49.99</v>
+        <v>48.43</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>49.18</v>
+        <v>47.73</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>48.5</v>
+        <v>47.7</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -28057,22 +28057,22 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>67.31</v>
+        <v>61.73</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>62.57</v>
+        <v>57.73</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>58.93</v>
+        <v>53.07</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>54.68</v>
+        <v>48.8</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>50.66</v>
+        <v>46.42</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>47.4</v>
+        <v>46.25</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -28103,22 +28103,22 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>58.58</v>
+        <v>58.41</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>56.66</v>
+        <v>56.38</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>53.58</v>
+        <v>54.06</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>49.87</v>
+        <v>52.19</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>46.18</v>
+        <v>50.18</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>43.55</v>
+        <v>49.68</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -28149,22 +28149,22 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46.29</v>
+        <v>44.87</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>43.62</v>
+        <v>42.89</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>40.98</v>
+        <v>41.14</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>38.39</v>
+        <v>39.61</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>36.01</v>
+        <v>37.88</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>34.5</v>
+        <v>36.88</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -28195,22 +28195,22 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>50.82</v>
+        <v>51.78</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>49.12</v>
+        <v>50.51</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>47.02</v>
+        <v>49.7</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>45.45</v>
+        <v>49.26</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>44.77</v>
+        <v>49.27</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>46.29</v>
+        <v>50.04</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -28241,22 +28241,22 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>56.94</v>
+        <v>56.86</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>56.83</v>
+        <v>56.06</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>55.99</v>
+        <v>54.57</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>54.4</v>
+        <v>51.99</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>51.64</v>
+        <v>48.34</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>47.18</v>
+        <v>46.6</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -28287,22 +28287,22 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>64.47</v>
+        <v>63.12</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>63.89</v>
+        <v>61.18</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>62.36</v>
+        <v>59.47</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>61.09</v>
+        <v>57.41</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>59.57</v>
+        <v>53.46</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>54.41</v>
+        <v>49.64</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -28333,22 +28333,22 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="H60" s="3" t="n">
         <v>54.96</v>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>55.25</v>
-      </c>
       <c r="I60" s="3" t="n">
-        <v>55.8</v>
+        <v>55.39</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>56.46</v>
+        <v>53.77</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -28379,22 +28379,22 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>65.39</v>
+        <v>62.73</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>63.4</v>
+        <v>59.83</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>60.97</v>
+        <v>56.52</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>58.2</v>
+        <v>53.08</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>55.26</v>
+        <v>49.23</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>50.1</v>
+        <v>46.7</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -28425,22 +28425,22 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>47.12</v>
+        <v>49.07</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>49.87</v>
+        <v>51.34</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>52.8</v>
+        <v>53.47</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>56.04</v>
+        <v>56.71</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>60.72</v>
+        <v>60.85</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>65</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -28471,22 +28471,22 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>57.66</v>
+        <v>59.48</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>60.66</v>
+        <v>62.63</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>64.47</v>
+        <v>65.62</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>68.5</v>
+        <v>69.05</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>73.54000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>78.22</v>
+        <v>76.83</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -28517,22 +28517,22 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>63.99</v>
+        <v>63.44</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>64.44</v>
+        <v>64.87</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>66.34</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>69.56</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>73.79000000000001</v>
+        <v>74.39</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>78.04000000000001</v>
+        <v>77.67</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -28563,22 +28563,22 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>58.81</v>
+        <v>58.75</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>59.53</v>
+        <v>59.72</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>61.11</v>
+        <v>61.52</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>63.88</v>
+        <v>65.19</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>68.89</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>73.31</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -28609,19 +28609,19 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>63.44</v>
+        <v>62.78</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>63.99</v>
+        <v>64.03</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>66.89</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>69.92</v>
+        <v>72.23</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>76.66</v>
+        <v>78.66</v>
       </c>
       <c r="J66" s="6" t="n">
         <v>83.11</v>
@@ -28655,22 +28655,22 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>45.35</v>
+        <v>44.33</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>44.13</v>
+        <v>43.08</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>42.65</v>
+        <v>41.89</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>41.18</v>
+        <v>41.52</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>40.49</v>
-      </c>
-      <c r="J67" s="4" t="n">
-        <v>39.49</v>
+        <v>41.39</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>41.67</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
@@ -28701,22 +28701,22 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>37.06</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>39.01</v>
+        <v>38.87</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>40.23</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>40.29</v>
+        <v>41.34</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>41.41</v>
+        <v>42.06</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>42</v>
+        <v>42.8</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>42.23</v>
+        <v>42.2</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -28746,23 +28746,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>19.74</v>
+      <c r="E69" s="4" t="n">
+        <v>20.98</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>21.49</v>
+        <v>22.24</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>22.99</v>
+        <v>22.98</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>24.11</v>
+        <v>23.2</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>24.87</v>
+        <v>23.84</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>25.58</v>
+        <v>24.72</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
@@ -28792,23 +28792,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E70" s="4" t="n">
-        <v>38.13</v>
+      <c r="E70" s="3" t="n">
+        <v>40.13</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>40.18</v>
+        <v>42.03</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>41.97</v>
+        <v>43.63</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>43.43</v>
+        <v>43.07</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>42.73</v>
+        <v>42.72</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>42.51</v>
+        <v>41.79</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -28838,23 +28838,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E71" s="4" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>20.01</v>
+      <c r="E71" s="5" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>19.31</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>19.54</v>
+        <v>18.87</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>19.66</v>
+        <v>19.39</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>20.75</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>20.97</v>
+        <v>22.56</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
@@ -28885,22 +28885,22 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>39.38</v>
+        <v>39.47</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>40.49</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>40.31</v>
+        <v>41.71</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>41.41</v>
+        <v>42.68</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>42.17</v>
+        <v>43.65</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -28931,22 +28931,22 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>55.87</v>
+        <v>56.09</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>56.47</v>
+        <v>55.55</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>55.75</v>
+        <v>55.4</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>55.45</v>
+        <v>53.77</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>53.68</v>
+        <v>51.85</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>52.06</v>
+        <v>48.77</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
@@ -28976,23 +28976,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E74" s="3" t="n">
-        <v>40.79</v>
+      <c r="E74" s="4" t="n">
+        <v>39.04</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>39.03</v>
+        <v>37.4</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>37.27</v>
+        <v>35.87</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>35.66</v>
+        <v>35.05</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>34.82</v>
+        <v>34.54</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>34.1</v>
+        <v>34.47</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -29023,22 +29023,22 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>41.25</v>
+        <v>40.99</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>41.26</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>40.89</v>
+        <v>40.49</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>39.17</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>39.79</v>
+        <v>37.3</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>38.28</v>
+        <v>35.84</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>37</v>
+        <v>34.45</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
@@ -29069,22 +29069,22 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>29.98</v>
+        <v>30.6</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>30.29</v>
+        <v>31.57</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>31.05</v>
+        <v>33.39</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>32.55</v>
+        <v>34.76</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>33.44</v>
+        <v>35.45</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>33.31</v>
+        <v>34.87</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -29115,22 +29115,22 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>56.21</v>
+        <v>54.46</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>56.08</v>
+        <v>53.88</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>56.32</v>
+        <v>52.99</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>56.65</v>
+        <v>52.03</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>57.53</v>
+        <v>51.47</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>58.36</v>
+        <v>54.15</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
@@ -29161,22 +29161,22 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>35.14</v>
+        <v>34</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>34.09</v>
+        <v>32.9</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>33.07</v>
+        <v>31.68</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>32.01</v>
+        <v>31.27</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>31.82</v>
+        <v>31.66</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>32.61</v>
+        <v>34.2</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -29207,22 +29207,22 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>64.81</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>65.84999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>65.86</v>
+        <v>64.03</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>66.33</v>
+        <v>62.99</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>66.33</v>
+        <v>62.4</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>67.26000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -29253,22 +29253,22 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>57.98</v>
+        <v>57.72</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>58.04</v>
+        <v>57.78</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>58.29</v>
+        <v>58.31</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>59.11</v>
+        <v>58.76</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>59.99</v>
+        <v>59.55</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>61.8</v>
+        <v>62.34</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -29299,22 +29299,22 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>55.54</v>
+        <v>53.57</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>54.22</v>
+        <v>52.06</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>53.16</v>
+        <v>50.58</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>52.36</v>
+        <v>49.71</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>52.53</v>
+        <v>50.65</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>55.25</v>
+        <v>55.11</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -29345,22 +29345,22 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>32.13</v>
+        <v>35.65</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>34.46</v>
+        <v>38.09</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>37.07</v>
+        <v>39.37</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>35.95</v>
+        <v>37.89</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>34.15</v>
+        <v>35.82</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -29391,22 +29391,22 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>57.72</v>
+        <v>56.58</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>55.91</v>
+        <v>56.07</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>55.07</v>
+        <v>55.61</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>54.13</v>
+        <v>54.37</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>52.36</v>
+        <v>53.55</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>50.05</v>
+        <v>53.48</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -29437,22 +29437,22 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>52.2</v>
+        <v>48.06</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>48.59</v>
+        <v>46.94</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>47.76</v>
+        <v>47.67</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>48.65</v>
+        <v>48.08</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>49.25</v>
+        <v>48.15</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>49.61</v>
+        <v>47.6</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -29483,22 +29483,22 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>42.08</v>
+        <v>44.19</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>44.59</v>
+        <v>46.07</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>46.78</v>
+        <v>46.14</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>47.25</v>
+        <v>44.54</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>46.21</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>40.68</v>
+        <v>40.78</v>
+      </c>
+      <c r="J85" s="4" t="n">
+        <v>38.05</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -29529,22 +29529,22 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>58.36</v>
+        <v>57.15</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>57.85</v>
+        <v>56.78</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>57.98</v>
+        <v>56.21</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>58.14</v>
+        <v>54.69</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>57.62</v>
+        <v>51.33</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>54.48</v>
+        <v>46.24</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -29574,23 +29574,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E87" s="3" t="n">
-        <v>40.61</v>
+      <c r="E87" s="4" t="n">
+        <v>38.16</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>37.53</v>
+        <v>37.07</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>36.12</v>
+        <v>36.51</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>35.04</v>
+        <v>35.43</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>33.27</v>
+        <v>34.41</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>30.65</v>
+        <v>34.2</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -29621,22 +29621,22 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>35.28</v>
+        <v>38.06</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>37.03</v>
+        <v>39.91</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>38.33</v>
+        <v>39.58</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>37.28</v>
+        <v>39.04</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>35.94</v>
+        <v>37.51</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>33.07</v>
+        <v>36.19</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -29667,22 +29667,22 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>58.26</v>
+        <v>58.03</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>58.9</v>
+        <v>58.76</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>60.08</v>
+        <v>59.91</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>61.9</v>
+        <v>59.35</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>62.24</v>
+        <v>57.79</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>60.26</v>
+        <v>58.84</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -29713,22 +29713,22 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>58.79</v>
+        <v>61.05</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>61.8</v>
+        <v>62.89</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>63.84</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>65.95</v>
+        <v>62.55</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>64.73</v>
+        <v>62.81</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -29759,22 +29759,22 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>69.5</v>
+        <v>70.94</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>71.51000000000001</v>
+        <v>70.75</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>71.61</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>71.39</v>
+        <v>68.47</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>70.72</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>69.3</v>
+        <v>65.73</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
@@ -29805,22 +29805,22 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>59.44</v>
+        <v>58.84</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>58.43</v>
+        <v>58.25</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>57.61</v>
+        <v>57.73</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>56.75</v>
+        <v>56.41</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>55.04</v>
+        <v>54.18</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>52.77</v>
+        <v>50.87</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -29851,22 +29851,22 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>46.59</v>
+        <v>48.77</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>49.7</v>
+        <v>51.64</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>53.41</v>
+        <v>54.38</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>57.39</v>
+        <v>58.36</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>62.74</v>
+        <v>62.26</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>67.33</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
@@ -29897,22 +29897,22 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>46.85</v>
+        <v>46.03</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>46.01</v>
+        <v>45.05</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>45.2</v>
+        <v>44.64</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>45.01</v>
+        <v>44.23</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>44.89</v>
+        <v>43.65</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>45.56</v>
+        <v>43.81</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -29943,22 +29943,22 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>45.38</v>
+        <v>47.9</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>48.02</v>
+        <v>51.9</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>52.27</v>
+        <v>57.27</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>57.95</v>
+        <v>63.8</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>64.61</v>
+        <v>70.05</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>70.98</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
@@ -29988,23 +29988,23 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E96" s="3" t="n">
-        <v>41.38</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>40.15</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>40.23</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>40.63</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>41.34</v>
+      <c r="E96" s="4" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>38.97</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -30035,22 +30035,22 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>62.3</v>
+        <v>61.89</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>63.77</v>
+        <v>63.06</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>65.7</v>
+        <v>66.39</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>70.39</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>74.84</v>
+        <v>72.94</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
@@ -30081,22 +30081,22 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>47.89</v>
+        <v>49.08</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>49.61</v>
+        <v>50.53</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>51.81</v>
+        <v>52.57</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>54.86</v>
+        <v>55.46</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>59.05</v>
+        <v>57.33</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>63.08</v>
+        <v>58.98</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -30127,22 +30127,22 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>65.53</v>
+        <v>64.36</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>66.94</v>
+        <v>65.19</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>69.08</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>71.11</v>
+        <v>63.96</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>70.98</v>
+        <v>61.83</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>68.63</v>
+        <v>58.01</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -30173,22 +30173,22 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>37.65</v>
+        <v>37.28</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>38.08</v>
+        <v>37.49</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>38.61</v>
+        <v>38.2</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>39.77</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="J100" s="3" t="n">
-        <v>42.87</v>
+        <v>38.71</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="J100" s="4" t="n">
+        <v>36.93</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -30219,22 +30219,22 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>58.6</v>
+        <v>57.34</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>58.85</v>
+        <v>57.13</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>59.4</v>
+        <v>56.31</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>59.7</v>
+        <v>55.28</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>60.3</v>
+        <v>54.55</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>60.84</v>
+        <v>57</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -30265,22 +30265,22 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>39.49</v>
+        <v>38.84</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>38.85</v>
+        <v>38.12</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>38.16</v>
+        <v>37.43</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>37.55</v>
+        <v>37.53</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>37.77</v>
-      </c>
-      <c r="J102" s="4" t="n">
-        <v>39.23</v>
+        <v>38.49</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>41.09</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -30311,22 +30311,22 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>60.86</v>
+        <v>59.19</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>58.06</v>
+        <v>55.93</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>54.25</v>
+        <v>52.82</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>50.46</v>
+        <v>50.61</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>47.46</v>
+        <v>49.68</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>46.71</v>
+        <v>49.95</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -30356,23 +30356,23 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E104" s="3" t="n">
-        <v>44.35</v>
+      <c r="E104" s="4" t="n">
+        <v>39.09</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>39.91</v>
+        <v>35</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>36.25</v>
+        <v>32.21</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>34.02</v>
+        <v>30.37</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>33.06</v>
+        <v>29.44</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>32.41</v>
+        <v>31.22</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -30403,22 +30403,22 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>55.23</v>
+        <v>55.65</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>56.41</v>
+        <v>54.67</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>55.74</v>
+        <v>53.79</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>55.23</v>
+        <v>53.27</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>55.12</v>
+        <v>52.87</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>55.55</v>
+        <v>51.85</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -30449,22 +30449,22 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>48.52</v>
+        <v>45.85</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>45.05</v>
+        <v>42.82</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>41.7</v>
+        <v>40.84</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>39.34</v>
+        <v>39.23</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>37.45</v>
-      </c>
-      <c r="J106" s="4" t="n">
-        <v>36.92</v>
+        <v>38.87</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>40.4</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -30495,22 +30495,22 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>58.01</v>
+        <v>53.73</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>53.85</v>
+        <v>48.56</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>48.95</v>
+        <v>43.88</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>41.95</v>
-      </c>
-      <c r="J107" s="3" t="n">
-        <v>41.04</v>
+        <v>40.66</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="J107" s="4" t="n">
+        <v>39.52</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -30541,22 +30541,22 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>54.46</v>
+        <v>54.34</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>53.57</v>
+        <v>51.99</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>50.92</v>
+        <v>49.88</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>48.33</v>
+        <v>49</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>46.8</v>
+        <v>48.38</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>45.42</v>
+        <v>49.61</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -30587,22 +30587,22 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>58.85</v>
+        <v>54.64</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>54.46</v>
+        <v>49.75</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>49.54</v>
+        <v>45.54</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>45.29</v>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>41.52</v>
-      </c>
-      <c r="J109" s="4" t="n">
-        <v>39.3</v>
+        <v>41.77</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>40.39</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -30633,22 +30633,22 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>34.69</v>
+        <v>34.08</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>33.88</v>
+        <v>34.01</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>33.64</v>
+        <v>34.19</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>33.52</v>
+        <v>34.23</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>33.11</v>
+        <v>33.7</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>31.22</v>
+        <v>32.72</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -30679,22 +30679,22 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>35.06</v>
+        <v>33.51</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>33.9</v>
+        <v>32.52</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>33.15</v>
+        <v>30.91</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>31.9</v>
+        <v>29.3</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>30.79</v>
+        <v>28.12</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>29.4</v>
+        <v>28.19</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
@@ -30725,22 +30725,22 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>30.48</v>
+        <v>28.21</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>28.86</v>
+        <v>27.45</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>28.38</v>
+        <v>26.73</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>27.97</v>
+        <v>25.8</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>27.5</v>
+        <v>25.69</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>26.99</v>
+        <v>25.29</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -30771,22 +30771,22 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>44.76</v>
+        <v>43.73</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>42.05</v>
+        <v>43.44</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>42.3</v>
+        <v>44.49</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>42.7</v>
+        <v>45.8</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>43.8</v>
+        <v>46.28</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
@@ -30817,22 +30817,22 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>33.94</v>
+        <v>34.65</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>34.41</v>
+        <v>35.69</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>35.35</v>
+        <v>37.18</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>36.66</v>
-      </c>
-      <c r="I114" s="4" t="n">
-        <v>37.89</v>
+        <v>38.73</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>41.26</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>40.59</v>
+        <v>41.3</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -30863,22 +30863,22 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>33.43</v>
+        <v>33.89</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>33.31</v>
+        <v>34.37</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>33.76</v>
+        <v>37.02</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>36.24</v>
-      </c>
-      <c r="I115" s="4" t="n">
-        <v>38.32</v>
+        <v>39.19</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>40.95</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>40.62</v>
+        <v>40.1</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
@@ -30908,23 +30908,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E116" s="3" t="n">
-        <v>40.36</v>
+      <c r="E116" s="4" t="n">
+        <v>37.63</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>37.73</v>
+        <v>35.89</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>36.11</v>
+        <v>37.55</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>37.96</v>
-      </c>
-      <c r="I116" s="4" t="n">
-        <v>39.74</v>
+        <v>39.24</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>40.5</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>40.24</v>
+        <v>40.62</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -30955,22 +30955,22 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>26.35</v>
+        <v>25.8</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>26.2</v>
+        <v>26.22</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>26.89</v>
+        <v>26.64</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>27.5</v>
+        <v>27.25</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>28.04</v>
+        <v>28.42</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>28.66</v>
+        <v>28.45</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
@@ -31001,22 +31001,22 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>37.67</v>
+        <v>36.19</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>36.47</v>
+        <v>35.93</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>36.33</v>
+        <v>36.96</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>37.51</v>
-      </c>
-      <c r="I118" s="4" t="n">
-        <v>39.12</v>
+        <v>38.16</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>40.39</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>41</v>
+        <v>41.74</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -31047,22 +31047,22 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>40.83</v>
-      </c>
-      <c r="G119" s="4" t="n">
-        <v>39.94</v>
+        <v>40.84</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>40.71</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>40.65</v>
+        <v>41.46</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>41.25</v>
+        <v>42.78</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>41.95</v>
+        <v>42.51</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
@@ -31093,22 +31093,22 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>42.17</v>
+        <v>41.67</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="G120" s="4" t="n">
-        <v>39.93</v>
-      </c>
-      <c r="H120" s="4" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="I120" s="4" t="n">
-        <v>39.12</v>
+        <v>41.32</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>43.89</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>40.55</v>
+        <v>44.71</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -31139,22 +31139,22 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>40</v>
+        <v>38.71</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>38.93</v>
+        <v>37.83</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>38.2</v>
+        <v>37.39</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>37.97</v>
+        <v>37.16</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>37.85</v>
+        <v>37.17</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>37.45</v>
+        <v>37.77</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
@@ -31185,22 +31185,22 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>34.02</v>
+        <v>32.46</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>33.41</v>
+        <v>32.04</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>33.66</v>
+        <v>31.85</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>34.32</v>
+        <v>32.05</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>35.35</v>
+        <v>32.91</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>34.96</v>
+        <v>32.21</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -31231,22 +31231,22 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>48.9</v>
+        <v>48.84</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>49.01</v>
+        <v>49.14</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>49.56</v>
+        <v>49.21</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>49.97</v>
+        <v>49.35</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>50.55</v>
+        <v>49.7</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>51.43</v>
+        <v>50.02</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
@@ -31277,22 +31277,22 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>70.83</v>
+        <v>70.38</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>70.09</v>
+        <v>68.8</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>68.39</v>
+        <v>66.48</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>65.81999999999999</v>
+        <v>63.86</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>62.76</v>
+        <v>61.18</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>59.18</v>
+        <v>58.91</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -31323,22 +31323,22 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>64.41</v>
+        <v>63.79</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>63.54</v>
+        <v>62.78</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>62.37</v>
+        <v>62.05</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>61.38</v>
+        <v>61.43</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>60.2</v>
+        <v>59.51</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>57.81</v>
+        <v>57.66</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
@@ -31369,22 +31369,22 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>51.02</v>
+        <v>51.09</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>52.76</v>
+        <v>52.42</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>54.97</v>
+        <v>52.58</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>56.04</v>
+        <v>51.91</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>55.99</v>
+        <v>52.41</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>56.22</v>
+        <v>52.19</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -31415,22 +31415,22 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>53.83</v>
+        <v>51.33</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>50.35</v>
+        <v>48.98</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>47.9</v>
+        <v>48.21</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>46.84</v>
+        <v>49.37</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>47.37</v>
+        <v>50.61</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>47.83</v>
+        <v>54.05</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
@@ -31461,22 +31461,22 @@
         </is>
       </c>
       <c r="E128" s="6" t="n">
-        <v>82.42</v>
-      </c>
-      <c r="F128" s="6" t="n">
-        <v>80.7</v>
+        <v>80.59</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>78.06999999999999</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>78.33</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>75.45999999999999</v>
+        <v>72.53</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>73.45</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>71.62</v>
+        <v>68.45</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -31507,22 +31507,22 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>53.04</v>
+        <v>52.54</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>51.87</v>
+        <v>51.71</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>50.72</v>
+        <v>51.11</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>49.68</v>
+        <v>49.86</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>48.03</v>
+        <v>47.97</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>46.54</v>
+        <v>45.14</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
@@ -31553,22 +31553,22 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>70.59</v>
+        <v>66.81</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>66.22</v>
+        <v>61.68</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>60.84</v>
+        <v>58.33</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>57.35</v>
+        <v>57.67</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>56.51</v>
+        <v>58.63</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>56.81</v>
+        <v>60.35</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -31599,22 +31599,22 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>67.53</v>
+        <v>70.42</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>68.31</v>
+        <v>70.91</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>68.54000000000001</v>
+        <v>71.22</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>69.19</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>69.15000000000001</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>69.06</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
@@ -31645,22 +31645,22 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>60.45</v>
+        <v>59.81</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>59.01</v>
+        <v>57.91</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>56.97</v>
+        <v>55.79</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>54.75</v>
+        <v>54.25</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>53.02</v>
+        <v>53.14</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>51.34</v>
+        <v>54.38</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -31691,22 +31691,22 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>73.13</v>
+        <v>72.66</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>72.83</v>
+        <v>71.75</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>71.94</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>70.22</v>
+        <v>67.11</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>67.2</v>
+        <v>63.12</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>63.17</v>
+        <v>57.21</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
@@ -31737,22 +31737,22 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>46.35</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>41.69</v>
+        <v>42.59</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>38.66</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>37.6</v>
+        <v>36.56</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>35.4</v>
+        <v>36.31</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>35.48</v>
+        <v>36.7</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>36.3</v>
+        <v>37.98</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -31783,22 +31783,22 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>56.63</v>
+        <v>51.04</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>49.9</v>
+        <v>45.89</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>44.61</v>
+        <v>42.59</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>41.47</v>
+        <v>41.72</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>40.96</v>
+        <v>41.25</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>41</v>
+        <v>41.63</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
@@ -31829,22 +31829,22 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>48.92</v>
+        <v>46.39</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>41.05</v>
+        <v>42.59</v>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>37.93</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>36.19</v>
+        <v>34.88</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>33.33</v>
+        <v>33.55</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>32.73</v>
+        <v>32.88</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -31874,23 +31874,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E137" s="3" t="n">
-        <v>40.57</v>
+      <c r="E137" s="4" t="n">
+        <v>39.38</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>37.55</v>
+        <v>36.45</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>34.06</v>
+        <v>33.77</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>31.11</v>
+        <v>32.74</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>29.89</v>
+        <v>33.23</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>31.08</v>
+        <v>34.17</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
@@ -31921,22 +31921,22 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="F138" s="4" t="n">
-        <v>20.07</v>
+        <v>20.86</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>18.66</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>17.64</v>
+        <v>16.43</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>15.41</v>
+        <v>15.57</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>14.57</v>
+        <v>15.53</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>14.55</v>
+        <v>16.78</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -31967,22 +31967,22 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>59.27</v>
+        <v>57.54</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>57.36</v>
+        <v>54.76</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>54.39</v>
+        <v>51.81</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>51.29</v>
+        <v>49.25</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>48.68</v>
+        <v>46.4</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>45.44</v>
+        <v>44.7</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
@@ -32013,22 +32013,22 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>46.27</v>
+        <v>44.9</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>43.95</v>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>40.36</v>
+        <v>41.75</v>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>37.49</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>35.98</v>
+        <v>35.82</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>34.24</v>
+        <v>34.62</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>33.08</v>
+        <v>33.28</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -32059,22 +32059,22 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>49.72</v>
+        <v>46.06</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>45.18</v>
+        <v>42.51</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>41.38</v>
+        <v>40.38</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>39.17</v>
+        <v>39.82</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>38.81</v>
-      </c>
-      <c r="J141" s="4" t="n">
-        <v>39.13</v>
+        <v>39.6</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>40.39</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -32105,22 +32105,22 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>31.94</v>
+        <v>30.67</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>30.2</v>
+        <v>28.78</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>28.01</v>
+        <v>26.17</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>25.25</v>
+        <v>24.58</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>23.58</v>
+        <v>23.51</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>22.38</v>
+        <v>22.43</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -32151,22 +32151,22 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>35.6</v>
+        <v>33.83</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>33.77</v>
+        <v>32.4</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>32.13</v>
+        <v>31.46</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>31.04</v>
+        <v>30.69</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>30.25</v>
+        <v>30.31</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>29.23</v>
+        <v>29.26</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
@@ -32197,22 +32197,22 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>58.57</v>
+        <v>54.2</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>52.76</v>
+        <v>48.1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>46.3</v>
+        <v>43.16</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>41.24</v>
+        <v>40.44</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>38.79</v>
+        <v>39.07</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>38.28</v>
+        <v>37.83</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -32243,22 +32243,22 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>64.97</v>
+        <v>60.4</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>58.63</v>
+        <v>54.99</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>52.54</v>
+        <v>50.56</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>47.8</v>
+        <v>47.75</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>45.15</v>
+        <v>45.43</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>43.98</v>
+        <v>44.59</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
@@ -32289,22 +32289,22 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>55.6</v>
+        <v>52.78</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>52.03</v>
+        <v>47.91</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>46.89</v>
+        <v>44.46</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>43.41</v>
+        <v>42.91</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>42.01</v>
+        <v>41.4</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>40.96</v>
+        <v>40.73</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -32335,22 +32335,22 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>28.32</v>
+        <v>27.14</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>23.43</v>
+        <v>22.78</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="I147" s="5" t="n">
-        <v>19.72</v>
+        <v>21.51</v>
+      </c>
+      <c r="I147" s="4" t="n">
+        <v>21.86</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>20.42</v>
+        <v>23.28</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
@@ -32381,22 +32381,22 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>60.28</v>
+        <v>58.52</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>57.77</v>
+        <v>55.33</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>54.15</v>
+        <v>52.67</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>51.16</v>
+        <v>50.77</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>49.12</v>
+        <v>48.54</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>47.37</v>
+        <v>47.32</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -32427,22 +32427,22 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>66.97</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>68.68000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>71.20999999999999</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>73.67</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>73.81999999999999</v>
+        <v>64.95</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>71.58</v>
+        <v>60.9</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
@@ -32473,22 +32473,22 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>76.06</v>
+        <v>76.03</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>77.31999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>78.63</v>
+        <v>77.34</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>79.58</v>
+        <v>75.87</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>78.97</v>
+        <v>73.86</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>77.70999999999999</v>
+        <v>71.62</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -32519,22 +32519,22 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>67.26000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>67.81999999999999</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>67.95</v>
+        <v>64.47</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>68.34999999999999</v>
+        <v>62</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>67.69</v>
+        <v>60.49</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>67.76000000000001</v>
+        <v>58.87</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
@@ -32565,22 +32565,22 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>49.38</v>
+        <v>50.78</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>50.87</v>
+        <v>52.37</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>52.48</v>
+        <v>53.11</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>53.24</v>
+        <v>52.42</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>52.59</v>
+        <v>50.06</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>50.15</v>
+        <v>46.5</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -32611,22 +32611,22 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>57.56</v>
+        <v>57.02</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>57.87</v>
+        <v>57.57</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>58.77</v>
+        <v>58.38</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>60.04</v>
+        <v>58.84</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>61.12</v>
+        <v>59.02</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>61.69</v>
+        <v>57.21</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
@@ -32657,22 +32657,22 @@
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>51.68</v>
+        <v>52.17</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>52.62</v>
+        <v>53.27</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>53.86</v>
+        <v>53.73</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>54.56</v>
+        <v>51.98</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>53.22</v>
+        <v>48.57</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>49.74</v>
+        <v>44.01</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -32703,22 +32703,22 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>32.61</v>
+        <v>32.63</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>32.53</v>
+        <v>31.93</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>31.66</v>
+        <v>31.48</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>31.02</v>
+        <v>32.09</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>31.44</v>
+        <v>34.46</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>33.34</v>
+        <v>36.14</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
@@ -32749,22 +32749,22 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>45.19</v>
+        <v>44.11</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>43.9</v>
+        <v>42.8</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>42.36</v>
+        <v>41.51</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>40.79</v>
-      </c>
-      <c r="I156" s="4" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="J156" s="4" t="n">
-        <v>38.9</v>
+        <v>40.98</v>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>40.89</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -32794,23 +32794,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E157" s="5" t="n">
-        <v>19.49</v>
+      <c r="E157" s="4" t="n">
+        <v>20.6</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>21.08</v>
+        <v>21.68</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>22.38</v>
+        <v>22.3</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>23.36</v>
+        <v>22.51</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>24.11</v>
+        <v>23.14</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>24.9</v>
+        <v>24.03</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
@@ -32840,23 +32840,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E158" s="4" t="n">
-        <v>38.93</v>
+      <c r="E158" s="3" t="n">
+        <v>40.43</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>40.55</v>
+        <v>41.79</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>41.81</v>
+        <v>42.95</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>42.86</v>
+        <v>42.26</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>42.08</v>
+        <v>41.75</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>41.67</v>
+        <v>40.98</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -32886,23 +32886,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E159" s="4" t="n">
-        <v>20.59</v>
-      </c>
-      <c r="F159" s="4" t="n">
-        <v>20.07</v>
+      <c r="E159" s="5" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>19.39</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>19.61</v>
+        <v>18.94</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>19.19</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>19.73</v>
+        <v>19.47</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>20.83</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>21.04</v>
+        <v>22.62</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
@@ -32933,22 +32933,22 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F160" s="4" t="n">
-        <v>39</v>
+        <v>39.07</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>40.22</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>40.08</v>
+        <v>41.55</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>41.3</v>
+        <v>42.56</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>42.13</v>
+        <v>43.56</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>42.31</v>
+        <v>42.44</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -32979,22 +32979,22 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>55.66</v>
+        <v>55.91</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>56.31</v>
+        <v>55.53</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>55.74</v>
+        <v>55.55</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>55.6</v>
+        <v>53.92</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>53.82</v>
+        <v>52.06</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>52.28</v>
+        <v>48.9</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
@@ -33025,22 +33025,22 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>39.26</v>
+        <v>37.44</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>37.49</v>
+        <v>35.82</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>35.78</v>
+        <v>34.25</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>34.18</v>
+        <v>33.39</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>33.36</v>
+        <v>32.88</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>32.66</v>
+        <v>32.92</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -33071,22 +33071,22 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>40.75</v>
+        <v>40.48</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>40.73</v>
-      </c>
-      <c r="G163" s="3" t="n">
-        <v>40.36</v>
+        <v>40.01</v>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>38.8</v>
       </c>
       <c r="H163" s="4" t="n">
-        <v>39.36</v>
+        <v>37.07</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>37.96</v>
+        <v>35.7</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>36.75</v>
+        <v>34.37</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
@@ -33117,22 +33117,22 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>63.38</v>
+        <v>61.6</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>63.1</v>
+        <v>60.22</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>62.4</v>
+        <v>57.91</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>60.94</v>
+        <v>54.89</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>59</v>
+        <v>52.6</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>58.1</v>
+        <v>50.82</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -33163,22 +33163,22 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>63.07</v>
+        <v>62.8</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>63.91</v>
+        <v>63.1</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>64.61</v>
+        <v>61.13</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>63.15</v>
+        <v>57.12</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>59.9</v>
+        <v>54.18</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>57.66</v>
+        <v>52.88</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
@@ -33209,22 +33209,22 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>63.58</v>
+        <v>63.31</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>63.19</v>
+        <v>63.92</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>63.36</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>63.24</v>
+        <v>63.06</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>60.95</v>
+        <v>59.84</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>59.77</v>
+        <v>58.29</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -33255,22 +33255,22 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>57.63</v>
+        <v>56.46</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>55.8</v>
+        <v>55.89</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>54.92</v>
+        <v>55.35</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>53.92</v>
+        <v>54.03</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>52.1</v>
+        <v>53.17</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>49.81</v>
+        <v>53.08</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
@@ -33301,22 +33301,22 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>51.12</v>
+        <v>46.48</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>46.62</v>
+        <v>45.12</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>45.41</v>
+        <v>45.99</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>46.24</v>
+        <v>46.63</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>46.97</v>
+        <v>46.98</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>48</v>
+        <v>46.53</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -33347,22 +33347,22 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>62.91</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>63.93</v>
+        <v>66.25</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>65.5</v>
+        <v>67.45</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>66.05</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>65.78</v>
+        <v>63.07</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>64.51000000000001</v>
+        <v>60.12</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
@@ -33393,22 +33393,22 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>65.64</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>67.11</v>
+        <v>68.13</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>68.45999999999999</v>
+        <v>67.28</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>67.56</v>
+        <v>64.62</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>64.97</v>
+        <v>61.73</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>61.97</v>
+        <v>58.84</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -33439,22 +33439,22 @@
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>57.48</v>
+        <v>57.84</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>57.43</v>
+        <v>59.34</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>58.75</v>
+        <v>60.89</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>60.11</v>
+        <v>60.81</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>60</v>
+        <v>59.28</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>58.93</v>
+        <v>55.69</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
@@ -33485,22 +33485,22 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>44.85</v>
+        <v>44.76</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>45.28</v>
+        <v>45.24</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>45.86</v>
+        <v>45.99</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>46.58</v>
+        <v>45.67</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>46.1</v>
+        <v>45.48</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>45.83</v>
+        <v>44.72</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -33531,22 +33531,22 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>58.18</v>
+        <v>57.93</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>58.79</v>
+        <v>58.64</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>59.96</v>
+        <v>59.8</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>61.78</v>
+        <v>59.23</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>62.09</v>
+        <v>57.6</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>60</v>
+        <v>58.65</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
@@ -33577,22 +33577,22 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>58.76</v>
+        <v>61.09</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>61.81</v>
+        <v>62.95</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>63.91</v>
+        <v>64.05</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>65.42</v>
+        <v>63.92</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>65.91</v>
+        <v>62.67</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>64.69</v>
+        <v>63.04</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -33623,22 +33623,22 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>69.47</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>71.48999999999999</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>71.58</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>71.38</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>70.73</v>
+        <v>66.39</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>69.31</v>
+        <v>65.69</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
@@ -33669,22 +33669,22 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>75.75</v>
+        <v>75.89</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>77.3</v>
+        <v>74.64</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>76.48999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>68.87</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>72.95</v>
+        <v>65.14</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>70.45999999999999</v>
+        <v>61.93</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -33715,22 +33715,22 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>48.07</v>
+        <v>48.08</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>48.16</v>
+        <v>48.56</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>48.85</v>
+        <v>48.65</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>49.21</v>
+        <v>48.66</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>49.58</v>
+        <v>48.93</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>50.24</v>
+        <v>49.35</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
@@ -33761,22 +33761,22 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>61.5</v>
+        <v>60.97</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>61.73</v>
+        <v>60.97</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>62.3</v>
+        <v>59.55</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>62.31</v>
+        <v>56.61</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>61.79</v>
+        <v>53.8</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>59.1</v>
+        <v>53.67</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -33807,22 +33807,22 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>61.75</v>
+        <v>62.88</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>63.1</v>
+        <v>62.59</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>63.13</v>
+        <v>61.37</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>62.53</v>
+        <v>59.74</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>61.81</v>
+        <v>59.09</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>61.4</v>
+        <v>59.68</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
@@ -33853,22 +33853,22 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>61.01</v>
+        <v>61.42</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>61.69</v>
+        <v>60.3</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>60.86</v>
+        <v>57.48</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>58.28</v>
+        <v>55.4</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>56.38</v>
+        <v>53.62</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>55.39</v>
+        <v>52.65</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -33899,22 +33899,22 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>57.33</v>
+        <v>59.03</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>60.24</v>
+        <v>62.2</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>64.08</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>68.19</v>
+        <v>68.75</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>73.31999999999999</v>
+        <v>72.73</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>78.01000000000001</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
@@ -33945,22 +33945,22 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>46.62</v>
+        <v>45.84</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>45.76</v>
+        <v>45.02</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>45.08</v>
+        <v>44.8</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>44.99</v>
+        <v>44.52</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>44.9</v>
+        <v>44.22</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>45.56</v>
+        <v>44.57</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -33991,22 +33991,22 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>41.67</v>
+        <v>44.08</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>44.05</v>
+        <v>48.42</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>48.52</v>
+        <v>53.44</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>53.62</v>
+        <v>59.91</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>59.99</v>
+        <v>65.66</v>
       </c>
       <c r="J183" s="3" t="n">
-        <v>65.88</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
@@ -34036,23 +34036,23 @@
           <t>甘蔗</t>
         </is>
       </c>
-      <c r="E184" s="3" t="n">
-        <v>40.97</v>
+      <c r="E184" s="4" t="n">
+        <v>39.67</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="G184" s="3" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="H184" s="3" t="n">
-        <v>40.51</v>
-      </c>
-      <c r="I184" s="3" t="n">
-        <v>40.94</v>
-      </c>
-      <c r="J184" s="3" t="n">
-        <v>40.88</v>
+        <v>39.47</v>
+      </c>
+      <c r="G184" s="4" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="H184" s="4" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="J184" s="4" t="n">
+        <v>38.44</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -34082,23 +34082,23 @@
           <t>甘蔗</t>
         </is>
       </c>
-      <c r="E185" s="3" t="n">
-        <v>41.41</v>
-      </c>
-      <c r="F185" s="3" t="n">
-        <v>40.31</v>
+      <c r="E185" s="4" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>39.3</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>39.98</v>
-      </c>
-      <c r="H185" s="3" t="n">
-        <v>40.05</v>
+        <v>38.86</v>
+      </c>
+      <c r="H185" s="4" t="n">
+        <v>39.35</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>41.53</v>
+        <v>40.84</v>
       </c>
       <c r="J185" s="3" t="n">
-        <v>42.84</v>
+        <v>40.53</v>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
@@ -34129,22 +34129,22 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>48.19</v>
+        <v>49.38</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>49.87</v>
+        <v>50.75</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>51.96</v>
+        <v>52.74</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>54.93</v>
+        <v>55.68</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>59.16</v>
+        <v>57.62</v>
       </c>
       <c r="J186" s="3" t="n">
-        <v>63.27</v>
+        <v>59.36</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -34175,22 +34175,22 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>70.45999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>72.06</v>
+        <v>70.38</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>74.31</v>
+        <v>71.05</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>76.34</v>
+        <v>67.33</v>
       </c>
       <c r="J187" s="3" t="n">
-        <v>74.31999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
@@ -34221,22 +34221,22 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>76.17</v>
+        <v>76.23</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>77.48</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>78.81999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>79.86</v>
+        <v>76.3</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>79.29000000000001</v>
+        <v>74.34</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>78.08</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -34267,22 +34267,22 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>66.33</v>
+        <v>65.45</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>67.19</v>
+        <v>65.23</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>67.87</v>
+        <v>65.14</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>68.98</v>
+        <v>62.76</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>68.31</v>
+        <v>61.46</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>68.28</v>
+        <v>59.76</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
@@ -34313,22 +34313,22 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>49.86</v>
+        <v>51.05</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>51.23</v>
+        <v>52.46</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>52.7</v>
+        <v>53.01</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>53.32</v>
+        <v>52.18</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>52.61</v>
+        <v>49.9</v>
       </c>
       <c r="J190" s="3" t="n">
-        <v>50.29</v>
+        <v>46.45</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -34359,22 +34359,22 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>57.64</v>
+        <v>57.07</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>57.93</v>
+        <v>57.57</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>58.79</v>
+        <v>58.28</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>59.98</v>
+        <v>58.68</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>61.02</v>
+        <v>58.86</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>61.58</v>
+        <v>57.04</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
@@ -34405,22 +34405,22 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>56.21</v>
+        <v>56.13</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>56.93</v>
+        <v>57.31</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>58.45</v>
+        <v>57.94</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>59.58</v>
+        <v>56.08</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>58.51</v>
+        <v>52.69</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>55.15</v>
+        <v>47.23</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -34451,22 +34451,22 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>49.28</v>
+        <v>49.3</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>49.45</v>
+        <v>49.65</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>50.05</v>
+        <v>49.73</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>50.44</v>
+        <v>49.82</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>50.93</v>
+        <v>50.13</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>51.78</v>
+        <v>50.45</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
@@ -34497,22 +34497,22 @@
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>51.04</v>
+        <v>51.1</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>52.81</v>
+        <v>52.43</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>55.02</v>
+        <v>52.64</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>56.13</v>
+        <v>52.07</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>56.15</v>
+        <v>52.54</v>
       </c>
       <c r="J194" s="3" t="n">
-        <v>56.31</v>
+        <v>52.26</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -34543,22 +34543,22 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>64.94</v>
+        <v>66.87</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>66.67</v>
+        <v>69.11</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>69.13</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>72.70999999999999</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>74.5</v>
+        <v>66.44</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>72.53</v>
+        <v>66.58</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
@@ -34589,22 +34589,22 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>50.97</v>
+        <v>54.47</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>53.75</v>
+        <v>58.18</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>57.4</v>
+        <v>62.24</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>61.71</v>
+        <v>64.86</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>65.52</v>
+        <v>64.48</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>65.86</v>
+        <v>64.97</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -34635,22 +34635,22 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>65.23999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>65.52</v>
+        <v>64.86</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>66.22</v>
+        <v>64.92</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>67.23999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>68.15000000000001</v>
+        <v>64.14</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>68.45999999999999</v>
+        <v>62.96</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
@@ -34681,22 +34681,22 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>61.01</v>
+        <v>62.2</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>62.15</v>
+        <v>62.03</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>62.31</v>
+        <v>62.09</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>63.12</v>
+        <v>59.56</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>62.55</v>
+        <v>54.07</v>
       </c>
       <c r="J198" s="3" t="n">
-        <v>58.49</v>
+        <v>53.29</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -34727,22 +34727,22 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>65.01000000000001</v>
+        <v>64.05</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>63.96</v>
+        <v>62.1</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>62.2</v>
+        <v>60.64</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>60.97</v>
+        <v>59.23</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>59.94</v>
+        <v>56.51</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>57.19</v>
+        <v>56.63</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
@@ -34773,22 +34773,22 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>59.88</v>
+        <v>60.21</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>60.74</v>
+        <v>59.1</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>59.95</v>
+        <v>56.34</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>57.58</v>
+        <v>54.3</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>55.97</v>
+        <v>52.62</v>
       </c>
       <c r="J200" s="3" t="n">
-        <v>55</v>
+        <v>51.55</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -34819,22 +34819,22 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>67.37</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>67.76000000000001</v>
+        <v>62.74</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>65.98</v>
+        <v>58.88</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>62.72</v>
+        <v>54.67</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>58.08</v>
+        <v>50.92</v>
       </c>
       <c r="J201" s="3" t="n">
-        <v>54.72</v>
+        <v>48.81</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
@@ -34865,22 +34865,22 @@
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>57.18</v>
+        <v>57.07</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>57.03</v>
+        <v>56.23</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>56.14</v>
+        <v>54.72</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>54.53</v>
+        <v>52.1</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>51.72</v>
+        <v>48.39</v>
       </c>
       <c r="J202" s="3" t="n">
-        <v>47.21</v>
+        <v>46.62</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -34911,22 +34911,22 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>64.12</v>
+        <v>62.71</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>63.51</v>
+        <v>60.72</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>61.94</v>
+        <v>59</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>60.67</v>
+        <v>56.97</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>59.2</v>
+        <v>53.12</v>
       </c>
       <c r="J203" s="3" t="n">
-        <v>54.14</v>
+        <v>49.42</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
@@ -34957,22 +34957,22 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>63.47</v>
+        <v>59.87</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>61.02</v>
+        <v>56.54</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>58.24</v>
+        <v>53.1</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>55.31</v>
+        <v>49.25</v>
       </c>
       <c r="J204" s="3" t="n">
-        <v>50.15</v>
+        <v>46.72</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -35003,22 +35003,22 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>64.26000000000001</v>
+        <v>63.73</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>64.72</v>
+        <v>65.09</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>66.54000000000001</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>69.7</v>
+        <v>70.55</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>73.81</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="J205" s="3" t="n">
-        <v>78.04000000000001</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
@@ -35049,22 +35049,22 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>47.47</v>
+        <v>49.45</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>50.19</v>
+        <v>51.69</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>53.03</v>
+        <v>53.93</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>56.29</v>
+        <v>57.17</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>60.83</v>
+        <v>61.53</v>
       </c>
       <c r="J206" s="3" t="n">
-        <v>65.03</v>
+        <v>65.73</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -35095,22 +35095,22 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>58.19</v>
+        <v>58.01</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>60.39</v>
+        <v>60.87</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>63.23</v>
+        <v>64.58</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>68.29000000000001</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J207" s="3" t="n">
-        <v>72.72</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
@@ -35141,22 +35141,22 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>57.52</v>
+        <v>59.59</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>60.75</v>
+        <v>62.87</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>64.67</v>
+        <v>66</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>68.83</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>73.92</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>78.62</v>
+        <v>77.12</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -35187,22 +35187,22 @@
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>44.2</v>
+        <v>45.25</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>45.66</v>
+        <v>46.62</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>47.32</v>
+        <v>49.17</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>50.31</v>
+        <v>52.56</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>54.34</v>
+        <v>57.57</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>59.77</v>
+        <v>60.68</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
@@ -35233,22 +35233,22 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="F210" s="4" t="n">
-        <v>38.98</v>
+        <v>38.85</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>40.21</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>40.27</v>
+        <v>41.33</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>41.4</v>
+        <v>42.05</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="J210" s="3" t="n">
-        <v>42.22</v>
+        <v>42.19</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -35279,22 +35279,22 @@
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>43.39</v>
+        <v>44.07</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>44.52</v>
+        <v>45.03</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>45.86</v>
+        <v>47.32</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>48.73</v>
+        <v>48.28</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>50.14</v>
+        <v>48.29</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>49.58</v>
+        <v>45.7</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
@@ -35324,23 +35324,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E212" s="5" t="n">
-        <v>19.13</v>
+      <c r="E212" s="4" t="n">
+        <v>20.39</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>20.89</v>
+        <v>21.66</v>
       </c>
       <c r="G212" s="4" t="n">
         <v>22.38</v>
       </c>
       <c r="H212" s="4" t="n">
-        <v>23.47</v>
+        <v>22.56</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>24.18</v>
+        <v>23.17</v>
       </c>
       <c r="J212" s="4" t="n">
-        <v>24.88</v>
+        <v>24.02</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -35370,23 +35370,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E213" s="4" t="n">
-        <v>38.1</v>
+      <c r="E213" s="3" t="n">
+        <v>40.1</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>40.16</v>
+        <v>42</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>41.94</v>
+        <v>43.6</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>43.4</v>
+        <v>43.04</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>42.7</v>
+        <v>42.69</v>
       </c>
       <c r="J213" s="3" t="n">
-        <v>42.48</v>
+        <v>41.75</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
@@ -35416,23 +35416,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E214" s="4" t="n">
-        <v>20.53</v>
-      </c>
-      <c r="F214" s="4" t="n">
-        <v>20.01</v>
+      <c r="E214" s="5" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>19.31</v>
       </c>
       <c r="G214" s="5" t="n">
-        <v>19.53</v>
+        <v>18.87</v>
       </c>
       <c r="H214" s="5" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="I214" s="5" t="n">
-        <v>19.65</v>
+        <v>19.38</v>
+      </c>
+      <c r="I214" s="4" t="n">
+        <v>20.74</v>
       </c>
       <c r="J214" s="4" t="n">
-        <v>20.96</v>
+        <v>22.55</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -35463,22 +35463,22 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>58.14</v>
+        <v>58.21</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>58.77</v>
+        <v>56.22</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>56.87</v>
+        <v>53.39</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>54.23</v>
+        <v>49.95</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>51.15</v>
+        <v>47.36</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>48.29</v>
+        <v>44.37</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
@@ -35509,22 +35509,22 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>55.85</v>
+        <v>56.07</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>56.46</v>
+        <v>55.53</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>55.74</v>
+        <v>55.39</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>55.45</v>
+        <v>53.76</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>53.67</v>
+        <v>51.85</v>
       </c>
       <c r="J216" s="3" t="n">
-        <v>52.05</v>
+        <v>48.76</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -35554,23 +35554,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E217" s="3" t="n">
-        <v>40.72</v>
+      <c r="E217" s="4" t="n">
+        <v>38.96</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>38.95</v>
+        <v>37.29</v>
       </c>
       <c r="G217" s="4" t="n">
-        <v>37.17</v>
+        <v>35.72</v>
       </c>
       <c r="H217" s="4" t="n">
-        <v>35.52</v>
+        <v>34.89</v>
       </c>
       <c r="I217" s="4" t="n">
-        <v>34.67</v>
+        <v>34.36</v>
       </c>
       <c r="J217" s="4" t="n">
-        <v>33.94</v>
+        <v>34.29</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
@@ -35601,22 +35601,22 @@
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>57.36</v>
+        <v>55.68</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>57.3</v>
+        <v>55.13</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>57.58</v>
+        <v>54.31</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>57.98</v>
+        <v>53.44</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>58.96</v>
+        <v>52.95</v>
       </c>
       <c r="J218" s="3" t="n">
-        <v>59.93</v>
+        <v>55.67</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -35647,22 +35647,22 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>66.37</v>
+        <v>65.3</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>66.36</v>
+        <v>64.8</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>66.38</v>
+        <v>64.55</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>66.87</v>
+        <v>63.5</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>66.89</v>
+        <v>62.89</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>67.8</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
@@ -35693,22 +35693,22 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>58.6</v>
+        <v>58.4</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>58.69</v>
+        <v>58.48</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>58.96</v>
+        <v>59.09</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>59.83</v>
+        <v>59.65</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>60.8</v>
+        <v>60.56</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>62.75</v>
+        <v>63.47</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -35739,22 +35739,22 @@
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>55.63</v>
+        <v>53.66</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>54.31</v>
+        <v>52.15</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>53.25</v>
+        <v>50.66</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>52.45</v>
+        <v>49.76</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>52.61</v>
+        <v>50.7</v>
       </c>
       <c r="J221" s="3" t="n">
-        <v>55.33</v>
+        <v>55.16</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
@@ -35785,22 +35785,22 @@
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>46.35</v>
-      </c>
-      <c r="F222" s="3" t="n">
-        <v>41.69</v>
+        <v>42.59</v>
+      </c>
+      <c r="F222" s="4" t="n">
+        <v>38.66</v>
       </c>
       <c r="G222" s="4" t="n">
-        <v>37.6</v>
+        <v>36.56</v>
       </c>
       <c r="H222" s="4" t="n">
-        <v>35.4</v>
+        <v>36.31</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>35.48</v>
+        <v>36.7</v>
       </c>
       <c r="J222" s="4" t="n">
-        <v>36.3</v>
+        <v>37.98</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -35831,22 +35831,22 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>59.27</v>
+        <v>58.04</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>57.74</v>
+        <v>55.82</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>55.19</v>
+        <v>52.92</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>52.01</v>
+        <v>49.59</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>48.41</v>
+        <v>46.17</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>44.99</v>
+        <v>44.87</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
@@ -35877,22 +35877,22 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>48.92</v>
+        <v>46.39</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="G224" s="3" t="n">
-        <v>41.05</v>
+        <v>42.59</v>
+      </c>
+      <c r="G224" s="4" t="n">
+        <v>37.93</v>
       </c>
       <c r="H224" s="4" t="n">
-        <v>36.19</v>
+        <v>34.88</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>33.33</v>
+        <v>33.55</v>
       </c>
       <c r="J224" s="4" t="n">
-        <v>32.73</v>
+        <v>32.88</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -35922,23 +35922,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E225" s="3" t="n">
-        <v>40.57</v>
+      <c r="E225" s="4" t="n">
+        <v>39.38</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>37.55</v>
+        <v>36.45</v>
       </c>
       <c r="G225" s="4" t="n">
-        <v>34.06</v>
+        <v>33.77</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>31.11</v>
+        <v>32.74</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>29.89</v>
+        <v>33.23</v>
       </c>
       <c r="J225" s="4" t="n">
-        <v>31.08</v>
+        <v>34.17</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
@@ -35969,22 +35969,22 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>53.72</v>
+        <v>51.14</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>49.06</v>
+        <v>47.21</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>44.43</v>
+        <v>43.88</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="I226" s="4" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="J226" s="4" t="n">
-        <v>38.56</v>
+        <v>42.26</v>
+      </c>
+      <c r="I226" s="3" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="J226" s="3" t="n">
+        <v>40.19</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -36015,22 +36015,22 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="F227" s="4" t="n">
-        <v>20.07</v>
+        <v>20.86</v>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>18.66</v>
       </c>
       <c r="G227" s="5" t="n">
-        <v>17.64</v>
+        <v>16.43</v>
       </c>
       <c r="H227" s="5" t="n">
-        <v>15.41</v>
+        <v>15.57</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>14.57</v>
+        <v>15.53</v>
       </c>
       <c r="J227" s="5" t="n">
-        <v>14.55</v>
+        <v>16.78</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
@@ -36061,22 +36061,22 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>46.27</v>
+        <v>44.9</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>43.95</v>
-      </c>
-      <c r="G228" s="3" t="n">
-        <v>40.36</v>
+        <v>41.75</v>
+      </c>
+      <c r="G228" s="4" t="n">
+        <v>37.49</v>
       </c>
       <c r="H228" s="4" t="n">
-        <v>35.98</v>
+        <v>35.82</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>34.24</v>
+        <v>34.62</v>
       </c>
       <c r="J228" s="4" t="n">
-        <v>33.08</v>
+        <v>33.28</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -36107,22 +36107,22 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>46.27</v>
+        <v>44.9</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>43.95</v>
-      </c>
-      <c r="G229" s="3" t="n">
-        <v>40.36</v>
+        <v>41.75</v>
+      </c>
+      <c r="G229" s="4" t="n">
+        <v>37.49</v>
       </c>
       <c r="H229" s="4" t="n">
-        <v>35.98</v>
+        <v>35.82</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>34.24</v>
+        <v>34.62</v>
       </c>
       <c r="J229" s="4" t="n">
-        <v>33.08</v>
+        <v>33.28</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
@@ -36153,22 +36153,22 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>53.31</v>
+        <v>51.98</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>49.22</v>
+        <v>48.56</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>44.8</v>
+        <v>45.02</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>40.61</v>
-      </c>
-      <c r="I230" s="4" t="n">
-        <v>38.23</v>
-      </c>
-      <c r="J230" s="4" t="n">
-        <v>37.94</v>
+        <v>43.37</v>
+      </c>
+      <c r="I230" s="3" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="J230" s="3" t="n">
+        <v>42.14</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -36199,22 +36199,22 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>35.6</v>
+        <v>33.83</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>33.77</v>
+        <v>32.4</v>
       </c>
       <c r="G231" s="4" t="n">
-        <v>32.13</v>
+        <v>31.46</v>
       </c>
       <c r="H231" s="4" t="n">
-        <v>31.04</v>
+        <v>30.69</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>30.25</v>
+        <v>30.31</v>
       </c>
       <c r="J231" s="4" t="n">
-        <v>29.23</v>
+        <v>29.26</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
@@ -36245,22 +36245,22 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>58.57</v>
+        <v>54.2</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>52.76</v>
+        <v>48.1</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>46.3</v>
+        <v>43.16</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>41.24</v>
+        <v>40.44</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>38.79</v>
+        <v>39.07</v>
       </c>
       <c r="J232" s="4" t="n">
-        <v>38.28</v>
+        <v>37.83</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -36291,22 +36291,22 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>64.97</v>
+        <v>60.4</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>58.63</v>
+        <v>54.99</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>52.54</v>
+        <v>50.56</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>47.8</v>
+        <v>47.75</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>45.15</v>
+        <v>45.43</v>
       </c>
       <c r="J233" s="3" t="n">
-        <v>43.98</v>
+        <v>44.59</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
@@ -36337,22 +36337,22 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>55.6</v>
+        <v>52.78</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>52.03</v>
+        <v>47.91</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>46.89</v>
+        <v>44.46</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>43.41</v>
+        <v>42.91</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>42.01</v>
+        <v>41.4</v>
       </c>
       <c r="J234" s="3" t="n">
-        <v>40.96</v>
+        <v>40.73</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -36383,22 +36383,22 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>28.32</v>
+        <v>27.14</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>23.43</v>
+        <v>22.78</v>
       </c>
       <c r="H235" s="4" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="I235" s="5" t="n">
-        <v>19.72</v>
+        <v>21.51</v>
+      </c>
+      <c r="I235" s="4" t="n">
+        <v>21.86</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>20.42</v>
+        <v>23.28</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
@@ -36429,22 +36429,22 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>67.52</v>
+        <v>63.94</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>62.67</v>
+        <v>58.94</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>57.13</v>
+        <v>54.11</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>51.94</v>
+        <v>50.48</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>48.25</v>
+        <v>47.42</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>46.2</v>
+        <v>46.15</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -36475,22 +36475,22 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>67.81</v>
+        <v>62.44</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>63.3</v>
+        <v>58.24</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>59.48</v>
+        <v>53.3</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>54.98</v>
+        <v>48.78</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>50.74</v>
+        <v>46.12</v>
       </c>
       <c r="J237" s="3" t="n">
-        <v>47.09</v>
+        <v>45.84</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
@@ -36521,22 +36521,22 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>57.29</v>
+        <v>57.15</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>54.99</v>
+        <v>54.77</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>51.33</v>
+        <v>52.3</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>47.23</v>
+        <v>50.5</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>43.1</v>
+        <v>48.4</v>
       </c>
       <c r="J238" s="3" t="n">
-        <v>40.19</v>
+        <v>48.21</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -36567,22 +36567,22 @@
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>49.95</v>
+        <v>48.52</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>46.8</v>
+        <v>46.52</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>44.16</v>
+        <v>45.27</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="I239" s="4" t="n">
-        <v>39.27</v>
+        <v>43.94</v>
+      </c>
+      <c r="I239" s="3" t="n">
+        <v>41.78</v>
       </c>
       <c r="J239" s="4" t="n">
-        <v>37.97</v>
+        <v>39.17</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
@@ -36613,22 +36613,22 @@
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>45.13</v>
+        <v>44.08</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>43.87</v>
+        <v>42.79</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>42.34</v>
+        <v>41.53</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="I240" s="4" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="J240" s="4" t="n">
-        <v>38.99</v>
+        <v>41.06</v>
+      </c>
+      <c r="I240" s="3" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="J240" s="3" t="n">
+        <v>41.12</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -36658,23 +36658,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E241" s="5" t="n">
-        <v>19.09</v>
+      <c r="E241" s="4" t="n">
+        <v>20.24</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>20.74</v>
+        <v>21.41</v>
       </c>
       <c r="G241" s="4" t="n">
-        <v>22.14</v>
+        <v>22.12</v>
       </c>
       <c r="H241" s="4" t="n">
-        <v>23.21</v>
+        <v>22.4</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>24.03</v>
+        <v>23.09</v>
       </c>
       <c r="J241" s="4" t="n">
-        <v>24.82</v>
+        <v>23.99</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
@@ -36704,23 +36704,23 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E242" s="4" t="n">
-        <v>20.29</v>
+      <c r="E242" s="5" t="n">
+        <v>19.58</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>19.78</v>
+        <v>19.11</v>
       </c>
       <c r="G242" s="5" t="n">
-        <v>19.33</v>
+        <v>18.69</v>
       </c>
       <c r="H242" s="5" t="n">
-        <v>18.94</v>
-      </c>
-      <c r="I242" s="5" t="n">
-        <v>19.49</v>
+        <v>19.23</v>
+      </c>
+      <c r="I242" s="4" t="n">
+        <v>20.59</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>20.8</v>
+        <v>22.37</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -36751,22 +36751,22 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>39.89</v>
+        <v>38.08</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>38.11</v>
+        <v>36.43</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>36.36</v>
+        <v>34.85</v>
       </c>
       <c r="H243" s="4" t="n">
-        <v>34.72</v>
+        <v>33.99</v>
       </c>
       <c r="I243" s="4" t="n">
-        <v>33.88</v>
+        <v>33.47</v>
       </c>
       <c r="J243" s="4" t="n">
-        <v>33.17</v>
+        <v>33.46</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
@@ -36797,22 +36797,22 @@
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>41.12</v>
+        <v>40.94</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="G244" s="3" t="n">
-        <v>40.7</v>
+        <v>40.39</v>
+      </c>
+      <c r="G244" s="4" t="n">
+        <v>38.83</v>
       </c>
       <c r="H244" s="4" t="n">
-        <v>39.34</v>
+        <v>36.68</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>37.53</v>
+        <v>35.01</v>
       </c>
       <c r="J244" s="4" t="n">
-        <v>36.07</v>
+        <v>33.47</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -36843,22 +36843,22 @@
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>58.17</v>
+        <v>57.92</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>58.77</v>
+        <v>58.65</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>59.94</v>
+        <v>59.83</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>61.78</v>
+        <v>59.28</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>62.11</v>
+        <v>57.64</v>
       </c>
       <c r="J245" s="3" t="n">
-        <v>60.01</v>
+        <v>58.71</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
@@ -36889,22 +36889,22 @@
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>58.64</v>
+        <v>57.19</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>58.47</v>
+        <v>56.81</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>58.79</v>
+        <v>56.11</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>59.3</v>
+        <v>53.4</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>58.49</v>
+        <v>50.1</v>
       </c>
       <c r="J246" s="3" t="n">
-        <v>55.98</v>
+        <v>49.62</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -36935,22 +36935,22 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>69.75</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>71.81</v>
+        <v>71.05</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>70.31</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>71.67</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>70.95999999999999</v>
+        <v>66.61</v>
       </c>
       <c r="J247" s="3" t="n">
-        <v>69.47</v>
+        <v>65.88</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
@@ -36981,22 +36981,22 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>25.55</v>
+        <v>25.33</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>25.73</v>
+        <v>26.85</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>27.43</v>
+        <v>28.52</v>
       </c>
       <c r="H248" s="4" t="n">
-        <v>29.46</v>
+        <v>31.64</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>32.78</v>
-      </c>
-      <c r="J248" s="4" t="n">
-        <v>38.77</v>
+        <v>37.58</v>
+      </c>
+      <c r="J248" s="3" t="n">
+        <v>44.44</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -37027,22 +37027,22 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="F249" s="4" t="n">
-        <v>38.57</v>
+        <v>37.79</v>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>42.26</v>
       </c>
       <c r="G249" s="3" t="n">
-        <v>43.56</v>
+        <v>47.88</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>49.96</v>
+        <v>54.42</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>57.39</v>
+        <v>61.35</v>
       </c>
       <c r="J249" s="3" t="n">
-        <v>64.22</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
@@ -37073,22 +37073,22 @@
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>52.04</v>
+        <v>52.88</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>52.65</v>
+        <v>55.94</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>55.68</v>
+        <v>59.91</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>59.57</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="J250" s="3" t="n">
-        <v>73.23</v>
+        <v>79.03</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -37119,22 +37119,22 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>29.81</v>
+        <v>29.44</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>30.35</v>
+        <v>31.51</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>33.04</v>
+        <v>34.11</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>36.78</v>
+        <v>37.75</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>42.17</v>
+        <v>43.06</v>
       </c>
       <c r="J251" s="3" t="n">
-        <v>47.64</v>
+        <v>49.24</v>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
@@ -37165,22 +37165,22 @@
         </is>
       </c>
       <c r="E252" s="3" t="n">
-        <v>56.52</v>
+        <v>59.57</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>60.46</v>
+        <v>64.05</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>69.64</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>71.65000000000001</v>
-      </c>
-      <c r="I252" s="3" t="n">
-        <v>78.98</v>
+        <v>76.31999999999999</v>
+      </c>
+      <c r="I252" s="6" t="n">
+        <v>82.39</v>
       </c>
       <c r="J252" s="6" t="n">
-        <v>84.5</v>
+        <v>87.19</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -37210,23 +37210,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E253" s="4" t="n">
-        <v>37.97</v>
+      <c r="E253" s="3" t="n">
+        <v>40.37</v>
       </c>
       <c r="F253" s="3" t="n">
-        <v>40.76</v>
+        <v>43.57</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>44.28</v>
+        <v>46.91</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>48.03</v>
+        <v>51.26</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>52.76</v>
+        <v>56</v>
       </c>
       <c r="J253" s="3" t="n">
-        <v>57.51</v>
+        <v>61.9</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
@@ -37257,22 +37257,22 @@
         </is>
       </c>
       <c r="E254" s="3" t="n">
-        <v>52.59</v>
+        <v>54.81</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>55.62</v>
+        <v>58.99</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>60.31</v>
+        <v>65.2</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="I254" s="3" t="n">
-        <v>75.81999999999999</v>
+        <v>73.34</v>
+      </c>
+      <c r="I254" s="6" t="n">
+        <v>82.27</v>
       </c>
       <c r="J254" s="6" t="n">
-        <v>84.03</v>
+        <v>89.34</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -37303,22 +37303,22 @@
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>63.12</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>65.05</v>
+        <v>67.47</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>68.94</v>
+        <v>72.13</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>74.45</v>
+        <v>77.92</v>
       </c>
       <c r="I255" s="6" t="n">
-        <v>80.84</v>
+        <v>84.28</v>
       </c>
       <c r="J255" s="6" t="n">
-        <v>86.83</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
@@ -37349,22 +37349,22 @@
         </is>
       </c>
       <c r="E256" s="3" t="n">
-        <v>41.18</v>
+        <v>42.97</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>43.3</v>
+        <v>46.05</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>46.62</v>
+        <v>49.69</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>50.59</v>
+        <v>54.05</v>
       </c>
       <c r="I256" s="3" t="n">
-        <v>55.47</v>
+        <v>58.98</v>
       </c>
       <c r="J256" s="3" t="n">
-        <v>60.02</v>
+        <v>63.77</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -37395,22 +37395,22 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>28.53</v>
+        <v>30.25</v>
       </c>
       <c r="F257" s="4" t="n">
-        <v>30.64</v>
+        <v>33.13</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="H257" s="4" t="n">
-        <v>37.79</v>
+        <v>36.62</v>
+      </c>
+      <c r="H257" s="3" t="n">
+        <v>40.94</v>
       </c>
       <c r="I257" s="3" t="n">
-        <v>42.69</v>
+        <v>46.08</v>
       </c>
       <c r="J257" s="3" t="n">
-        <v>46.14</v>
+        <v>52.57</v>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
@@ -37441,22 +37441,22 @@
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="F258" s="4" t="n">
-        <v>39.46</v>
+        <v>39.43</v>
+      </c>
+      <c r="F258" s="3" t="n">
+        <v>40.54</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>40.55</v>
+        <v>41.57</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>41.46</v>
+        <v>43.44</v>
       </c>
       <c r="I258" s="3" t="n">
-        <v>43.16</v>
+        <v>46.98</v>
       </c>
       <c r="J258" s="3" t="n">
-        <v>47.13</v>
+        <v>51.76</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -37487,22 +37487,22 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>64.08</v>
+        <v>65.37</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>65.62</v>
+        <v>69.14</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>69.59</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>74.93000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I259" s="6" t="n">
-        <v>80.31999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="J259" s="6" t="n">
-        <v>85.54000000000001</v>
+        <v>88.06</v>
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
@@ -37533,22 +37533,22 @@
         </is>
       </c>
       <c r="E260" s="4" t="n">
-        <v>34.17</v>
+        <v>35.43</v>
       </c>
       <c r="F260" s="4" t="n">
-        <v>35.12</v>
+        <v>36.63</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>36.02</v>
+        <v>37.66</v>
       </c>
       <c r="H260" s="4" t="n">
-        <v>36.47</v>
-      </c>
-      <c r="I260" s="4" t="n">
-        <v>37.3</v>
+        <v>39.47</v>
+      </c>
+      <c r="I260" s="3" t="n">
+        <v>42.81</v>
       </c>
       <c r="J260" s="3" t="n">
-        <v>40.52</v>
+        <v>46.74</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -37579,22 +37579,22 @@
         </is>
       </c>
       <c r="E261" s="3" t="n">
-        <v>46.15</v>
+        <v>48.1</v>
       </c>
       <c r="F261" s="3" t="n">
-        <v>48.18</v>
+        <v>52.46</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>52.69</v>
+        <v>57.93</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>58.25</v>
+        <v>65.03</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>65.23</v>
+        <v>72.48</v>
       </c>
       <c r="J261" s="3" t="n">
-        <v>72.7</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
@@ -37625,22 +37625,22 @@
         </is>
       </c>
       <c r="E262" s="3" t="n">
-        <v>51.44</v>
+        <v>53.72</v>
       </c>
       <c r="F262" s="3" t="n">
-        <v>53.55</v>
+        <v>58.1</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>57.75</v>
+        <v>64.44</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>63.58</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="I262" s="3" t="n">
-        <v>70.05</v>
-      </c>
-      <c r="J262" s="3" t="n">
-        <v>77.64</v>
+        <v>79.51000000000001</v>
+      </c>
+      <c r="J262" s="6" t="n">
+        <v>85.45999999999999</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -37671,22 +37671,22 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>75.64</v>
+        <v>75.62</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>76.54000000000001</v>
+        <v>76.12</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>76.34</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>78.12</v>
+        <v>74.84</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J263" s="3" t="n">
-        <v>76.09</v>
+        <v>70.83</v>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
@@ -37717,22 +37717,22 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>50.23</v>
+        <v>51.32</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>51.49</v>
+        <v>52.76</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>52.99</v>
+        <v>53.44</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>53.74</v>
+        <v>52.73</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>53.14</v>
+        <v>50.44</v>
       </c>
       <c r="J264" s="3" t="n">
-        <v>50.83</v>
+        <v>46.82</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -37763,22 +37763,22 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>56.84</v>
+        <v>56.55</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>57.35</v>
+        <v>57.22</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>58.34</v>
+        <v>57.98</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>59.57</v>
+        <v>58.19</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>60.48</v>
+        <v>57.94</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>60.74</v>
+        <v>55.39</v>
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
@@ -37809,22 +37809,22 @@
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>51.2</v>
+        <v>51.58</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>52.05</v>
+        <v>52.65</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>53.95</v>
+        <v>51.27</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>52.56</v>
+        <v>47.85</v>
       </c>
       <c r="J266" s="3" t="n">
-        <v>49.1</v>
+        <v>43.28</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -37855,22 +37855,22 @@
         </is>
       </c>
       <c r="E267" s="3" t="n">
-        <v>57.87</v>
+        <v>56.83</v>
       </c>
       <c r="F267" s="3" t="n">
-        <v>56.19</v>
+        <v>56.4</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>55.46</v>
+        <v>55.98</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>54.6</v>
+        <v>54.68</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>52.82</v>
+        <v>53.72</v>
       </c>
       <c r="J267" s="3" t="n">
-        <v>50.37</v>
+        <v>53.61</v>
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
@@ -37901,22 +37901,22 @@
         </is>
       </c>
       <c r="E268" s="4" t="n">
-        <v>35.55</v>
+        <v>34.98</v>
       </c>
       <c r="F268" s="4" t="n">
-        <v>34.91</v>
+        <v>34.95</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>34.75</v>
+        <v>35.25</v>
       </c>
       <c r="H268" s="4" t="n">
-        <v>34.82</v>
+        <v>35.38</v>
       </c>
       <c r="I268" s="4" t="n">
-        <v>34.56</v>
+        <v>35.16</v>
       </c>
       <c r="J268" s="4" t="n">
-        <v>33.02</v>
+        <v>34.87</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25604,32 +25604,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>W36</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W37</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>W38</t>
+          <t>W39</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>W39</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -25665,22 +25665,22 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>64.34</v>
+        <v>66.31</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>63.24</v>
+        <v>66.17</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>62.41</v>
+        <v>66.78</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>61.79</v>
+        <v>66.28</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>59.84</v>
+        <v>63.92</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>57.94</v>
+        <v>59.41</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -25711,22 +25711,22 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>51.63</v>
+        <v>52.87</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>53.18</v>
+        <v>53.21</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>53.41</v>
+        <v>52.74</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>52.63</v>
+        <v>53.52</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>53.09</v>
+        <v>54.26</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>52.73</v>
+        <v>56.16</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -25757,22 +25757,22 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>67.93000000000001</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>70.44</v>
+        <v>70.06</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>73.22</v>
+        <v>71.89</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>72.09</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>67.15000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>66.58</v>
+        <v>69.48</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -25803,22 +25803,22 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>70.41</v>
+        <v>66.11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>71.61</v>
+        <v>67.48</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>69.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>64.12</v>
+        <v>68.22</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>64.23999999999999</v>
+        <v>70.88</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -25849,22 +25849,22 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>73.25</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>72.22</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>70.2</v>
+        <v>68.27</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>67</v>
+        <v>64.63</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>62.9</v>
+        <v>59.97</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>56.91</v>
+        <v>56.16</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -25895,22 +25895,22 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>68.88</v>
+        <v>68.69</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>67.81999999999999</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>66.11</v>
+        <v>65.52</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>63.36</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>61.98</v>
+        <v>65.03</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>60.72</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -25941,22 +25941,22 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>66.63</v>
+        <v>68.92</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>67.98</v>
+        <v>70.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>69.05</v>
+        <v>69.63</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>67.51000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>65.78</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>61.84</v>
+        <v>65.91</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -25987,22 +25987,22 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>35.87</v>
+        <v>35.34</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>35.72</v>
+        <v>35.52</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>36.01</v>
+        <v>35.96</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>36.63</v>
+        <v>36.96</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>37.88</v>
+        <v>35.92</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>36.23</v>
+        <v>35.27</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -26033,22 +26033,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>65.84</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>65.34</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>64.39</v>
+        <v>63.16</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>61.92</v>
+        <v>61.94</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>60.46</v>
+        <v>60.72</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>58.85</v>
+        <v>59.03</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -26079,22 +26079,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>50.92</v>
+        <v>53.36</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>52.46</v>
+        <v>54.52</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>53.17</v>
+        <v>54.38</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>52.45</v>
+        <v>52.93</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>50.11</v>
+        <v>50.61</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>46.54</v>
+        <v>47.6</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -26125,22 +26125,22 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>60.72</v>
+        <v>61.87</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>61.46</v>
+        <v>62.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>62.26</v>
+        <v>63.24</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>62.38</v>
+        <v>62.99</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>59.78</v>
+        <v>60.47</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -26171,22 +26171,22 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>51.9</v>
+        <v>54.02</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>52.95</v>
+        <v>55.09</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>53.37</v>
+        <v>54.19</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>51.61</v>
+        <v>51.99</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>48.2</v>
+        <v>48.67</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>43.69</v>
+        <v>45.99</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -26217,22 +26217,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>61.91</v>
+        <v>59.12</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>60.48</v>
+        <v>56.06</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>58.08</v>
+        <v>52.11</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>54.95</v>
+        <v>48.9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>52.61</v>
+        <v>46.73</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>50.89</v>
+        <v>45.99</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -26263,22 +26263,22 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>62.81</v>
+        <v>61.57</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>63.11</v>
+        <v>58.71</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>61.15</v>
+        <v>53.4</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>57.14</v>
+        <v>49.45</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>54.22</v>
+        <v>48.02</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>52.91</v>
+        <v>47.87</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -26309,22 +26309,22 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>63.31</v>
+        <v>61.58</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>63.92</v>
+        <v>61.45</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>64.54000000000001</v>
+        <v>59.22</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>63.06</v>
+        <v>55.26</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>59.84</v>
+        <v>52.64</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>58.29</v>
+        <v>51.42</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -26355,22 +26355,22 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46.8</v>
+        <v>43.39</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>45.41</v>
+        <v>43.43</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>46.22</v>
+        <v>43.11</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>46.79</v>
+        <v>42.54</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>47.06</v>
+        <v>42.63</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>46.56</v>
+        <v>44.62</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -26401,22 +26401,22 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>54.08</v>
+        <v>51.37</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>51.25</v>
+        <v>49.19</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48.86</v>
+        <v>46.82</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>46.22</v>
+        <v>46.03</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>45.01</v>
+        <v>46.07</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>45.38</v>
+        <v>45.39</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -26447,22 +26447,22 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>68.29000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>70.04000000000001</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>69.33</v>
+        <v>65.78</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>65.65000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>62.56</v>
+        <v>62.42</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -26493,22 +26493,22 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>61.44</v>
+        <v>59.65</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>60.23</v>
+        <v>57.96</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>58.86</v>
+        <v>55.87</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>57.17</v>
+        <v>51.72</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>53.66</v>
+        <v>47.64</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>48.43</v>
+        <v>46.13</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -26539,22 +26539,22 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>62.41</v>
+        <v>61</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>63.81</v>
+        <v>61.33</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>65.25</v>
+        <v>59.93</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>64.7</v>
+        <v>57.35</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>62.38</v>
+        <v>54.42</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>58.66</v>
+        <v>52.09</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -26585,22 +26585,22 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>57.9</v>
+        <v>59.22</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>58.61</v>
+        <v>60.73</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>59.77</v>
+        <v>60.72</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>59.2</v>
+        <v>59.97</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>57.58</v>
+        <v>59.47</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>58.63</v>
+        <v>59.64</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -26631,22 +26631,22 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>61.15</v>
+        <v>63.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>62.97</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>64.06999999999999</v>
+        <v>64.52</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>63.91</v>
+        <v>63.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>62.66</v>
+        <v>63.28</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>62.99</v>
+        <v>63.54</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -26677,22 +26677,22 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>70.73999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>70.55</v>
+        <v>70.86</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>69.84</v>
+        <v>70.02</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>68.34</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>66.3</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>65.65000000000001</v>
+        <v>70.03</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -26723,22 +26723,22 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>75.76000000000001</v>
+        <v>75.45</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>74.67</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>72.36</v>
+        <v>70.78</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>69.06999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>62.35</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -26769,22 +26769,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>62.91</v>
+        <v>59.35</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>57.98</v>
+        <v>54.71</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>52.83</v>
+        <v>51.6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>49.43</v>
+        <v>49.67</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>47.42</v>
+        <v>47.92</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>46.52</v>
+        <v>46.85</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -26815,22 +26815,22 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>52.09</v>
+        <v>50.77</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>50.67</v>
+        <v>49.81</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>49.62</v>
+        <v>48.72</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>48.46</v>
+        <v>47.85</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>47.72</v>
+        <v>47.63</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>47.69</v>
+        <v>47.76</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -26861,22 +26861,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>61.9</v>
+        <v>59.36</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>57.85</v>
+        <v>55.2</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>53.16</v>
+        <v>51.14</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>48.84</v>
+        <v>48.14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46.41</v>
+        <v>46.95</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>46.22</v>
+        <v>46.85</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -26907,22 +26907,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>57.62</v>
+        <v>56.95</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>55.29</v>
+        <v>55.43</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>52.77</v>
+        <v>55.03</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>50.97</v>
+        <v>55.09</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>48.92</v>
+        <v>55.58</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>48.73</v>
+        <v>56.72</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -26953,22 +26953,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>44.27</v>
+        <v>43.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>42.38</v>
+        <v>43</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>40.75</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>36.61</v>
+        <v>42.76</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>41.98</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -26999,22 +26999,22 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>52.19</v>
+        <v>50.46</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>50.85</v>
+        <v>49.35</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>49.92</v>
+        <v>48.53</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>49.41</v>
+        <v>48.14</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>49.3</v>
+        <v>48.52</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>49.99</v>
+        <v>48.24</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -27045,22 +27045,22 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>51.38</v>
+        <v>49.83</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>49.52</v>
+        <v>47.32</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>47.24</v>
+        <v>45.93</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>46.35</v>
+        <v>45.63</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>45.96</v>
+        <v>46.51</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>46.19</v>
+        <v>47.76</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -27091,22 +27091,22 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>44.08</v>
+        <v>44.83</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>45.03</v>
+        <v>46.85</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>47.32</v>
+        <v>47.51</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>48.28</v>
+        <v>47.09</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>48.29</v>
+        <v>45.71</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>45.7</v>
+        <v>44.35</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -27137,22 +27137,22 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>20.49</v>
+        <v>21.8</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>21.76</v>
+        <v>22.49</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>22.48</v>
+        <v>22.59</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>22.66</v>
+        <v>23.07</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23.26</v>
+        <v>24.01</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>24.12</v>
+        <v>25.61</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -27183,22 +27183,22 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>40.19</v>
+        <v>41.39</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>42.08</v>
+        <v>42.67</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>43.67</v>
+        <v>41.82</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>43.1</v>
+        <v>41.11</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>42.74</v>
+        <v>41.01</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>41.8</v>
+        <v>40.9</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -27229,22 +27229,22 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>19.79</v>
+        <v>18.89</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>19.3</v>
+        <v>18.28</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>18.86</v>
+        <v>18.61</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>19.37</v>
+        <v>19.65</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20.73</v>
+        <v>21.24</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>22.54</v>
+        <v>23.9</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -27274,23 +27274,23 @@
           <t>大麦</t>
         </is>
       </c>
-      <c r="E37" s="4" t="n">
-        <v>39.73</v>
+      <c r="E37" s="3" t="n">
+        <v>40.37</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>40.76</v>
+        <v>41.4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>41.97</v>
+        <v>42.1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>42.92</v>
+        <v>42.66</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>42.61</v>
+        <v>41.99</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>39.99</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -27321,22 +27321,22 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>56.08</v>
+        <v>54.99</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>55.54</v>
+        <v>54.53</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>55.4</v>
+        <v>52.55</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>53.76</v>
+        <v>50.18</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>51.84</v>
+        <v>48.13</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>48.76</v>
+        <v>46.88</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -27367,22 +27367,22 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>39.02</v>
+        <v>37.55</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>37.38</v>
+        <v>36.08</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>35.84</v>
+        <v>35.32</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>35.02</v>
+        <v>34.83</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>34.5</v>
+        <v>34.52</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>34.43</v>
+        <v>34.74</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -27413,22 +27413,22 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>40.87</v>
+        <v>41.57</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>40.38</v>
+        <v>40.67</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>38.98</v>
+        <v>39.06</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>37.02</v>
+        <v>37.69</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>35.47</v>
+        <v>37.04</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>34.01</v>
+        <v>37.71</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -27459,22 +27459,22 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>55.16</v>
+        <v>55.11</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>54.59</v>
+        <v>54.44</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>53.73</v>
+        <v>53.81</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>52.83</v>
+        <v>53.7</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>52.32</v>
+        <v>54.68</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>55.04</v>
+        <v>58.5</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -27505,22 +27505,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>65.09</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>64.56</v>
+        <v>65.5</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>64.31</v>
+        <v>64.88</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>63.27</v>
+        <v>64.78</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>62.66</v>
+        <v>65.75</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>65.73999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -27551,22 +27551,22 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>58.12</v>
+        <v>58.73</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>58.19</v>
+        <v>59.59</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>58.79</v>
+        <v>60.49</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>59.31</v>
+        <v>61.96</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>60.2</v>
+        <v>64.28</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>63.08</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -27597,22 +27597,22 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>53.67</v>
+        <v>51.89</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>52.15</v>
+        <v>50.2</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>50.66</v>
+        <v>49.04</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>49.76</v>
+        <v>49.6</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>50.7</v>
+        <v>52.24</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>55.16</v>
+        <v>58.34</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -27643,22 +27643,22 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>57.69</v>
+        <v>59.03</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>58.49</v>
+        <v>60.59</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>59.73</v>
+        <v>60.64</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>59.26</v>
+        <v>59.95</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>57.73</v>
+        <v>59.52</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>58.8</v>
+        <v>59.8</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -27689,22 +27689,22 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>67.66</v>
+        <v>66.62</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>70.38</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>73.48999999999999</v>
+        <v>72.09</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>67.06999999999999</v>
+        <v>70.44</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>66.16</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -27735,22 +27735,22 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>51.52</v>
+        <v>48.77</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>49.17</v>
+        <v>47.62</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>48.41</v>
+        <v>48.29</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>49.57</v>
+        <v>48.97</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>50.8</v>
+        <v>51.01</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>54.26</v>
+        <v>50.45</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -27781,22 +27781,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>51.79</v>
+        <v>51.19</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>51.13</v>
+        <v>50.74</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>50.65</v>
+        <v>49.64</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>49.54</v>
+        <v>47.78</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>47.78</v>
+        <v>45.01</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>45.11</v>
+        <v>41.59</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -27827,22 +27827,22 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>57.1</v>
+        <v>57.31</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>60.53</v>
+        <v>60.83</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>64.43000000000001</v>
+        <v>63.86</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>66.68000000000001</v>
+        <v>65.67</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>67.34999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -27873,22 +27873,22 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>66.29000000000001</v>
+        <v>60.49</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>61.11</v>
+        <v>56.97</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>58.1</v>
+        <v>56.04</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>57.91</v>
+        <v>56.37</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>59.2</v>
+        <v>57.33</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>61.03</v>
+        <v>54.98</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -27919,22 +27919,22 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>70.64</v>
+        <v>66.25</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>71.18000000000001</v>
+        <v>66.97</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>71.56</v>
+        <v>67.36</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>69.18000000000001</v>
+        <v>67.45</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>64.29000000000001</v>
+        <v>68.03</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -27965,22 +27965,22 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>62.9</v>
+        <v>59.35</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>57.99</v>
+        <v>54.72</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>52.85</v>
+        <v>51.61</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>49.45</v>
+        <v>49.68</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>47.44</v>
+        <v>47.93</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>46.54</v>
+        <v>46.86</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -28011,22 +28011,22 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>51.93</v>
+        <v>50.63</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>50.54</v>
+        <v>49.72</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>49.55</v>
+        <v>48.67</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>48.43</v>
+        <v>47.83</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>47.73</v>
+        <v>47.63</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>47.7</v>
+        <v>47.77</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -28057,22 +28057,22 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>61.73</v>
+        <v>59.24</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>57.73</v>
+        <v>55.11</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>53.07</v>
+        <v>51.07</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>48.8</v>
+        <v>48.13</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>46.42</v>
+        <v>46.97</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>46.25</v>
+        <v>46.89</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -28103,22 +28103,22 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>58.41</v>
+        <v>58.07</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>56.38</v>
+        <v>56.75</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>54.06</v>
+        <v>56.3</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>52.19</v>
+        <v>56.4</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>50.18</v>
+        <v>56.76</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>49.68</v>
+        <v>58.35</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -28149,22 +28149,22 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>44.87</v>
+        <v>44.36</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>42.89</v>
+        <v>43.44</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>41.14</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>39.61</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>37.88</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>36.88</v>
+        <v>43.14</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>42.48</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -28195,22 +28195,22 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>51.78</v>
+        <v>50.13</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>50.51</v>
+        <v>49.13</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>49.7</v>
+        <v>48.39</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>49.26</v>
+        <v>48.11</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>49.27</v>
+        <v>48.58</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>50.04</v>
+        <v>48.31</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -28241,22 +28241,22 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>56.86</v>
+        <v>57.02</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>56.06</v>
+        <v>55.83</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>54.57</v>
+        <v>53.76</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>51.99</v>
+        <v>50.44</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>48.34</v>
+        <v>47.06</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>46.6</v>
+        <v>43.73</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -28287,22 +28287,22 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>63.12</v>
+        <v>61.57</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>61.18</v>
+        <v>60.16</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>59.47</v>
+        <v>58.56</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>57.41</v>
+        <v>55.02</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>53.46</v>
+        <v>51.11</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>49.64</v>
+        <v>48.52</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -28333,22 +28333,22 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>54.61</v>
+        <v>54.28</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>54.38</v>
+        <v>54.45</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>54.48</v>
+        <v>55.02</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>54.96</v>
+        <v>55.81</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>55.39</v>
+        <v>55.82</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>53.77</v>
+        <v>55.77</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -28379,22 +28379,22 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>62.73</v>
+        <v>60.86</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>59.83</v>
+        <v>58.03</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>56.52</v>
+        <v>55.14</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>53.08</v>
+        <v>51.73</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>49.23</v>
+        <v>48.27</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>46.7</v>
+        <v>45.87</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -28425,22 +28425,22 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>49.07</v>
+        <v>50.44</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>51.34</v>
+        <v>51.53</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>53.47</v>
+        <v>53.17</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>56.71</v>
+        <v>54.99</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>60.85</v>
+        <v>56.95</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>61.08</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -28471,22 +28471,22 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>59.48</v>
+        <v>61.73</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>62.63</v>
+        <v>63.93</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>65.62</v>
+        <v>66.17</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>69.05</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>73.08</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>76.83</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -28517,22 +28517,22 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>63.44</v>
+        <v>64.77</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>64.87</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>67.34999999999999</v>
+        <v>68.78</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>70.48999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>74.39</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>77.67</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -28563,22 +28563,22 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>58.75</v>
+        <v>58.72</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>59.72</v>
+        <v>59.57</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>61.52</v>
+        <v>61.76</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>65.19</v>
+        <v>62.74</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>68.31999999999999</v>
+        <v>62.45</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>70.65000000000001</v>
+        <v>63.84</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -28609,22 +28609,22 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>62.78</v>
+        <v>63.07</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>64.03</v>
+        <v>65.06</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>66.89</v>
+        <v>69.52</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>72.23</v>
+        <v>74.83</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>78.66</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>83.11</v>
+        <v>80.81</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -28655,22 +28655,22 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>44.33</v>
+        <v>43.4</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>43.08</v>
+        <v>42.4</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>41.89</v>
+        <v>42.29</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>41.52</v>
+        <v>42.53</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>41.39</v>
+        <v>42.71</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>41.67</v>
+        <v>40.79</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
@@ -28701,22 +28701,22 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>40.23</v>
+        <v>39.28</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>39.96</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>41.34</v>
+        <v>40.41</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>42.06</v>
+        <v>41.11</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>42.8</v>
+        <v>41.69</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>42.2</v>
+        <v>42.37</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -28747,22 +28747,22 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>20.98</v>
+        <v>22.27</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>22.24</v>
+        <v>22.97</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>22.98</v>
+        <v>23.08</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>23.2</v>
+        <v>23.58</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>23.84</v>
+        <v>24.51</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>24.72</v>
+        <v>26.14</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
@@ -28793,22 +28793,22 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>40.13</v>
+        <v>41.34</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>42.03</v>
+        <v>42.62</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>43.63</v>
+        <v>41.78</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>43.07</v>
+        <v>41.08</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>42.72</v>
+        <v>40.99</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>41.79</v>
+        <v>40.88</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -28839,22 +28839,22 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>19.81</v>
+        <v>18.91</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>19.31</v>
+        <v>18.3</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>19.39</v>
+        <v>19.67</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>20.75</v>
+        <v>21.26</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>22.56</v>
+        <v>23.92</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
@@ -28884,23 +28884,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E72" s="4" t="n">
-        <v>39.47</v>
+      <c r="E72" s="3" t="n">
+        <v>40.1</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>40.49</v>
+        <v>41.15</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>41.71</v>
+        <v>41.88</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>42.68</v>
+        <v>42.47</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>43.65</v>
-      </c>
-      <c r="J72" s="3" t="n">
-        <v>42.5</v>
+        <v>41.89</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>39.94</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -28931,22 +28931,22 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>56.09</v>
+        <v>54.99</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>55.55</v>
+        <v>54.54</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>55.4</v>
+        <v>52.55</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>53.77</v>
+        <v>50.18</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>51.85</v>
+        <v>48.13</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>48.77</v>
+        <v>46.89</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
@@ -28977,22 +28977,22 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>39.04</v>
+        <v>37.57</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>37.4</v>
+        <v>36.12</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>35.87</v>
+        <v>35.36</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>35.05</v>
+        <v>34.88</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>34.54</v>
+        <v>34.57</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>34.47</v>
+        <v>34.79</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -29023,22 +29023,22 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>40.99</v>
+        <v>41.65</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>40.49</v>
+        <v>40.81</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>39.17</v>
+        <v>39.28</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>37.3</v>
+        <v>37.98</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>35.84</v>
+        <v>37.37</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>34.45</v>
+        <v>38.03</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
@@ -29069,22 +29069,22 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>30.6</v>
+        <v>31.71</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>31.57</v>
+        <v>33.62</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>33.39</v>
+        <v>35.09</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>34.76</v>
+        <v>35.75</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>35.45</v>
+        <v>35.8</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>34.87</v>
+        <v>35.49</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -29115,22 +29115,22 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>54.46</v>
+        <v>54.44</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>53.88</v>
+        <v>53.76</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>52.99</v>
+        <v>53.1</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>52.03</v>
+        <v>53</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>51.47</v>
+        <v>53.97</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>54.15</v>
+        <v>57.75</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
@@ -29161,22 +29161,22 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>34</v>
+        <v>33.12</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>32.9</v>
+        <v>31.94</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>31.27</v>
+        <v>32.13</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>31.66</v>
+        <v>33.48</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>34.2</v>
+        <v>34.27</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -29207,22 +29207,22 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>64.81</v>
+        <v>65.2</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>64.3</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>64.03</v>
+        <v>64.62</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>62.99</v>
+        <v>64.55</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>62.4</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>65.5</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -29253,22 +29253,22 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>57.72</v>
+        <v>58.35</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>57.78</v>
+        <v>59.15</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>58.31</v>
+        <v>60</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>58.76</v>
+        <v>61.4</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>59.55</v>
+        <v>63.64</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>62.34</v>
+        <v>68.13</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -29299,22 +29299,22 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>53.57</v>
+        <v>51.8</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>52.06</v>
+        <v>50.13</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>50.58</v>
+        <v>48.99</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>49.71</v>
+        <v>49.56</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>50.65</v>
+        <v>52.2</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>55.11</v>
+        <v>58.29</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -29345,22 +29345,22 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>35.65</v>
+        <v>37.34</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>38.09</v>
+        <v>38.3</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>39.5</v>
+        <v>37.51</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>39.37</v>
+        <v>35.23</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>37.89</v>
+        <v>33.17</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>35.82</v>
+        <v>31.22</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -29391,22 +29391,22 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>56.58</v>
+        <v>56.2</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>56.07</v>
+        <v>55.9</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>55.61</v>
+        <v>54.91</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>54.37</v>
+        <v>54.45</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>53.55</v>
+        <v>54.63</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>53.48</v>
+        <v>53.77</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -29437,22 +29437,22 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>48.06</v>
+        <v>45.06</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.94</v>
+        <v>45.09</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>47.67</v>
+        <v>44.72</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>48.08</v>
+        <v>44.09</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>48.15</v>
+        <v>44.17</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>47.6</v>
+        <v>45.83</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -29483,22 +29483,22 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>44.19</v>
+        <v>46.45</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>46.07</v>
+        <v>46.71</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>46.14</v>
+        <v>45.4</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>40.78</v>
+        <v>41.95</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>39</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>38.05</v>
+        <v>37.37</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -29529,22 +29529,22 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>57.15</v>
+        <v>56.33</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>56.78</v>
+        <v>55.51</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>56.21</v>
+        <v>53.68</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>54.69</v>
+        <v>49.88</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>51.33</v>
+        <v>45.98</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>46.24</v>
+        <v>44.47</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -29575,22 +29575,22 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>38.16</v>
+        <v>37.05</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>37.07</v>
+        <v>36.55</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>36.51</v>
+        <v>35.46</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>35.43</v>
+        <v>34.33</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>34.41</v>
+        <v>34.15</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>34.2</v>
+        <v>32.46</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -29620,23 +29620,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E88" s="4" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="F88" s="4" t="n">
-        <v>39.91</v>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v>39.58</v>
+      <c r="E88" s="3" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>40.67</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>39.04</v>
+        <v>39.64</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>37.51</v>
+        <v>37.31</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>36.19</v>
+        <v>33.1</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -29667,22 +29667,22 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>58.03</v>
+        <v>59.33</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>58.76</v>
+        <v>60.81</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>59.91</v>
+        <v>60.78</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>59.35</v>
+        <v>60.07</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>57.79</v>
+        <v>59.61</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>58.84</v>
+        <v>59.85</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -29713,22 +29713,22 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>61.05</v>
+        <v>63.12</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>62.89</v>
+        <v>64.41</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>64.01000000000001</v>
+        <v>64.44</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>63.84</v>
+        <v>63.49</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>62.55</v>
+        <v>63.13</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>62.81</v>
+        <v>63.44</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -29759,22 +29759,22 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>70.94</v>
+        <v>71.37</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>70.75</v>
+        <v>71.06</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>70.01000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>68.47</v>
+        <v>69.09</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>65.73</v>
+        <v>70.19</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
@@ -29805,22 +29805,22 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>58.84</v>
+        <v>58.21</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>58.25</v>
+        <v>57.74</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>57.73</v>
+        <v>56.44</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>56.41</v>
+        <v>54.19</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>54.18</v>
+        <v>50.8</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>50.87</v>
+        <v>46.11</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -29851,22 +29851,22 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>48.77</v>
+        <v>50.4</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>51.64</v>
+        <v>51.8</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>54.38</v>
+        <v>53.79</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>58.36</v>
+        <v>54.78</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>62.26</v>
+        <v>55.37</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>65.68000000000001</v>
+        <v>59.13</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
@@ -29897,22 +29897,22 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>46.03</v>
+        <v>44.31</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>45.05</v>
+        <v>43.24</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>44.64</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>44.23</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>43.65</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>43.81</v>
+        <v>41.77</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>39.64</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -29943,22 +29943,22 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>47.9</v>
+        <v>51.34</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>51.9</v>
+        <v>55.89</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>57.27</v>
+        <v>61.27</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>63.8</v>
+        <v>65.92</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>70.05</v>
+        <v>69.36</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>74.65000000000001</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
@@ -29989,22 +29989,22 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>39.9</v>
+        <v>39.1</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>39.6</v>
+        <v>38.44</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>39.56</v>
+        <v>37.53</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>39.57</v>
+        <v>35.8</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>39.25</v>
+        <v>35.22</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>38.97</v>
+        <v>35.8</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -30035,22 +30035,22 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>61.89</v>
+        <v>61.15</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>62.17</v>
+        <v>61.05</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>63.06</v>
+        <v>62.9</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>66.39</v>
+        <v>64.23</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>69.79000000000001</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>72.94</v>
+        <v>65.88</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
@@ -30081,22 +30081,22 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>49.08</v>
+        <v>49.51</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>50.53</v>
+        <v>50.28</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>52.57</v>
+        <v>51.32</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>55.46</v>
+        <v>50.26</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>57.33</v>
+        <v>49.78</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>58.98</v>
+        <v>53.33</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -30127,22 +30127,22 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>64.36</v>
+        <v>66.2</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>65.19</v>
+        <v>67.31</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>65.76000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>63.96</v>
+        <v>65.14</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>61.83</v>
+        <v>63.17</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>58.01</v>
+        <v>62.58</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -30173,22 +30173,22 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>37.28</v>
+        <v>37.54</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>37.49</v>
+        <v>38.3</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>38.2</v>
+        <v>38.88</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>38.71</v>
+        <v>39.45</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>39.15</v>
+        <v>37.81</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>36.93</v>
+        <v>36.59</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -30219,22 +30219,22 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>57.34</v>
+        <v>57.63</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>57.13</v>
+        <v>56.97</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>56.31</v>
+        <v>56.11</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>55.28</v>
+        <v>55.66</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>54.55</v>
+        <v>56.24</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>57</v>
+        <v>59.53</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -30265,22 +30265,22 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>38.84</v>
+        <v>38.25</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>38.12</v>
+        <v>37.56</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>37.43</v>
+        <v>37.71</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="I102" s="4" t="n">
-        <v>38.49</v>
+        <v>38.77</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>40.49</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>41.09</v>
+        <v>41.3</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -30311,22 +30311,22 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>59.19</v>
+        <v>55.2</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>55.93</v>
+        <v>51.95</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>52.82</v>
+        <v>49.58</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>50.61</v>
+        <v>48.25</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>49.68</v>
+        <v>47.85</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>49.95</v>
+        <v>46.87</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -30357,22 +30357,22 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>39.09</v>
+        <v>33.81</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>35</v>
+        <v>30.6</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>32.21</v>
+        <v>28.15</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>30.37</v>
+        <v>26.12</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>29.44</v>
+        <v>26.15</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>31.22</v>
+        <v>26.64</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -30403,22 +30403,22 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>55.65</v>
+        <v>55.09</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>54.67</v>
+        <v>54.24</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>53.79</v>
+        <v>53.61</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>53.27</v>
+        <v>52.79</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>52.87</v>
+        <v>50.82</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>51.85</v>
+        <v>49.52</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -30449,22 +30449,22 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>45.85</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>42.82</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>40.84</v>
+        <v>41.35</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>36.54</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>39.23</v>
+        <v>34.75</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="J106" s="3" t="n">
-        <v>40.4</v>
+        <v>35.16</v>
+      </c>
+      <c r="J106" s="4" t="n">
+        <v>35.41</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -30495,22 +30495,22 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>53.73</v>
+        <v>47.53</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>43.88</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>40.66</v>
+        <v>42.28</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>35.17</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>38.93</v>
+        <v>34.15</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>39.52</v>
+        <v>33.96</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -30541,22 +30541,22 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>54.34</v>
+        <v>52.69</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>51.99</v>
+        <v>50.91</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>49.88</v>
+        <v>50.55</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>49</v>
+        <v>50.69</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>48.38</v>
+        <v>51.11</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>49.61</v>
+        <v>49.41</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -30587,22 +30587,22 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>54.64</v>
+        <v>48.36</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>45.54</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>41.77</v>
+        <v>43.61</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>35.69</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="J109" s="3" t="n">
-        <v>40.39</v>
+        <v>35.05</v>
+      </c>
+      <c r="J109" s="4" t="n">
+        <v>35.28</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -30633,22 +30633,22 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>34.08</v>
+        <v>34.94</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>34.01</v>
+        <v>35.68</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>34.19</v>
+        <v>36.61</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>34.23</v>
+        <v>37.49</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>33.7</v>
+        <v>37.71</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>32.72</v>
+        <v>36.7</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -30679,22 +30679,22 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>33.51</v>
+        <v>32.38</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>32.52</v>
+        <v>30.66</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>30.91</v>
+        <v>28.87</v>
       </c>
       <c r="H111" s="4" t="n">
-        <